--- a/final_score_table/forecast_zscores_wide.xlsx
+++ b/final_score_table/forecast_zscores_wide.xlsx
@@ -414,7 +414,7 @@
         <v>2024</v>
       </c>
       <c r="C2">
-        <v>0.2047503575580006</v>
+        <v>-0.2047503575580006</v>
       </c>
       <c r="D2">
         <v>1.088643224174508</v>
@@ -446,7 +446,7 @@
         <v>2025</v>
       </c>
       <c r="C3">
-        <v>0.4089429145988393</v>
+        <v>-0.4089429145988393</v>
       </c>
       <c r="D3">
         <v>1.068996857323751</v>
@@ -478,7 +478,7 @@
         <v>2026</v>
       </c>
       <c r="C4">
-        <v>0.4900056133628146</v>
+        <v>-0.4900056133628146</v>
       </c>
       <c r="D4">
         <v>1.061511947544306</v>
@@ -510,7 +510,7 @@
         <v>2027</v>
       </c>
       <c r="C5">
-        <v>0.6503556080621492</v>
+        <v>-0.6503556080621492</v>
       </c>
       <c r="D5">
         <v>1.039959373099151</v>
@@ -542,7 +542,7 @@
         <v>2028</v>
       </c>
       <c r="C6">
-        <v>0.7380949901130263</v>
+        <v>-0.7380949901130263</v>
       </c>
       <c r="D6">
         <v>1.026874569841009</v>
@@ -574,7 +574,7 @@
         <v>2024</v>
       </c>
       <c r="C7">
-        <v>0.9309513912651732</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0.7974182992894058</v>
@@ -606,7 +606,7 @@
         <v>2025</v>
       </c>
       <c r="C8">
-        <v>1.243615167443926</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0.9368560921624454</v>
@@ -638,7 +638,7 @@
         <v>2026</v>
       </c>
       <c r="C9">
-        <v>1.348562884586847</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>1.042266216579894</v>
@@ -670,7 +670,7 @@
         <v>2027</v>
       </c>
       <c r="C10">
-        <v>1.570393950438111</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>1.0996642471092</v>
@@ -702,7 +702,7 @@
         <v>2028</v>
       </c>
       <c r="C11">
-        <v>1.682779980410776</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>1.141220600339714</v>
@@ -734,7 +734,7 @@
         <v>2024</v>
       </c>
       <c r="C12">
-        <v>0.2913741423697488</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0.6105486193744318</v>
@@ -766,7 +766,7 @@
         <v>2025</v>
       </c>
       <c r="C13">
-        <v>0.4999701650184121</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0.5435913002277679</v>
@@ -798,7 +798,7 @@
         <v>2026</v>
       </c>
       <c r="C14">
-        <v>0.5743346207263206</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0.6652865840407556</v>
@@ -830,7 +830,7 @@
         <v>2027</v>
       </c>
       <c r="C15">
-        <v>0.7317004182140671</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0.6344481204097908</v>
@@ -862,7 +862,7 @@
         <v>2028</v>
       </c>
       <c r="C16">
-        <v>0.8126359322501562</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0.7162688728861804</v>
@@ -894,7 +894,7 @@
         <v>2024</v>
       </c>
       <c r="C17">
-        <v>-0.7950737117006716</v>
+        <v>0.7950737117006716</v>
       </c>
       <c r="D17">
         <v>1.889586441867893</v>
@@ -926,7 +926,7 @@
         <v>2025</v>
       </c>
       <c r="C18">
-        <v>-0.7376150024351756</v>
+        <v>0.7376150024351756</v>
       </c>
       <c r="D18">
         <v>1.858574745939966</v>
@@ -958,7 +958,7 @@
         <v>2026</v>
       </c>
       <c r="C19">
-        <v>-0.7023642967509975</v>
+        <v>0.7023642967509975</v>
       </c>
       <c r="D19">
         <v>1.848162238883517</v>
@@ -990,7 +990,7 @@
         <v>2027</v>
       </c>
       <c r="C20">
-        <v>-0.6392779393388621</v>
+        <v>0.6392779393388621</v>
       </c>
       <c r="D20">
         <v>1.816237940419469</v>
@@ -1022,7 +1022,7 @@
         <v>2028</v>
       </c>
       <c r="C21">
-        <v>-0.5932044281480345</v>
+        <v>0.5932044281480345</v>
       </c>
       <c r="D21">
         <v>1.794950853632645</v>
@@ -1043,7 +1043,7 @@
         <v>0.3188087441796537</v>
       </c>
       <c r="J21">
-        <v>4.390549192683923</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1054,7 +1054,7 @@
         <v>2024</v>
       </c>
       <c r="C22">
-        <v>-0.7869106322107737</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0.7773893227680161</v>
@@ -1086,7 +1086,7 @@
         <v>2025</v>
       </c>
       <c r="C23">
-        <v>-0.7556281716036514</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0.749425992882634</v>
@@ -1118,7 +1118,7 @@
         <v>2026</v>
       </c>
       <c r="C24">
-        <v>-0.7357275883741345</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0.7340510641908564</v>
@@ -1150,7 +1150,7 @@
         <v>2027</v>
       </c>
       <c r="C25">
-        <v>-0.6933595785866249</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0.7075057793202223</v>
@@ -1182,7 +1182,7 @@
         <v>2028</v>
       </c>
       <c r="C26">
-        <v>-0.6622346495545581</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0.6891551391905344</v>
@@ -1214,7 +1214,7 @@
         <v>2024</v>
       </c>
       <c r="C27">
-        <v>-0.565022285812565</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0.04761720890301822</v>
@@ -1243,7 +1243,7 @@
         <v>2025</v>
       </c>
       <c r="C28">
-        <v>-0.5332027104066973</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>-0.02160743430014859</v>
@@ -1272,7 +1272,7 @@
         <v>2026</v>
       </c>
       <c r="C29">
-        <v>-0.5214995714101364</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>-0.08232596012692903</v>
@@ -1301,7 +1301,7 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>-0.4845402721671402</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>-0.1451245691150496</v>
@@ -1330,7 +1330,7 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>-0.4647899677756821</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>-0.1993966232126926</v>
@@ -1359,7 +1359,7 @@
         <v>2024</v>
       </c>
       <c r="C32">
-        <v>2.378795884306607</v>
+        <v>-4</v>
       </c>
       <c r="D32">
         <v>1.603790430453003</v>
@@ -1385,7 +1385,7 @@
         <v>2025</v>
       </c>
       <c r="C33">
-        <v>2.970391248394523</v>
+        <v>-4</v>
       </c>
       <c r="D33">
         <v>1.574613302673614</v>
@@ -1411,7 +1411,7 @@
         <v>2026</v>
       </c>
       <c r="C34">
-        <v>3.19654350155972</v>
+        <v>-4</v>
       </c>
       <c r="D34">
         <v>1.562465419853307</v>
@@ -1437,7 +1437,7 @@
         <v>2027</v>
       </c>
       <c r="C35">
-        <v>3.62103904022804</v>
+        <v>-4</v>
       </c>
       <c r="D35">
         <v>1.531756860502582</v>
@@ -1463,7 +1463,7 @@
         <v>2028</v>
       </c>
       <c r="C36">
-        <v>3.863042648548745</v>
+        <v>-4</v>
       </c>
       <c r="D36">
         <v>1.511013753543208</v>
@@ -1489,7 +1489,7 @@
         <v>2024</v>
       </c>
       <c r="C37">
-        <v>-0.9298697504667764</v>
+        <v>1.859739500933553</v>
       </c>
       <c r="D37">
         <v>1.79822778018215</v>
@@ -1512,7 +1512,7 @@
         <v>2025</v>
       </c>
       <c r="C38">
-        <v>-0.7857114675786532</v>
+        <v>1.571422935157306</v>
       </c>
       <c r="D38">
         <v>1.855465789882804</v>
@@ -1535,7 +1535,7 @@
         <v>2026</v>
       </c>
       <c r="C39">
-        <v>-0.6943278678674409</v>
+        <v>1.388655735734882</v>
       </c>
       <c r="D39">
         <v>1.892281018225264</v>
@@ -1558,7 +1558,7 @@
         <v>2027</v>
       </c>
       <c r="C40">
-        <v>-0.554391603443945</v>
+        <v>1.10878320688789</v>
       </c>
       <c r="D40">
         <v>1.930856101561249</v>
@@ -1581,7 +1581,7 @@
         <v>2028</v>
       </c>
       <c r="C41">
-        <v>-0.4395040220172894</v>
+        <v>0.8790080440345789</v>
       </c>
       <c r="D41">
         <v>1.957489842603969</v>
@@ -1604,7 +1604,7 @@
         <v>2024</v>
       </c>
       <c r="C42">
-        <v>-0.1314014531380753</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0.1087511595139274</v>
@@ -1636,7 +1636,7 @@
         <v>2025</v>
       </c>
       <c r="C43">
-        <v>0.04313611544181436</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0.05231929293203925</v>
@@ -1668,7 +1668,7 @@
         <v>2026</v>
       </c>
       <c r="C44">
-        <v>0.1200753010000356</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>-0.0314745326756545</v>
@@ -1700,7 +1700,7 @@
         <v>2027</v>
       </c>
       <c r="C45">
-        <v>0.2645742009934685</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>-0.08692041029094442</v>
@@ -1732,7 +1732,7 @@
         <v>2028</v>
       </c>
       <c r="C46">
-        <v>0.3513708003105606</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>-0.1574333286503674</v>
@@ -1764,7 +1764,7 @@
         <v>2024</v>
       </c>
       <c r="C47">
-        <v>1.021481643638772</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>-0.08121491716450326</v>
@@ -1796,7 +1796,7 @@
         <v>2025</v>
       </c>
       <c r="C48">
-        <v>1.338023004374662</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>-0.1437278528107072</v>
@@ -1828,7 +1828,7 @@
         <v>2026</v>
       </c>
       <c r="C49">
-        <v>1.442205275193656</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>-0.1972361745015511</v>
@@ -1860,7 +1860,7 @@
         <v>2027</v>
       </c>
       <c r="C50">
-        <v>1.665508454828213</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>-0.251876882002566</v>
@@ -1892,7 +1892,7 @@
         <v>2028</v>
       </c>
       <c r="C51">
-        <v>1.775670219850402</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>-0.2985781367665969</v>
@@ -1924,7 +1924,7 @@
         <v>2024</v>
       </c>
       <c r="C52">
-        <v>-0.1005707902862025</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>-0.00480400621742147</v>
@@ -1956,7 +1956,7 @@
         <v>2025</v>
       </c>
       <c r="C53">
-        <v>0.07612337188624266</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>-0.01884635889108726</v>
@@ -1988,7 +1988,7 @@
         <v>2026</v>
       </c>
       <c r="C54">
-        <v>0.1520475991885312</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0.00163931952857742</v>
@@ -2020,7 +2020,7 @@
         <v>2027</v>
       </c>
       <c r="C55">
-        <v>0.2967383396707776</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>-0.00473521004127388</v>
@@ -2052,7 +2052,7 @@
         <v>2028</v>
       </c>
       <c r="C56">
-        <v>0.3823559889995352</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0.00991308057288667</v>
@@ -2564,7 +2564,7 @@
         <v>2024</v>
       </c>
       <c r="C72">
-        <v>-0.5895368614989521</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>-0.6763822088233228</v>
@@ -2596,7 +2596,7 @@
         <v>2025</v>
       </c>
       <c r="C73">
-        <v>-0.5577766284243875</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>-0.5867154869608413</v>
@@ -2628,7 +2628,7 @@
         <v>2026</v>
       </c>
       <c r="C74">
-        <v>-0.5451678223758832</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>-0.6346870874226689</v>
@@ -2660,7 +2660,7 @@
         <v>2027</v>
       </c>
       <c r="C75">
-        <v>-0.5076109606764473</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>-0.6041882217575349</v>
@@ -2692,7 +2692,7 @@
         <v>2028</v>
       </c>
       <c r="C76">
-        <v>-0.4866039696771174</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>-0.6134407624353353</v>
@@ -2724,7 +2724,7 @@
         <v>2024</v>
       </c>
       <c r="C77">
-        <v>-0.7039382194041883</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>-0.2937583236874212</v>
@@ -2753,7 +2753,7 @@
         <v>2025</v>
       </c>
       <c r="C78">
-        <v>-0.6724549116803208</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>-0.3614724694905754</v>
@@ -2782,7 +2782,7 @@
         <v>2026</v>
       </c>
       <c r="C79">
-        <v>-0.6556196617450907</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>-0.4216756308592854</v>
@@ -2811,7 +2811,7 @@
         <v>2027</v>
       </c>
       <c r="C80">
-        <v>-0.6152741728313973</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>-0.4807680663140202</v>
@@ -2840,7 +2840,7 @@
         <v>2028</v>
       </c>
       <c r="C81">
-        <v>-0.5884026446008841</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>-0.5321101398875256</v>
@@ -3014,7 +3014,7 @@
         <v>2024</v>
       </c>
       <c r="C87">
-        <v>0.1785864676492396</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>-0.1930224922061285</v>
@@ -3043,7 +3043,7 @@
         <v>2025</v>
       </c>
       <c r="C88">
-        <v>0.2122061541034803</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>-0.1876873965118502</v>
@@ -3072,7 +3072,7 @@
         <v>2026</v>
       </c>
       <c r="C89">
-        <v>0.1964373723257007</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>-0.1763690020649563</v>
@@ -3101,7 +3101,7 @@
         <v>2027</v>
       </c>
       <c r="C90">
-        <v>0.2152706387451157</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>-0.1696310160159818</v>
@@ -3130,7 +3130,7 @@
         <v>2028</v>
       </c>
       <c r="C91">
-        <v>0.1969014494378392</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>-0.1581596365987551</v>
@@ -3159,7 +3159,7 @@
         <v>2024</v>
       </c>
       <c r="C92">
-        <v>-0.4653549388414845</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>1.012203066990088</v>
@@ -3188,7 +3188,7 @@
         <v>2025</v>
       </c>
       <c r="C93">
-        <v>-0.3462288941741009</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>1.004243633957952</v>
@@ -3217,7 +3217,7 @@
         <v>2026</v>
       </c>
       <c r="C94">
-        <v>-0.3178652110159146</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>1.008679899431938</v>
@@ -3246,7 +3246,7 @@
         <v>2027</v>
       </c>
       <c r="C95">
-        <v>-0.2317725951799918</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0.9986847670116628</v>
@@ -3275,7 +3275,7 @@
         <v>2028</v>
       </c>
       <c r="C96">
-        <v>-0.1860627590117763</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0.9964936212478162</v>
@@ -3304,7 +3304,7 @@
         <v>2024</v>
       </c>
       <c r="C97">
-        <v>-1.103116304286143</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0.2012202762903103</v>
@@ -3333,7 +3333,7 @@
         <v>2025</v>
       </c>
       <c r="C98">
-        <v>-1.027688334934093</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0.09891977876466264</v>
@@ -3362,7 +3362,7 @@
         <v>2026</v>
       </c>
       <c r="C99">
-        <v>-0.9856125872998796</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0.00435501250117581</v>
@@ -3391,7 +3391,7 @@
         <v>2027</v>
       </c>
       <c r="C100">
-        <v>-0.9089391287159708</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>-0.09192509494513632</v>
@@ -3420,7 +3420,7 @@
         <v>2028</v>
       </c>
       <c r="C101">
-        <v>-0.8455784422051902</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>-0.1778441446082217</v>
@@ -3449,7 +3449,7 @@
         <v>2024</v>
       </c>
       <c r="C102">
-        <v>-1.505122912372284</v>
+        <v>1.505122912372284</v>
       </c>
       <c r="D102">
         <v>1.59716530828951</v>
@@ -3478,7 +3478,7 @@
         <v>2025</v>
       </c>
       <c r="C103">
-        <v>-1.457239544660443</v>
+        <v>1.457239544660443</v>
       </c>
       <c r="D103">
         <v>1.597710962302539</v>
@@ -3507,7 +3507,7 @@
         <v>2026</v>
       </c>
       <c r="C104">
-        <v>-1.406520528405586</v>
+        <v>1.406520528405586</v>
       </c>
       <c r="D104">
         <v>1.614040463867948</v>
@@ -3536,7 +3536,7 @@
         <v>2027</v>
       </c>
       <c r="C105">
-        <v>-1.335784327104697</v>
+        <v>1.335784327104697</v>
       </c>
       <c r="D105">
         <v>1.60994750438619</v>
@@ -3565,7 +3565,7 @@
         <v>2028</v>
       </c>
       <c r="C106">
-        <v>-1.261297589761371</v>
+        <v>1.261297589761371</v>
       </c>
       <c r="D106">
         <v>1.614506474334649</v>
@@ -3594,7 +3594,7 @@
         <v>2024</v>
       </c>
       <c r="C107">
-        <v>-0.08280937439553511</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0.02333820811668506</v>
@@ -3623,7 +3623,7 @@
         <v>2025</v>
       </c>
       <c r="C108">
-        <v>0.06252791841725024</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0.05651207951189402</v>
@@ -3652,7 +3652,7 @@
         <v>2026</v>
       </c>
       <c r="C109">
-        <v>0.08266675683710342</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0.09823016880666904</v>
@@ -3681,7 +3681,7 @@
         <v>2027</v>
       </c>
       <c r="C110">
-        <v>0.1744092321240079</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0.1312061031759061</v>
@@ -3710,7 +3710,7 @@
         <v>2028</v>
       </c>
       <c r="C111">
-        <v>0.2095316428241858</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0.1680653555012248</v>
@@ -3739,7 +3739,7 @@
         <v>2024</v>
       </c>
       <c r="C112">
-        <v>-1.053073992844042</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>1.407711971454026</v>
@@ -3765,7 +3765,7 @@
         <v>2025</v>
       </c>
       <c r="C113">
-        <v>-0.974217232592188</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>1.347120743812022</v>
@@ -3791,7 +3791,7 @@
         <v>2026</v>
       </c>
       <c r="C114">
-        <v>-0.9332174101578136</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>1.330027796791996</v>
@@ -3817,7 +3817,7 @@
         <v>2027</v>
       </c>
       <c r="C115">
-        <v>-0.8558048730933941</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>1.287776321510499</v>
@@ -3843,7 +3843,7 @@
         <v>2028</v>
       </c>
       <c r="C116">
-        <v>-0.7938291714134424</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>1.258677455169753</v>
@@ -3869,7 +3869,7 @@
         <v>2024</v>
       </c>
       <c r="C117">
-        <v>-1.458416829937125</v>
+        <v>1.458416829937125</v>
       </c>
       <c r="D117">
         <v>1.81738674811564</v>
@@ -3901,7 +3901,7 @@
         <v>2025</v>
       </c>
       <c r="C118">
-        <v>-1.439975310010022</v>
+        <v>1.439975310010022</v>
       </c>
       <c r="D118">
         <v>1.729427395720806</v>
@@ -3933,7 +3933,7 @@
         <v>2026</v>
       </c>
       <c r="C119">
-        <v>-1.396923494969016</v>
+        <v>1.396923494969016</v>
       </c>
       <c r="D119">
         <v>1.664960837341283</v>
@@ -3965,7 +3965,7 @@
         <v>2027</v>
       </c>
       <c r="C120">
-        <v>-1.34348868960988</v>
+        <v>1.34348868960988</v>
       </c>
       <c r="D120">
         <v>1.583158040017986</v>
@@ -3997,7 +3997,7 @@
         <v>2028</v>
       </c>
       <c r="C121">
-        <v>-1.280682370735155</v>
+        <v>1.280682370735155</v>
       </c>
       <c r="D121">
         <v>1.514299493692664</v>
@@ -4174,7 +4174,7 @@
         <v>2024</v>
       </c>
       <c r="C127">
-        <v>-1.74953418487108</v>
+        <v>1.74953418487108</v>
       </c>
       <c r="D127">
         <v>1.505698566770268</v>
@@ -4206,7 +4206,7 @@
         <v>2025</v>
       </c>
       <c r="C128">
-        <v>-1.721724912398094</v>
+        <v>1.721724912398094</v>
       </c>
       <c r="D128">
         <v>1.409180058204849</v>
@@ -4238,7 +4238,7 @@
         <v>2026</v>
       </c>
       <c r="C129">
-        <v>-1.666430240791552</v>
+        <v>1.666430240791552</v>
       </c>
       <c r="D129">
         <v>1.390531747226765</v>
@@ -4270,7 +4270,7 @@
         <v>2027</v>
       </c>
       <c r="C130">
-        <v>-1.601137837825435</v>
+        <v>1.601137837825435</v>
       </c>
       <c r="D130">
         <v>1.319466821099921</v>
@@ -4302,7 +4302,7 @@
         <v>2028</v>
       </c>
       <c r="C131">
-        <v>-1.520945662154178</v>
+        <v>1.520945662154178</v>
       </c>
       <c r="D131">
         <v>1.281989786459828</v>
@@ -4334,7 +4334,7 @@
         <v>2024</v>
       </c>
       <c r="C132">
-        <v>-1.756615358327666</v>
+        <v>1.756615358327666</v>
       </c>
       <c r="D132">
         <v>1.257559808435544</v>
@@ -4363,7 +4363,7 @@
         <v>2025</v>
       </c>
       <c r="C133">
-        <v>-1.728578186545971</v>
+        <v>1.728578186545971</v>
       </c>
       <c r="D133">
         <v>1.206448486104454</v>
@@ -4392,7 +4392,7 @@
         <v>2026</v>
       </c>
       <c r="C134">
-        <v>-1.672985677738179</v>
+        <v>1.672985677738179</v>
       </c>
       <c r="D134">
         <v>0.9183707772131744</v>
@@ -4421,7 +4421,7 @@
         <v>2027</v>
       </c>
       <c r="C135">
-        <v>-1.607404814340294</v>
+        <v>1.607404814340294</v>
       </c>
       <c r="D135">
         <v>0.8679094886894617</v>
@@ -4450,7 +4450,7 @@
         <v>2028</v>
       </c>
       <c r="C136">
-        <v>-1.526789714432122</v>
+        <v>1.526789714432122</v>
       </c>
       <c r="D136">
         <v>0.6048572341447584</v>
@@ -4479,7 +4479,7 @@
         <v>2024</v>
       </c>
       <c r="C137">
-        <v>-1.769991025089999</v>
+        <v>1.769991025089999</v>
       </c>
       <c r="D137">
         <v>1.648016306046616</v>
@@ -4508,7 +4508,7 @@
         <v>2025</v>
       </c>
       <c r="C138">
-        <v>-1.741523432017263</v>
+        <v>1.741523432017263</v>
       </c>
       <c r="D138">
         <v>1.611757521909152</v>
@@ -4537,7 +4537,7 @@
         <v>2026</v>
       </c>
       <c r="C139">
-        <v>-1.685368415357349</v>
+        <v>1.685368415357349</v>
       </c>
       <c r="D139">
         <v>1.515182558048351</v>
@@ -4566,7 +4566,7 @@
         <v>2027</v>
       </c>
       <c r="C140">
-        <v>-1.619242737787056</v>
+        <v>1.619242737787056</v>
       </c>
       <c r="D140">
         <v>1.451580705846938</v>
@@ -4595,7 +4595,7 @@
         <v>2028</v>
       </c>
       <c r="C141">
-        <v>-1.53782882738212</v>
+        <v>1.53782882738212</v>
       </c>
       <c r="D141">
         <v>1.371241906243034</v>
@@ -4624,7 +4624,7 @@
         <v>2024</v>
       </c>
       <c r="C142">
-        <v>-0.5732632505469832</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>1.251547904649189</v>
@@ -4656,7 +4656,7 @@
         <v>2025</v>
       </c>
       <c r="C143">
-        <v>-0.5833043864640355</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>1.287491265741911</v>
@@ -4688,7 +4688,7 @@
         <v>2026</v>
       </c>
       <c r="C144">
-        <v>-0.5774777621452597</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>1.336267501276021</v>
@@ -4720,7 +4720,7 @@
         <v>2027</v>
       </c>
       <c r="C145">
-        <v>-0.5600963473220162</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>1.36546525602908</v>
@@ -4752,7 +4752,7 @@
         <v>2028</v>
       </c>
       <c r="C146">
-        <v>-0.5501525184253</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>1.401032321580667</v>
@@ -4784,7 +4784,7 @@
         <v>2024</v>
       </c>
       <c r="C147">
-        <v>-0.5158289613875106</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>1.197782732911095</v>
@@ -4816,7 +4816,7 @@
         <v>2025</v>
       </c>
       <c r="C148">
-        <v>-0.5277194527120233</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>1.235385982040917</v>
@@ -4848,7 +4848,7 @@
         <v>2026</v>
       </c>
       <c r="C149">
-        <v>-0.5243098067741473</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>1.126149041039348</v>
@@ -4880,7 +4880,7 @@
         <v>2027</v>
       </c>
       <c r="C150">
-        <v>-0.5092689939712139</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>1.115187189499298</v>
@@ -4912,7 +4912,7 @@
         <v>2028</v>
       </c>
       <c r="C151">
-        <v>-0.5027562915913704</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>1.038389021045497</v>
@@ -4944,7 +4944,7 @@
         <v>2024</v>
       </c>
       <c r="C152">
-        <v>-1.105928969566972</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>0.5063517922453471</v>
@@ -4976,7 +4976,7 @@
         <v>2025</v>
       </c>
       <c r="C153">
-        <v>-1.098829922377982</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>0.4757001391643632</v>
@@ -5008,7 +5008,7 @@
         <v>2026</v>
       </c>
       <c r="C154">
-        <v>-1.070601988569626</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>0.4559220836363062</v>
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="C155">
-        <v>-1.031524464943994</v>
+        <v>0</v>
       </c>
       <c r="D155">
         <v>0.427634764846843</v>
@@ -5072,7 +5072,7 @@
         <v>2028</v>
       </c>
       <c r="C156">
-        <v>-0.9897691630444112</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0.4071132696959041</v>
@@ -5104,7 +5104,7 @@
         <v>2024</v>
       </c>
       <c r="C157">
-        <v>-0.5538061049184124</v>
+        <v>0.5538061049184124</v>
       </c>
       <c r="D157">
         <v>2.252686196309628</v>
@@ -5136,7 +5136,7 @@
         <v>2025</v>
       </c>
       <c r="C158">
-        <v>-0.5644302899802935</v>
+        <v>0.5644302899802935</v>
       </c>
       <c r="D158">
         <v>2.27432661083661</v>
@@ -5168,7 +5168,7 @@
         <v>2026</v>
       </c>
       <c r="C159">
-        <v>-0.5594152741681854</v>
+        <v>0.5594152741681854</v>
       </c>
       <c r="D159">
         <v>2.279319302727216</v>
@@ -5200,7 +5200,7 @@
         <v>2027</v>
       </c>
       <c r="C160">
-        <v>-0.5428014112184345</v>
+        <v>0.5428014112184345</v>
       </c>
       <c r="D160">
         <v>2.273220823870919</v>
@@ -5232,7 +5232,7 @@
         <v>2028</v>
       </c>
       <c r="C161">
-        <v>-0.5340092103178697</v>
+        <v>0.5340092103178697</v>
       </c>
       <c r="D161">
         <v>2.271066911929202</v>
@@ -5264,7 +5264,7 @@
         <v>2024</v>
       </c>
       <c r="C162">
-        <v>-1.377652476020248</v>
+        <v>2.755304952040495</v>
       </c>
       <c r="D162">
         <v>2.214840165901232</v>
@@ -5273,7 +5273,7 @@
         <v>-1.445971857618978</v>
       </c>
       <c r="F162">
-        <v>4.104515199714942</v>
+        <v>4</v>
       </c>
       <c r="G162">
         <v>0.5777980059500056</v>
@@ -5296,7 +5296,7 @@
         <v>2025</v>
       </c>
       <c r="C163">
-        <v>-1.327195710197924</v>
+        <v>2.654391420395847</v>
       </c>
       <c r="D163">
         <v>2.256406742050777</v>
@@ -5305,7 +5305,7 @@
         <v>-1.387633917307909</v>
       </c>
       <c r="F163">
-        <v>4.084767443308899</v>
+        <v>4</v>
       </c>
       <c r="G163">
         <v>0.5091103779364949</v>
@@ -5328,7 +5328,7 @@
         <v>2026</v>
       </c>
       <c r="C164">
-        <v>-1.28138049024082</v>
+        <v>2.562760980481639</v>
       </c>
       <c r="D164">
         <v>2.157031215959998</v>
@@ -5360,7 +5360,7 @@
         <v>2027</v>
       </c>
       <c r="C165">
-        <v>-1.212212203308997</v>
+        <v>2.424424406617994</v>
       </c>
       <c r="D165">
         <v>2.178668812291308</v>
@@ -5392,7 +5392,7 @@
         <v>2028</v>
       </c>
       <c r="C166">
-        <v>-1.143917881773476</v>
+        <v>2.287835763546951</v>
       </c>
       <c r="D166">
         <v>2.083773052243682</v>
@@ -5424,7 +5424,7 @@
         <v>2024</v>
       </c>
       <c r="C167">
-        <v>-0.2685218962934419</v>
+        <v>0</v>
       </c>
       <c r="D167">
         <v>0.6314668645731673</v>
@@ -5453,7 +5453,7 @@
         <v>2025</v>
       </c>
       <c r="C168">
-        <v>-0.1359092522756076</v>
+        <v>0</v>
       </c>
       <c r="D168">
         <v>0.4523662839540729</v>
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="C169">
-        <v>-0.1117775388805325</v>
+        <v>0</v>
       </c>
       <c r="D169">
         <v>0.3111271506173183</v>
@@ -5511,7 +5511,7 @@
         <v>2027</v>
       </c>
       <c r="C170">
-        <v>-0.02277787394197265</v>
+        <v>0</v>
       </c>
       <c r="D170">
         <v>0.1826226342969771</v>
@@ -5540,7 +5540,7 @@
         <v>2028</v>
       </c>
       <c r="C171">
-        <v>0.0174843618587119</v>
+        <v>0</v>
       </c>
       <c r="D171">
         <v>0.07671841760570952</v>
@@ -5569,7 +5569,7 @@
         <v>2024</v>
       </c>
       <c r="C172">
-        <v>-0.6260463266299469</v>
+        <v>0</v>
       </c>
       <c r="D172">
         <v>-0.3335973980441499</v>
@@ -5598,7 +5598,7 @@
         <v>2025</v>
       </c>
       <c r="C173">
-        <v>-0.5179305257057369</v>
+        <v>0</v>
       </c>
       <c r="D173">
         <v>-0.3761555031325381</v>
@@ -5627,7 +5627,7 @@
         <v>2026</v>
       </c>
       <c r="C174">
-        <v>-0.4861119289848554</v>
+        <v>0</v>
       </c>
       <c r="D174">
         <v>-0.410839486809407</v>
@@ -5656,7 +5656,7 @@
         <v>2027</v>
       </c>
       <c r="C175">
-        <v>-0.4023925811376539</v>
+        <v>0</v>
       </c>
       <c r="D175">
         <v>-0.4456076860965736</v>
@@ -5685,7 +5685,7 @@
         <v>2028</v>
       </c>
       <c r="C176">
-        <v>-0.3522354093617605</v>
+        <v>0</v>
       </c>
       <c r="D176">
         <v>-0.4738775699304578</v>
@@ -6354,7 +6354,7 @@
         <v>2024</v>
       </c>
       <c r="C197">
-        <v>0.4022690583206992</v>
+        <v>-0.4022690583206992</v>
       </c>
       <c r="D197">
         <v>2.071156023339973</v>
@@ -6383,7 +6383,7 @@
         <v>2025</v>
       </c>
       <c r="C198">
-        <v>0.3855768735950799</v>
+        <v>-0.3855768735950799</v>
       </c>
       <c r="D198">
         <v>1.98070197494669</v>
@@ -6412,7 +6412,7 @@
         <v>2026</v>
       </c>
       <c r="C199">
-        <v>0.3320160318697025</v>
+        <v>-0.3320160318697025</v>
       </c>
       <c r="D199">
         <v>1.909831761100723</v>
@@ -6441,7 +6441,7 @@
         <v>2027</v>
       </c>
       <c r="C200">
-        <v>0.3112648096118453</v>
+        <v>-0.3112648096118453</v>
       </c>
       <c r="D200">
         <v>1.820812015960984</v>
@@ -6470,7 +6470,7 @@
         <v>2028</v>
       </c>
       <c r="C201">
-        <v>0.256191312700828</v>
+        <v>-0.256191312700828</v>
       </c>
       <c r="D201">
         <v>1.745387661079167</v>
@@ -6499,7 +6499,7 @@
         <v>2024</v>
       </c>
       <c r="C202">
-        <v>-0.5622501816821822</v>
+        <v>0.5622501816821822</v>
       </c>
       <c r="D202">
         <v>2.113539192629205</v>
@@ -6528,7 +6528,7 @@
         <v>2025</v>
       </c>
       <c r="C203">
-        <v>-0.5726468492566235</v>
+        <v>0.5726468492566235</v>
       </c>
       <c r="D203">
         <v>2.084037563666389</v>
@@ -6557,7 +6557,7 @@
         <v>2026</v>
       </c>
       <c r="C204">
-        <v>-0.5672848445606504</v>
+        <v>0.5672848445606504</v>
       </c>
       <c r="D204">
         <v>1.992677154191276</v>
@@ -6586,7 +6586,7 @@
         <v>2027</v>
       </c>
       <c r="C205">
-        <v>-0.5503531594758637</v>
+        <v>0.5503531594758637</v>
       </c>
       <c r="D205">
         <v>1.929317441090941</v>
@@ -6615,7 +6615,7 @@
         <v>2028</v>
       </c>
       <c r="C206">
-        <v>-0.5410680492136229</v>
+        <v>0.5410680492136229</v>
       </c>
       <c r="D206">
         <v>1.852061860882515</v>
@@ -6644,7 +6644,7 @@
         <v>2024</v>
       </c>
       <c r="C207">
-        <v>0.5762559342262412</v>
+        <v>0</v>
       </c>
       <c r="D207">
         <v>1.572535179147932</v>
@@ -6676,7 +6676,7 @@
         <v>2025</v>
       </c>
       <c r="C208">
-        <v>0.529225670868982</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>1.597913312208796</v>
@@ -6708,7 +6708,7 @@
         <v>2026</v>
       </c>
       <c r="C209">
-        <v>0.4867090531290115</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>1.372376532581162</v>
@@ -6740,7 +6740,7 @@
         <v>2027</v>
       </c>
       <c r="C210">
-        <v>0.4572692853553776</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>1.40778834824755</v>
@@ -6772,7 +6772,7 @@
         <v>2028</v>
       </c>
       <c r="C211">
-        <v>0.3985623510873903</v>
+        <v>0</v>
       </c>
       <c r="D211">
         <v>1.579818303794865</v>
@@ -6804,7 +6804,7 @@
         <v>2024</v>
       </c>
       <c r="C212">
-        <v>0.5056403383123973</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>0.4267801618579781</v>
@@ -6836,7 +6836,7 @@
         <v>2025</v>
       </c>
       <c r="C213">
-        <v>0.4955501741646709</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>0.355994459610357</v>
@@ -6868,7 +6868,7 @@
         <v>2026</v>
       </c>
       <c r="C214">
-        <v>0.3926086938056019</v>
+        <v>0</v>
       </c>
       <c r="D214">
         <v>0.3035009505233388</v>
@@ -6900,7 +6900,7 @@
         <v>2027</v>
       </c>
       <c r="C215">
-        <v>0.3535398370942445</v>
+        <v>0</v>
       </c>
       <c r="D215">
         <v>0.2438707807982965</v>
@@ -6932,7 +6932,7 @@
         <v>2028</v>
       </c>
       <c r="C216">
-        <v>0.2695114415087711</v>
+        <v>0</v>
       </c>
       <c r="D216">
         <v>0.193791335611021</v>
@@ -6964,7 +6964,7 @@
         <v>2024</v>
       </c>
       <c r="C217">
-        <v>1.085231177066166</v>
+        <v>-1.085231177066166</v>
       </c>
       <c r="D217">
         <v>1.468571767003244</v>
@@ -6996,7 +6996,7 @@
         <v>2025</v>
       </c>
       <c r="C218">
-        <v>1.045767531475922</v>
+        <v>-1.045767531475922</v>
       </c>
       <c r="D218">
         <v>1.46432647102827</v>
@@ -7028,7 +7028,7 @@
         <v>2026</v>
       </c>
       <c r="C219">
-        <v>0.9344821156636129</v>
+        <v>-0.9344821156636129</v>
       </c>
       <c r="D219">
         <v>1.440324668646202</v>
@@ -7060,7 +7060,7 @@
         <v>2027</v>
       </c>
       <c r="C220">
-        <v>0.8755256184042322</v>
+        <v>-0.8755256184042322</v>
       </c>
       <c r="D220">
         <v>1.416728267958015</v>
@@ -7092,7 +7092,7 @@
         <v>2028</v>
       </c>
       <c r="C221">
-        <v>0.7637764436793208</v>
+        <v>-0.7637764436793208</v>
       </c>
       <c r="D221">
         <v>1.393906182694892</v>
@@ -7124,7 +7124,7 @@
         <v>2024</v>
       </c>
       <c r="C222">
-        <v>-0.04209032553082557</v>
+        <v>0.04209032553082557</v>
       </c>
       <c r="D222">
         <v>2.277966909180638</v>
@@ -7156,7 +7156,7 @@
         <v>2025</v>
       </c>
       <c r="C223">
-        <v>-0.02694113421948743</v>
+        <v>0.02694113421948743</v>
       </c>
       <c r="D223">
         <v>2.194605289697952</v>
@@ -7188,7 +7188,7 @@
         <v>2026</v>
       </c>
       <c r="C224">
-        <v>-0.07785840896688155</v>
+        <v>0.07785840896688155</v>
       </c>
       <c r="D224">
         <v>2.133960886528969</v>
@@ -7220,7 +7220,7 @@
         <v>2027</v>
       </c>
       <c r="C225">
-        <v>-0.08146926530784356</v>
+        <v>0.08146926530784356</v>
       </c>
       <c r="D225">
         <v>2.052194645038668</v>
@@ -7252,7 +7252,7 @@
         <v>2028</v>
       </c>
       <c r="C226">
-        <v>-0.1164086882557235</v>
+        <v>0.1164086882557235</v>
       </c>
       <c r="D226">
         <v>1.984165931555518</v>
@@ -7284,7 +7284,7 @@
         <v>2024</v>
       </c>
       <c r="C227">
-        <v>0.5983873650233983</v>
+        <v>-0.5983873650233983</v>
       </c>
       <c r="D227">
         <v>2.40105078558851</v>
@@ -7316,7 +7316,7 @@
         <v>2025</v>
       </c>
       <c r="C228">
-        <v>0.6610312819811474</v>
+        <v>-0.6610312819811474</v>
       </c>
       <c r="D228">
         <v>2.345092996030989</v>
@@ -7348,7 +7348,7 @@
         <v>2026</v>
       </c>
       <c r="C229">
-        <v>0.5303557224588721</v>
+        <v>-0.5303557224588721</v>
       </c>
       <c r="D229">
         <v>2.305773397097826</v>
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="C230">
-        <v>0.4986536531037715</v>
+        <v>-0.4986536531037715</v>
       </c>
       <c r="D230">
         <v>2.244732485869714</v>
@@ -7412,7 +7412,7 @@
         <v>2028</v>
       </c>
       <c r="C231">
-        <v>0.4058257094026584</v>
+        <v>-0.4058257094026584</v>
       </c>
       <c r="D231">
         <v>2.195993841437792</v>
@@ -7444,7 +7444,7 @@
         <v>2024</v>
       </c>
       <c r="C232">
-        <v>1.056780861427546</v>
+        <v>0</v>
       </c>
       <c r="D232">
         <v>0.6160078283894358</v>
@@ -7476,7 +7476,7 @@
         <v>2025</v>
       </c>
       <c r="C233">
-        <v>1.126306492596283</v>
+        <v>0</v>
       </c>
       <c r="D233">
         <v>0.5882495468900817</v>
@@ -7508,7 +7508,7 @@
         <v>2026</v>
       </c>
       <c r="C234">
-        <v>0.9595994799624938</v>
+        <v>0</v>
       </c>
       <c r="D234">
         <v>0.6253475608450527</v>
@@ -7540,7 +7540,7 @@
         <v>2027</v>
       </c>
       <c r="C235">
-        <v>0.9091032145373678</v>
+        <v>0</v>
       </c>
       <c r="D235">
         <v>0.6142431071343369</v>
@@ -7572,7 +7572,7 @@
         <v>2028</v>
       </c>
       <c r="C236">
-        <v>0.7826549394070381</v>
+        <v>0</v>
       </c>
       <c r="D236">
         <v>0.6338324842911993</v>
@@ -7604,7 +7604,7 @@
         <v>2024</v>
       </c>
       <c r="C237">
-        <v>-0.3265664828949703</v>
+        <v>0.3265664828949703</v>
       </c>
       <c r="D237">
         <v>1.54730134420933</v>
@@ -7636,7 +7636,7 @@
         <v>2025</v>
       </c>
       <c r="C238">
-        <v>-0.3061116230950126</v>
+        <v>0.3061116230950126</v>
       </c>
       <c r="D238">
         <v>1.628879772203187</v>
@@ -7668,7 +7668,7 @@
         <v>2026</v>
       </c>
       <c r="C239">
-        <v>-0.3754112512907121</v>
+        <v>0.3754112512907121</v>
       </c>
       <c r="D239">
         <v>1.714039399872531</v>
@@ -7700,7 +7700,7 @@
         <v>2027</v>
       </c>
       <c r="C240">
-        <v>-0.3827391991118397</v>
+        <v>0.3827391991118397</v>
       </c>
       <c r="D240">
         <v>1.772823268175178</v>
@@ -7732,7 +7732,7 @@
         <v>2028</v>
       </c>
       <c r="C241">
-        <v>-0.4167325015585671</v>
+        <v>0.4167325015585671</v>
       </c>
       <c r="D241">
         <v>1.836785758513053</v>
@@ -7764,7 +7764,7 @@
         <v>2024</v>
       </c>
       <c r="C242">
-        <v>-0.7086401023185815</v>
+        <v>0.7086401023185815</v>
       </c>
       <c r="D242">
         <v>1.270027434685391</v>
@@ -7793,7 +7793,7 @@
         <v>2025</v>
       </c>
       <c r="C243">
-        <v>-0.6859758186925619</v>
+        <v>0.6859758186925619</v>
       </c>
       <c r="D243">
         <v>1.238918032441618</v>
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="C244">
-        <v>-0.7222153687455678</v>
+        <v>0.7222153687455678</v>
       </c>
       <c r="D244">
         <v>1.270572912530763</v>
@@ -7851,7 +7851,7 @@
         <v>2027</v>
       </c>
       <c r="C245">
-        <v>-0.7101333051658828</v>
+        <v>0.7101333051658828</v>
       </c>
       <c r="D245">
         <v>1.269027132424234</v>
@@ -7880,7 +7880,7 @@
         <v>2028</v>
       </c>
       <c r="C246">
-        <v>-0.7136449082879019</v>
+        <v>0.7136449082879019</v>
       </c>
       <c r="D246">
         <v>1.280118417415851</v>
@@ -7909,7 +7909,7 @@
         <v>2024</v>
       </c>
       <c r="C247">
-        <v>-0.3724612978845839</v>
+        <v>0.3724612978845839</v>
       </c>
       <c r="D247">
         <v>1.909990508500393</v>
@@ -7941,7 +7941,7 @@
         <v>2025</v>
       </c>
       <c r="C248">
-        <v>-0.3517411131506264</v>
+        <v>0.3517411131506264</v>
       </c>
       <c r="D248">
         <v>1.885011104685988</v>
@@ -7973,7 +7973,7 @@
         <v>2026</v>
       </c>
       <c r="C249">
-        <v>-0.4170696143143759</v>
+        <v>0.4170696143143759</v>
       </c>
       <c r="D249">
         <v>1.874197039385658</v>
@@ -8005,7 +8005,7 @@
         <v>2027</v>
       </c>
       <c r="C250">
-        <v>-0.4220660807839145</v>
+        <v>0.4220660807839145</v>
       </c>
       <c r="D250">
         <v>1.840155486897724</v>
@@ -8037,7 +8037,7 @@
         <v>2028</v>
       </c>
       <c r="C251">
-        <v>-0.4523979508423734</v>
+        <v>0.4523979508423734</v>
       </c>
       <c r="D251">
         <v>1.816042041519016</v>
@@ -8069,7 +8069,7 @@
         <v>2024</v>
       </c>
       <c r="C252">
-        <v>0.2172870797057888</v>
+        <v>0</v>
       </c>
       <c r="D252">
         <v>0.9705745388691488</v>
@@ -8101,7 +8101,7 @@
         <v>2025</v>
       </c>
       <c r="C253">
-        <v>0.2345978383211816</v>
+        <v>0</v>
       </c>
       <c r="D253">
         <v>1.039335458748188</v>
@@ -8133,7 +8133,7 @@
         <v>2026</v>
       </c>
       <c r="C254">
-        <v>0.1182403558853659</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>1.120171741273908</v>
@@ -8165,7 +8165,7 @@
         <v>2027</v>
       </c>
       <c r="C255">
-        <v>0.08328435448495694</v>
+        <v>0</v>
       </c>
       <c r="D255">
         <v>1.181239314722401</v>
@@ -8197,7 +8197,7 @@
         <v>2028</v>
       </c>
       <c r="C256">
-        <v>0.0059030785377791</v>
+        <v>0</v>
       </c>
       <c r="D256">
         <v>1.24666400182241</v>
@@ -8229,7 +8229,7 @@
         <v>2024</v>
       </c>
       <c r="C257">
-        <v>-0.4871983386449914</v>
+        <v>0</v>
       </c>
       <c r="E257">
         <v>1.232060348568788</v>
@@ -8258,7 +8258,7 @@
         <v>2025</v>
       </c>
       <c r="C258">
-        <v>-0.4658148383801522</v>
+        <v>0</v>
       </c>
       <c r="E258">
         <v>1.159858231033678</v>
@@ -8287,7 +8287,7 @@
         <v>2026</v>
       </c>
       <c r="C259">
-        <v>-0.521215521553727</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>1.062474768249118</v>
@@ -8316,7 +8316,7 @@
         <v>2027</v>
       </c>
       <c r="C260">
-        <v>-0.5203832835019813</v>
+        <v>0</v>
       </c>
       <c r="E260">
         <v>0.947867282374853</v>
@@ -8345,7 +8345,7 @@
         <v>2028</v>
       </c>
       <c r="C261">
-        <v>-0.5415615718839438</v>
+        <v>0</v>
       </c>
       <c r="E261">
         <v>0.8615572871191678</v>
@@ -8504,7 +8504,7 @@
         <v>2024</v>
       </c>
       <c r="C267">
-        <v>-0.8369158444948773</v>
+        <v>0</v>
       </c>
       <c r="D267">
         <v>0.1082615296770913</v>
@@ -8533,7 +8533,7 @@
         <v>2025</v>
       </c>
       <c r="C268">
-        <v>-0.8135380222962053</v>
+        <v>0</v>
       </c>
       <c r="D268">
         <v>0.07111425156914393</v>
@@ -8562,7 +8562,7 @@
         <v>2026</v>
       </c>
       <c r="C269">
-        <v>-0.8385555553869093</v>
+        <v>0</v>
       </c>
       <c r="D269">
         <v>0.00850666293529268</v>
@@ -8591,7 +8591,7 @@
         <v>2027</v>
       </c>
       <c r="C270">
-        <v>-0.8198922529516063</v>
+        <v>0</v>
       </c>
       <c r="D270">
         <v>-0.02775531609610212</v>
@@ -8620,7 +8620,7 @@
         <v>2028</v>
       </c>
       <c r="C271">
-        <v>-0.8131100174560171</v>
+        <v>0</v>
       </c>
       <c r="D271">
         <v>-0.08084268821085104</v>
@@ -8809,7 +8809,7 @@
         <v>2024</v>
       </c>
       <c r="C277">
-        <v>-1.760731040364422</v>
+        <v>0</v>
       </c>
       <c r="D277">
         <v>0.4499258027294325</v>
@@ -8835,7 +8835,7 @@
         <v>2025</v>
       </c>
       <c r="C278">
-        <v>-1.731033716649317</v>
+        <v>0</v>
       </c>
       <c r="D278">
         <v>0.353565132980329</v>
@@ -8861,7 +8861,7 @@
         <v>2026</v>
       </c>
       <c r="C279">
-        <v>-1.675376611042621</v>
+        <v>0</v>
       </c>
       <c r="D279">
         <v>0.2705195333836957</v>
@@ -8887,7 +8887,7 @@
         <v>2027</v>
       </c>
       <c r="C280">
-        <v>-1.609014232991381</v>
+        <v>0</v>
       </c>
       <c r="D280">
         <v>0.1837195468749803</v>
@@ -8913,7 +8913,7 @@
         <v>2028</v>
       </c>
       <c r="C281">
-        <v>-1.527953117827545</v>
+        <v>0</v>
       </c>
       <c r="D281">
         <v>0.1074382299037502</v>
@@ -8939,7 +8939,7 @@
         <v>2024</v>
       </c>
       <c r="C282">
-        <v>-1.456485956620847</v>
+        <v>0</v>
       </c>
       <c r="D282">
         <v>0.4506863636350434</v>
@@ -8968,7 +8968,7 @@
         <v>2025</v>
       </c>
       <c r="C283">
-        <v>-1.415305647693327</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>0.390499213219502</v>
@@ -8997,7 +8997,7 @@
         <v>2026</v>
       </c>
       <c r="C284">
-        <v>-1.373954065183479</v>
+        <v>0</v>
       </c>
       <c r="D284">
         <v>0.3432807672010557</v>
@@ -9026,7 +9026,7 @@
         <v>2027</v>
       </c>
       <c r="C285">
-        <v>-1.311435895134676</v>
+        <v>0</v>
       </c>
       <c r="D285">
         <v>0.2898254384892873</v>
@@ -9055,7 +9055,7 @@
         <v>2028</v>
       </c>
       <c r="C286">
-        <v>-1.24575653232056</v>
+        <v>0</v>
       </c>
       <c r="D286">
         <v>0.2452629255175789</v>
@@ -9229,7 +9229,7 @@
         <v>2024</v>
       </c>
       <c r="C292">
-        <v>-0.4405152914775896</v>
+        <v>0.4405152914775896</v>
       </c>
       <c r="D292">
         <v>1.356404901044492</v>
@@ -9252,7 +9252,7 @@
         <v>2025</v>
       </c>
       <c r="C293">
-        <v>-0.3609894144103662</v>
+        <v>0.3609894144103662</v>
       </c>
       <c r="D293">
         <v>1.324138387821111</v>
@@ -9275,7 +9275,7 @@
         <v>2026</v>
       </c>
       <c r="C294">
-        <v>-0.3674084810829257</v>
+        <v>0.3674084810829257</v>
       </c>
       <c r="D294">
         <v>1.291872867416976</v>
@@ -9298,7 +9298,7 @@
         <v>2027</v>
       </c>
       <c r="C295">
-        <v>-0.3177272563154964</v>
+        <v>0.3177272563154964</v>
       </c>
       <c r="D295">
         <v>1.237319423055388</v>
@@ -9321,7 +9321,7 @@
         <v>2028</v>
       </c>
       <c r="C296">
-        <v>-0.3034123836494789</v>
+        <v>0.3034123836494789</v>
       </c>
       <c r="D296">
         <v>1.190297944684945</v>
@@ -9344,7 +9344,7 @@
         <v>2024</v>
       </c>
       <c r="C297">
-        <v>-0.9517779150148916</v>
+        <v>0.9517779150148916</v>
       </c>
       <c r="D297">
         <v>1.791663877276838</v>
@@ -9370,7 +9370,7 @@
         <v>2025</v>
       </c>
       <c r="C298">
-        <v>-0.8915485397390123</v>
+        <v>0.8915485397390123</v>
       </c>
       <c r="D298">
         <v>1.708428692713363</v>
@@ -9396,7 +9396,7 @@
         <v>2026</v>
       </c>
       <c r="C299">
-        <v>-0.8739281866713513</v>
+        <v>0.8739281866713513</v>
       </c>
       <c r="D299">
         <v>1.657999857461295</v>
@@ -9422,7 +9422,7 @@
         <v>2027</v>
       </c>
       <c r="C300">
-        <v>-0.8177870881540996</v>
+        <v>0.8177870881540996</v>
       </c>
       <c r="D300">
         <v>1.594566248729678</v>
@@ -9448,7 +9448,7 @@
         <v>2028</v>
       </c>
       <c r="C301">
-        <v>-0.7776242851654753</v>
+        <v>0.7776242851654753</v>
       </c>
       <c r="D301">
         <v>1.544640503561424</v>
@@ -9474,7 +9474,7 @@
         <v>2024</v>
       </c>
       <c r="C302">
-        <v>-0.622406793814528</v>
+        <v>0</v>
       </c>
       <c r="D302">
         <v>1.106297176650713</v>
@@ -9503,7 +9503,7 @@
         <v>2025</v>
       </c>
       <c r="C303">
-        <v>-0.5497460233196361</v>
+        <v>0</v>
       </c>
       <c r="D303">
         <v>1.059769876083899</v>
@@ -9532,7 +9532,7 @@
         <v>2026</v>
       </c>
       <c r="C304">
-        <v>-0.5476126048352826</v>
+        <v>0</v>
       </c>
       <c r="D304">
         <v>1.029408564843333</v>
@@ -9561,7 +9561,7 @@
         <v>2027</v>
       </c>
       <c r="C305">
-        <v>-0.4956331575339439</v>
+        <v>0</v>
       </c>
       <c r="D305">
         <v>0.9858907408063708</v>
@@ -9590,7 +9590,7 @@
         <v>2028</v>
       </c>
       <c r="C306">
-        <v>-0.472122387996551</v>
+        <v>0</v>
       </c>
       <c r="D306">
         <v>0.9520401198946348</v>
@@ -9619,7 +9619,7 @@
         <v>2024</v>
       </c>
       <c r="C307">
-        <v>-1.72621576482939</v>
+        <v>1.72621576482939</v>
       </c>
       <c r="D307">
         <v>0.5571873356018062</v>
@@ -9648,7 +9648,7 @@
         <v>2025</v>
       </c>
       <c r="C308">
-        <v>-1.695866927592573</v>
+        <v>1.695866927592573</v>
       </c>
       <c r="D308">
         <v>0.488681745102296</v>
@@ -9677,7 +9677,7 @@
         <v>2026</v>
       </c>
       <c r="C309">
-        <v>-1.641339620252594</v>
+        <v>1.641339620252594</v>
       </c>
       <c r="D309">
         <v>0.4330875474873401</v>
@@ -9706,7 +9706,7 @@
         <v>2027</v>
       </c>
       <c r="C310">
-        <v>-1.575386943392819</v>
+        <v>1.575386943392819</v>
       </c>
       <c r="D310">
         <v>0.3709506601976973</v>
@@ -9735,7 +9735,7 @@
         <v>2028</v>
       </c>
       <c r="C311">
-        <v>-1.495892081145802</v>
+        <v>1.495892081145802</v>
       </c>
       <c r="D311">
         <v>0.3183305077131575</v>
@@ -9764,7 +9764,7 @@
         <v>2024</v>
       </c>
       <c r="C312">
-        <v>-0.6790300581702891</v>
+        <v>0</v>
       </c>
       <c r="D312">
         <v>0.05034184157720572</v>
@@ -9793,7 +9793,7 @@
         <v>2025</v>
       </c>
       <c r="C313">
-        <v>-0.6212539751955481</v>
+        <v>0</v>
       </c>
       <c r="D313">
         <v>0.05299990057629299</v>
@@ -9822,7 +9822,7 @@
         <v>2026</v>
       </c>
       <c r="C314">
-        <v>-0.6068033568396469</v>
+        <v>0</v>
       </c>
       <c r="D314">
         <v>0.09185719129606104</v>
@@ -9851,7 +9851,7 @@
         <v>2027</v>
       </c>
       <c r="C315">
-        <v>-0.5535903153099446</v>
+        <v>0</v>
       </c>
       <c r="D315">
         <v>0.1115476508942614</v>
@@ -9880,7 +9880,7 @@
         <v>2028</v>
       </c>
       <c r="C316">
-        <v>-0.5237166695235086</v>
+        <v>0</v>
       </c>
       <c r="D316">
         <v>0.1398863597408346</v>
@@ -9909,7 +9909,7 @@
         <v>2024</v>
       </c>
       <c r="C317">
-        <v>-0.5257593147279784</v>
+        <v>0</v>
       </c>
       <c r="E317">
         <v>0.2557420555566122</v>
@@ -9935,7 +9935,7 @@
         <v>2025</v>
       </c>
       <c r="C318">
-        <v>-0.4639687908080042</v>
+        <v>0</v>
       </c>
       <c r="E318">
         <v>0.05471360958291212</v>
@@ -9961,7 +9961,7 @@
         <v>2026</v>
       </c>
       <c r="C319">
-        <v>-0.4553839877030002</v>
+        <v>0</v>
       </c>
       <c r="E319">
         <v>-0.06771705871396916</v>
@@ -9987,7 +9987,7 @@
         <v>2027</v>
       </c>
       <c r="C320">
-        <v>-0.4040355517969726</v>
+        <v>0</v>
       </c>
       <c r="E320">
         <v>-0.183430708901453</v>
@@ -10013,7 +10013,7 @@
         <v>2028</v>
       </c>
       <c r="C321">
-        <v>-0.3814246819202798</v>
+        <v>0</v>
       </c>
       <c r="E321">
         <v>-0.2700775695307662</v>
@@ -10039,7 +10039,7 @@
         <v>2024</v>
       </c>
       <c r="C322">
-        <v>-1.200645085051891</v>
+        <v>0</v>
       </c>
       <c r="D322">
         <v>-0.5018155552549192</v>
@@ -10068,7 +10068,7 @@
         <v>2025</v>
       </c>
       <c r="C323">
-        <v>-1.1565309548736</v>
+        <v>0</v>
       </c>
       <c r="D323">
         <v>-0.5609974474574028</v>
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="C324">
-        <v>-1.122117651195329</v>
+        <v>0</v>
       </c>
       <c r="D324">
         <v>-0.6161236372406733</v>
@@ -10126,7 +10126,7 @@
         <v>2027</v>
       </c>
       <c r="C325">
-        <v>-1.062558895865299</v>
+        <v>0</v>
       </c>
       <c r="D325">
         <v>-0.6682079547906998</v>
@@ -10155,7 +10155,7 @@
         <v>2028</v>
       </c>
       <c r="C326">
-        <v>-1.007968367345335</v>
+        <v>0</v>
       </c>
       <c r="D326">
         <v>-0.7133489985103252</v>
@@ -10184,7 +10184,7 @@
         <v>2024</v>
       </c>
       <c r="C327">
-        <v>-0.171357345347191</v>
+        <v>0.171357345347191</v>
       </c>
       <c r="D327">
         <v>0.8186091533697976</v>
@@ -10210,7 +10210,7 @@
         <v>2025</v>
       </c>
       <c r="C328">
-        <v>-0.1541342063254201</v>
+        <v>0.1541342063254201</v>
       </c>
       <c r="D328">
         <v>0.7434108369921405</v>
@@ -10236,7 +10236,7 @@
         <v>2026</v>
       </c>
       <c r="C329">
-        <v>-0.1753825142473781</v>
+        <v>0.1753825142473781</v>
       </c>
       <c r="D329">
         <v>0.6825737697848095</v>
@@ -10262,7 +10262,7 @@
         <v>2027</v>
       </c>
       <c r="C330">
-        <v>-0.1581971226616976</v>
+        <v>0.1581971226616976</v>
       </c>
       <c r="D330">
         <v>0.613302788738515</v>
@@ -10288,7 +10288,7 @@
         <v>2028</v>
       </c>
       <c r="C331">
-        <v>-0.1713639272055215</v>
+        <v>0.1713639272055215</v>
       </c>
       <c r="D331">
         <v>0.5543903575502648</v>
@@ -10314,7 +10314,7 @@
         <v>2024</v>
       </c>
       <c r="C332">
-        <v>0.2890460861217849</v>
+        <v>0</v>
       </c>
       <c r="D332">
         <v>0.1352719260801429</v>
@@ -10343,7 +10343,7 @@
         <v>2025</v>
       </c>
       <c r="C333">
-        <v>0.2419063633916917</v>
+        <v>0</v>
       </c>
       <c r="D333">
         <v>0.1236423688501571</v>
@@ -10372,7 +10372,7 @@
         <v>2026</v>
       </c>
       <c r="C334">
-        <v>0.1993827526297574</v>
+        <v>0</v>
       </c>
       <c r="D334">
         <v>0.1438966504099704</v>
@@ -10401,7 +10401,7 @@
         <v>2027</v>
       </c>
       <c r="C335">
-        <v>0.1609762995289148</v>
+        <v>0</v>
       </c>
       <c r="D335">
         <v>0.1500027914979811</v>
@@ -10430,7 +10430,7 @@
         <v>2028</v>
       </c>
       <c r="C336">
-        <v>0.1115536781909437</v>
+        <v>0</v>
       </c>
       <c r="D336">
         <v>0.1631839224695572</v>
@@ -10749,7 +10749,7 @@
         <v>2024</v>
       </c>
       <c r="C347">
-        <v>-1.223786153169657</v>
+        <v>0</v>
       </c>
       <c r="D347">
         <v>-1.02855100506557</v>
@@ -10778,7 +10778,7 @@
         <v>2025</v>
       </c>
       <c r="C348">
-        <v>-1.191454380986974</v>
+        <v>0</v>
       </c>
       <c r="D348">
         <v>-0.9221412191378296</v>
@@ -10807,7 +10807,7 @@
         <v>2026</v>
       </c>
       <c r="C349">
-        <v>-1.158983821306791</v>
+        <v>0</v>
       </c>
       <c r="D349">
         <v>-0.8390644264804813</v>
@@ -10836,7 +10836,7 @@
         <v>2027</v>
       </c>
       <c r="C350">
-        <v>-1.105938372782804</v>
+        <v>0</v>
       </c>
       <c r="D350">
         <v>-0.7493481690825453</v>
@@ -10865,7 +10865,7 @@
         <v>2028</v>
       </c>
       <c r="C351">
-        <v>-1.054113737106166</v>
+        <v>0</v>
       </c>
       <c r="D351">
         <v>-0.6645505030774579</v>
@@ -11039,7 +11039,7 @@
         <v>2024</v>
       </c>
       <c r="C357">
-        <v>-0.993663279901893</v>
+        <v>0</v>
       </c>
       <c r="D357">
         <v>-1.320120667647869</v>
@@ -11071,7 +11071,7 @@
         <v>2025</v>
       </c>
       <c r="C358">
-        <v>-0.9450785200488272</v>
+        <v>0</v>
       </c>
       <c r="D358">
         <v>-1.348413430289584</v>
@@ -11103,7 +11103,7 @@
         <v>2026</v>
       </c>
       <c r="C359">
-        <v>-0.9188835788685376</v>
+        <v>0</v>
       </c>
       <c r="D359">
         <v>-1.37511789527658</v>
@@ -11135,7 +11135,7 @@
         <v>2027</v>
       </c>
       <c r="C360">
-        <v>-0.8624322704343889</v>
+        <v>0</v>
       </c>
       <c r="D360">
         <v>-1.39385939218151</v>
@@ -11167,7 +11167,7 @@
         <v>2028</v>
       </c>
       <c r="C361">
-        <v>-0.818022248045609</v>
+        <v>0</v>
       </c>
       <c r="D361">
         <v>-1.408751156300674</v>
@@ -11824,7 +11824,7 @@
         <v>2024</v>
       </c>
       <c r="C382">
-        <v>-0.8042615288789035</v>
+        <v>0</v>
       </c>
       <c r="D382">
         <v>-0.6405685656861702</v>
@@ -11853,7 +11853,7 @@
         <v>2025</v>
       </c>
       <c r="C383">
-        <v>-0.7228172576614434</v>
+        <v>0</v>
       </c>
       <c r="D383">
         <v>-0.6934405332322069</v>
@@ -11882,7 +11882,7 @@
         <v>2026</v>
       </c>
       <c r="C384">
-        <v>-0.6664748052413123</v>
+        <v>0</v>
       </c>
       <c r="D384">
         <v>-0.7458844413235499</v>
@@ -11911,7 +11911,7 @@
         <v>2027</v>
       </c>
       <c r="C385">
-        <v>-0.5798442277021418</v>
+        <v>0</v>
       </c>
       <c r="D385">
         <v>-0.79361462718195</v>
@@ -11940,7 +11940,7 @@
         <v>2028</v>
       </c>
       <c r="C386">
-        <v>-0.5136097246492367</v>
+        <v>0</v>
       </c>
       <c r="D386">
         <v>-0.8350408741517102</v>
@@ -12229,7 +12229,7 @@
         <v>2024</v>
       </c>
       <c r="C397">
-        <v>-1.097597944283745</v>
+        <v>0</v>
       </c>
       <c r="D397">
         <v>-0.3655733647564871</v>
@@ -12258,7 +12258,7 @@
         <v>2025</v>
       </c>
       <c r="C398">
-        <v>-1.030898078077326</v>
+        <v>0</v>
       </c>
       <c r="D398">
         <v>-0.4267801865627662</v>
@@ -12287,7 +12287,7 @@
         <v>2026</v>
       </c>
       <c r="C399">
-        <v>-0.9938970774083618</v>
+        <v>0</v>
       </c>
       <c r="D399">
         <v>-0.4823773864740893</v>
@@ -12316,7 +12316,7 @@
         <v>2027</v>
       </c>
       <c r="C400">
-        <v>-0.9238665807399216</v>
+        <v>0</v>
       </c>
       <c r="D400">
         <v>-0.5361650417738605</v>
@@ -12345,7 +12345,7 @@
         <v>2028</v>
       </c>
       <c r="C401">
-        <v>-0.8660341568703747</v>
+        <v>0</v>
       </c>
       <c r="D401">
         <v>-0.5826609947187151</v>
@@ -12374,7 +12374,7 @@
         <v>2024</v>
       </c>
       <c r="C402">
-        <v>0.06660043105490791</v>
+        <v>0</v>
       </c>
       <c r="D402">
         <v>-0.168165851985907</v>
@@ -12403,7 +12403,7 @@
         <v>2025</v>
       </c>
       <c r="C403">
-        <v>0.1949111152613053</v>
+        <v>0</v>
       </c>
       <c r="D403">
         <v>-0.2145141465738043</v>
@@ -12432,7 +12432,7 @@
         <v>2026</v>
       </c>
       <c r="C404">
-        <v>0.1950025369550518</v>
+        <v>0</v>
       </c>
       <c r="D404">
         <v>-0.2532097846638322</v>
@@ -12461,7 +12461,7 @@
         <v>2027</v>
       </c>
       <c r="C405">
-        <v>0.2675378319727758</v>
+        <v>0</v>
       </c>
       <c r="D405">
         <v>-0.2933110976894878</v>
@@ -12490,7 +12490,7 @@
         <v>2028</v>
       </c>
       <c r="C406">
-        <v>0.2811324045829402</v>
+        <v>0</v>
       </c>
       <c r="D406">
         <v>-0.3263525012521139</v>
@@ -12519,7 +12519,7 @@
         <v>2024</v>
       </c>
       <c r="C407">
-        <v>-0.6365974067325599</v>
+        <v>0.6365974067325599</v>
       </c>
       <c r="D407">
         <v>-1.159354871393768</v>
@@ -12548,7 +12548,7 @@
         <v>2025</v>
       </c>
       <c r="C408">
-        <v>-0.5286174820535969</v>
+        <v>0.5286174820535969</v>
       </c>
       <c r="D408">
         <v>-1.277209157320765</v>
@@ -12577,7 +12577,7 @@
         <v>2026</v>
       </c>
       <c r="C409">
-        <v>-0.4710698214653583</v>
+        <v>0.4710698214653583</v>
       </c>
       <c r="D409">
         <v>-1.35047077292976</v>
@@ -12606,7 +12606,7 @@
         <v>2027</v>
       </c>
       <c r="C410">
-        <v>-0.3709594394272249</v>
+        <v>0.3709594394272249</v>
       </c>
       <c r="D410">
         <v>-1.432834462919918</v>
@@ -12635,7 +12635,7 @@
         <v>2028</v>
       </c>
       <c r="C411">
-        <v>-0.3021025111798772</v>
+        <v>0.3021025111798772</v>
       </c>
       <c r="D411">
         <v>-1.498712446058626</v>
@@ -12664,7 +12664,7 @@
         <v>2024</v>
       </c>
       <c r="C412">
-        <v>-0.4474737881525681</v>
+        <v>0.4474737881525681</v>
       </c>
       <c r="D412">
         <v>0.3413930370847713</v>
@@ -12693,7 +12693,7 @@
         <v>2025</v>
       </c>
       <c r="C413">
-        <v>-0.3259602484515553</v>
+        <v>0.3259602484515553</v>
       </c>
       <c r="D413">
         <v>0.3532464920922067</v>
@@ -12722,7 +12722,7 @@
         <v>2026</v>
       </c>
       <c r="C414">
-        <v>-0.2664287280282661</v>
+        <v>0.2664287280282661</v>
       </c>
       <c r="D414">
         <v>0.3733553791843915</v>
@@ -12751,7 +12751,7 @@
         <v>2027</v>
       </c>
       <c r="C415">
-        <v>-0.1594872029942011</v>
+        <v>0.1594872029942011</v>
       </c>
       <c r="D415">
         <v>0.3836988668160402</v>
@@ -12780,7 +12780,7 @@
         <v>2028</v>
       </c>
       <c r="C416">
-        <v>-0.09136042966930016</v>
+        <v>0.09136042966930016</v>
       </c>
       <c r="D416">
         <v>0.3996070599751663</v>
@@ -12809,7 +12809,7 @@
         <v>2024</v>
       </c>
       <c r="C417">
-        <v>0.3129207806761741</v>
+        <v>0</v>
       </c>
       <c r="E417">
         <v>0.2376022512420033</v>
@@ -12832,7 +12832,7 @@
         <v>2025</v>
       </c>
       <c r="C418">
-        <v>0.4511663789495954</v>
+        <v>0</v>
       </c>
       <c r="E418">
         <v>0.1841680218722193</v>
@@ -12855,7 +12855,7 @@
         <v>2026</v>
       </c>
       <c r="C419">
-        <v>0.439693168833158</v>
+        <v>0</v>
       </c>
       <c r="E419">
         <v>-0.03314606798526708</v>
@@ -12878,7 +12878,7 @@
         <v>2027</v>
       </c>
       <c r="C420">
-        <v>0.5091619162260359</v>
+        <v>0</v>
       </c>
       <c r="E420">
         <v>-0.1078032244820237</v>
@@ -12901,7 +12901,7 @@
         <v>2028</v>
       </c>
       <c r="C421">
-        <v>0.5102567659052528</v>
+        <v>0</v>
       </c>
       <c r="E421">
         <v>-0.2341861009500873</v>
@@ -13069,7 +13069,7 @@
         <v>2024</v>
       </c>
       <c r="C427">
-        <v>-0.8856913899840821</v>
+        <v>0</v>
       </c>
       <c r="D427">
         <v>-0.3061363551423562</v>
@@ -13098,7 +13098,7 @@
         <v>2025</v>
       </c>
       <c r="C428">
-        <v>-0.8866401488848432</v>
+        <v>0</v>
       </c>
       <c r="D428">
         <v>-0.292422131513369</v>
@@ -13127,7 +13127,7 @@
         <v>2026</v>
       </c>
       <c r="C429">
-        <v>-0.91463492835451</v>
+        <v>0</v>
       </c>
       <c r="D429">
         <v>-0.2743473791817371</v>
@@ -13156,7 +13156,7 @@
         <v>2027</v>
       </c>
       <c r="C430">
-        <v>-0.9049421977795788</v>
+        <v>0</v>
       </c>
       <c r="D430">
         <v>-0.2603020215820229</v>
@@ -13185,7 +13185,7 @@
         <v>2028</v>
       </c>
       <c r="C431">
-        <v>-0.9005807459894873</v>
+        <v>0</v>
       </c>
       <c r="D431">
         <v>-0.2421041315352776</v>
@@ -14084,7 +14084,7 @@
         <v>2024</v>
       </c>
       <c r="C462">
-        <v>-1.491390064229221</v>
+        <v>0</v>
       </c>
       <c r="D462">
         <v>-0.01547269047407991</v>
@@ -14113,7 +14113,7 @@
         <v>2025</v>
       </c>
       <c r="C463">
-        <v>-1.472199394031598</v>
+        <v>0</v>
       </c>
       <c r="D463">
         <v>-0.02656241729134401</v>
@@ -14142,7 +14142,7 @@
         <v>2026</v>
       </c>
       <c r="C464">
-        <v>-1.443007267367663</v>
+        <v>0</v>
       </c>
       <c r="D464">
         <v>-0.00477239004002043</v>
@@ -14171,7 +14171,7 @@
         <v>2027</v>
       </c>
       <c r="C465">
-        <v>-1.394857104801411</v>
+        <v>0</v>
       </c>
       <c r="D465">
         <v>0.00195388910486114</v>
@@ -14200,7 +14200,7 @@
         <v>2028</v>
       </c>
       <c r="C466">
-        <v>-1.337951734072622</v>
+        <v>0</v>
       </c>
       <c r="D466">
         <v>0.0165646742773468</v>
@@ -14229,7 +14229,7 @@
         <v>2024</v>
       </c>
       <c r="C467">
-        <v>-0.8544009892195769</v>
+        <v>0</v>
       </c>
       <c r="E467">
         <v>-1.31303856918913</v>
@@ -14255,7 +14255,7 @@
         <v>2025</v>
       </c>
       <c r="C468">
-        <v>-0.7770829291485152</v>
+        <v>0</v>
       </c>
       <c r="E468">
         <v>-1.262559595843385</v>
@@ -14281,7 +14281,7 @@
         <v>2026</v>
       </c>
       <c r="C469">
-        <v>-0.7505881691851588</v>
+        <v>0</v>
       </c>
       <c r="E469">
         <v>-1.185371301601692</v>
@@ -14307,7 +14307,7 @@
         <v>2027</v>
       </c>
       <c r="C470">
-        <v>-0.6826961260140519</v>
+        <v>0</v>
       </c>
       <c r="E470">
         <v>-1.102736948465317</v>
@@ -14333,7 +14333,7 @@
         <v>2028</v>
       </c>
       <c r="C471">
-        <v>-0.6364398755944011</v>
+        <v>0</v>
       </c>
       <c r="E471">
         <v>-1.03599012022314</v>
@@ -14474,7 +14474,7 @@
         <v>2024</v>
       </c>
       <c r="C477">
-        <v>-0.9758214040125204</v>
+        <v>0</v>
       </c>
       <c r="D477">
         <v>0.08590853836272253</v>
@@ -14503,7 +14503,7 @@
         <v>2025</v>
       </c>
       <c r="C478">
-        <v>-0.9737733800501468</v>
+        <v>0</v>
       </c>
       <c r="D478">
         <v>0.03330603051546659</v>
@@ -14532,7 +14532,7 @@
         <v>2026</v>
       </c>
       <c r="C479">
-        <v>-0.9932585776210602</v>
+        <v>0</v>
       </c>
       <c r="D479">
         <v>-0.009814438980038779</v>
@@ -14561,7 +14561,7 @@
         <v>2027</v>
       </c>
       <c r="C480">
-        <v>-0.977843273177004</v>
+        <v>0</v>
       </c>
       <c r="D480">
         <v>-0.05621856729523428</v>
@@ -14590,7 +14590,7 @@
         <v>2028</v>
       </c>
       <c r="C481">
-        <v>-0.9656631226800853</v>
+        <v>0</v>
       </c>
       <c r="D481">
         <v>-0.09476882240789468</v>
@@ -14619,7 +14619,7 @@
         <v>2024</v>
       </c>
       <c r="C482">
-        <v>-1.406372622915387</v>
+        <v>1.406372622915387</v>
       </c>
       <c r="D482">
         <v>0.5809238833757993</v>
@@ -14648,7 +14648,7 @@
         <v>2025</v>
       </c>
       <c r="C483">
-        <v>-1.390349479662668</v>
+        <v>1.390349479662668</v>
       </c>
       <c r="D483">
         <v>0.578931982873227</v>
@@ -14677,7 +14677,7 @@
         <v>2026</v>
       </c>
       <c r="C484">
-        <v>-1.368597340004112</v>
+        <v>1.368597340004112</v>
       </c>
       <c r="D484">
         <v>0.5877770677443008</v>
@@ -14706,7 +14706,7 @@
         <v>2027</v>
       </c>
       <c r="C485">
-        <v>-1.325741818634872</v>
+        <v>1.325741818634872</v>
       </c>
       <c r="D485">
         <v>0.5856202662447259</v>
@@ -14735,7 +14735,7 @@
         <v>2028</v>
       </c>
       <c r="C486">
-        <v>-1.27598645522721</v>
+        <v>1.27598645522721</v>
       </c>
       <c r="D486">
         <v>0.5901014336103046</v>
@@ -15389,7 +15389,7 @@
         <v>2024</v>
       </c>
       <c r="C507">
-        <v>-0.948037529215032</v>
+        <v>0</v>
       </c>
       <c r="D507">
         <v>-1.161986523354516</v>
@@ -15415,7 +15415,7 @@
         <v>2025</v>
       </c>
       <c r="C508">
-        <v>-0.9585341059639308</v>
+        <v>0</v>
       </c>
       <c r="D508">
         <v>-1.221819082009827</v>
@@ -15441,7 +15441,7 @@
         <v>2026</v>
       </c>
       <c r="C509">
-        <v>-0.9652161881218064</v>
+        <v>0</v>
       </c>
       <c r="D509">
         <v>-1.307641305681064</v>
@@ -15467,7 +15467,7 @@
         <v>2027</v>
       </c>
       <c r="C510">
-        <v>-0.9524274789828876</v>
+        <v>0</v>
       </c>
       <c r="D510">
         <v>-1.361125568787928</v>
@@ -15493,7 +15493,7 @@
         <v>2028</v>
       </c>
       <c r="C511">
-        <v>-0.9366533468816308</v>
+        <v>0</v>
       </c>
       <c r="D511">
         <v>-1.425900139680736</v>
@@ -15519,7 +15519,7 @@
         <v>2024</v>
       </c>
       <c r="C512">
-        <v>-0.5175230597498505</v>
+        <v>0</v>
       </c>
       <c r="D512">
         <v>-0.7172660623099653</v>
@@ -15545,7 +15545,7 @@
         <v>2025</v>
       </c>
       <c r="C513">
-        <v>-0.4751045752717074</v>
+        <v>0</v>
       </c>
       <c r="D513">
         <v>-0.8027718993906094</v>
@@ -15571,7 +15571,7 @@
         <v>2026</v>
       </c>
       <c r="C514">
-        <v>-0.472839009993935</v>
+        <v>0</v>
       </c>
       <c r="D514">
         <v>-0.8386705016865875</v>
@@ -15597,7 +15597,7 @@
         <v>2027</v>
       </c>
       <c r="C515">
-        <v>-0.4355348498867573</v>
+        <v>0</v>
       </c>
       <c r="D515">
         <v>-0.89354870998852</v>
@@ -15623,7 +15623,7 @@
         <v>2028</v>
       </c>
       <c r="C516">
-        <v>-0.4210191670641581</v>
+        <v>0</v>
       </c>
       <c r="D516">
         <v>-0.9298399888917888</v>
@@ -15794,7 +15794,7 @@
         <v>2024</v>
       </c>
       <c r="C522">
-        <v>-1.452312656877222</v>
+        <v>0</v>
       </c>
       <c r="D522">
         <v>-0.1431920156276299</v>
@@ -15823,7 +15823,7 @@
         <v>2025</v>
       </c>
       <c r="C523">
-        <v>-1.434421291254224</v>
+        <v>0</v>
       </c>
       <c r="D523">
         <v>-0.1462246671340732</v>
@@ -15852,7 +15852,7 @@
         <v>2026</v>
       </c>
       <c r="C524">
-        <v>-1.408918610971318</v>
+        <v>0</v>
       </c>
       <c r="D524">
         <v>-0.1262933206408676</v>
@@ -15881,7 +15881,7 @@
         <v>2027</v>
       </c>
       <c r="C525">
-        <v>-1.363249555195172</v>
+        <v>0</v>
       </c>
       <c r="D525">
         <v>-0.1157902098770116</v>
@@ -15910,7 +15910,7 @@
         <v>2028</v>
       </c>
       <c r="C526">
-        <v>-1.309734101818051</v>
+        <v>0</v>
       </c>
       <c r="D526">
         <v>-0.09969287848099535</v>
@@ -15939,7 +15939,7 @@
         <v>2024</v>
       </c>
       <c r="C527">
-        <v>-0.3072670266119297</v>
+        <v>0</v>
       </c>
       <c r="D527">
         <v>-1.10360839381463</v>
@@ -15968,7 +15968,7 @@
         <v>2025</v>
       </c>
       <c r="C528">
-        <v>-0.4022085162923786</v>
+        <v>0</v>
       </c>
       <c r="D528">
         <v>-1.194216143419615</v>
@@ -15997,7 +15997,7 @@
         <v>2026</v>
       </c>
       <c r="C529">
-        <v>-0.3583319484261392</v>
+        <v>0</v>
       </c>
       <c r="D529">
         <v>-1.279753699014093</v>
@@ -16026,7 +16026,7 @@
         <v>2027</v>
       </c>
       <c r="C530">
-        <v>-0.3931349867537017</v>
+        <v>0</v>
       </c>
       <c r="D530">
         <v>-1.355410942900983</v>
@@ -16055,7 +16055,7 @@
         <v>2028</v>
       </c>
       <c r="C531">
-        <v>-0.3781398255021352</v>
+        <v>0</v>
       </c>
       <c r="D531">
         <v>-1.424039615127925</v>
@@ -16084,7 +16084,7 @@
         <v>2024</v>
       </c>
       <c r="C532">
-        <v>0.316497037344413</v>
+        <v>0</v>
       </c>
       <c r="D532">
         <v>-0.7570120377553629</v>
@@ -16110,7 +16110,7 @@
         <v>2025</v>
       </c>
       <c r="C533">
-        <v>0.2518843954332016</v>
+        <v>0</v>
       </c>
       <c r="D533">
         <v>-0.7371656405370651</v>
@@ -16136,7 +16136,7 @@
         <v>2026</v>
       </c>
       <c r="C534">
-        <v>0.1966331696331588</v>
+        <v>0</v>
       </c>
       <c r="D534">
         <v>-0.7222179505879119</v>
@@ -16162,7 +16162,7 @@
         <v>2027</v>
       </c>
       <c r="C535">
-        <v>0.1363817635874527</v>
+        <v>0</v>
       </c>
       <c r="D535">
         <v>-0.7057005799476377</v>
@@ -16188,7 +16188,7 @@
         <v>2028</v>
       </c>
       <c r="C536">
-        <v>0.07824852024905783</v>
+        <v>0</v>
       </c>
       <c r="D536">
         <v>-0.6863370886198881</v>
@@ -16214,7 +16214,7 @@
         <v>2024</v>
       </c>
       <c r="C537">
-        <v>0.4456682252001334</v>
+        <v>0</v>
       </c>
       <c r="D537">
         <v>-0.8190234941277238</v>
@@ -16243,7 +16243,7 @@
         <v>2025</v>
       </c>
       <c r="C538">
-        <v>0.3757071413702409</v>
+        <v>0</v>
       </c>
       <c r="D538">
         <v>-0.7879749425473325</v>
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="C539">
-        <v>0.3131183980993024</v>
+        <v>0</v>
       </c>
       <c r="D539">
         <v>-0.7495925517796287</v>
@@ -16301,7 +16301,7 @@
         <v>2027</v>
       </c>
       <c r="C540">
-        <v>0.245123505142443</v>
+        <v>0</v>
       </c>
       <c r="D540">
         <v>-0.7101900813749323</v>
@@ -16330,7 +16330,7 @@
         <v>2028</v>
       </c>
       <c r="C541">
-        <v>0.1781547598962261</v>
+        <v>0</v>
       </c>
       <c r="D541">
         <v>-0.6683126560661266</v>
@@ -16359,7 +16359,7 @@
         <v>2024</v>
       </c>
       <c r="C542">
-        <v>1.172628947793902</v>
+        <v>0</v>
       </c>
       <c r="D542">
         <v>-1.148779384452369</v>
@@ -16388,7 +16388,7 @@
         <v>2025</v>
       </c>
       <c r="C543">
-        <v>1.070423806197218</v>
+        <v>0</v>
       </c>
       <c r="D543">
         <v>-1.136670666807069</v>
@@ -16417,7 +16417,7 @@
         <v>2026</v>
       </c>
       <c r="C544">
-        <v>0.9689223667371872</v>
+        <v>0</v>
       </c>
       <c r="D544">
         <v>-1.116258238781224</v>
@@ -16446,7 +16446,7 @@
         <v>2027</v>
       </c>
       <c r="C545">
-        <v>0.8570038120941542</v>
+        <v>0</v>
       </c>
       <c r="D545">
         <v>-1.094623390381247</v>
@@ -16475,7 +16475,7 @@
         <v>2028</v>
       </c>
       <c r="C546">
-        <v>0.7413802494817191</v>
+        <v>0</v>
       </c>
       <c r="D546">
         <v>-1.0703259053666</v>
@@ -16504,7 +16504,7 @@
         <v>2024</v>
       </c>
       <c r="C547">
-        <v>-1.039849169199672</v>
+        <v>0</v>
       </c>
       <c r="D547">
         <v>-1.440217373603307</v>
@@ -16533,7 +16533,7 @@
         <v>2025</v>
       </c>
       <c r="C548">
-        <v>-1.043362946769161</v>
+        <v>0</v>
       </c>
       <c r="D548">
         <v>-1.441164043373958</v>
@@ -16562,7 +16562,7 @@
         <v>2026</v>
       </c>
       <c r="C549">
-        <v>-1.026301356761459</v>
+        <v>0</v>
       </c>
       <c r="D549">
         <v>-1.442405245290496</v>
@@ -16591,7 +16591,7 @@
         <v>2027</v>
       </c>
       <c r="C550">
-        <v>-1.004233551788263</v>
+        <v>0</v>
       </c>
       <c r="D550">
         <v>-1.436259358559477</v>
@@ -16620,7 +16620,7 @@
         <v>2028</v>
       </c>
       <c r="C551">
-        <v>-0.971640131773322</v>
+        <v>0</v>
       </c>
       <c r="D551">
         <v>-1.42766901606774</v>
@@ -16649,7 +16649,7 @@
         <v>2024</v>
       </c>
       <c r="C552">
-        <v>0.2438491008244983</v>
+        <v>0</v>
       </c>
       <c r="D552">
         <v>-1.372588877293848</v>
@@ -16678,7 +16678,7 @@
         <v>2025</v>
       </c>
       <c r="C553">
-        <v>0.1828396334490424</v>
+        <v>0</v>
       </c>
       <c r="D553">
         <v>-1.36706013369258</v>
@@ -16707,7 +16707,7 @@
         <v>2026</v>
       </c>
       <c r="C554">
-        <v>0.1310538465430872</v>
+        <v>0</v>
       </c>
       <c r="D554">
         <v>-1.370576400575805</v>
@@ -16736,7 +16736,7 @@
         <v>2027</v>
       </c>
       <c r="C555">
-        <v>0.07525306365225612</v>
+        <v>0</v>
       </c>
       <c r="D555">
         <v>-1.36549541532304</v>
@@ -16765,7 +16765,7 @@
         <v>2028</v>
       </c>
       <c r="C556">
-        <v>0.02179188761165605</v>
+        <v>0</v>
       </c>
       <c r="D556">
         <v>-1.358314848911763</v>
@@ -16794,7 +16794,7 @@
         <v>2024</v>
       </c>
       <c r="C557">
-        <v>0.3878331454777683</v>
+        <v>0</v>
       </c>
       <c r="E557">
         <v>-0.4991573748347767</v>
@@ -16823,7 +16823,7 @@
         <v>2025</v>
       </c>
       <c r="C558">
-        <v>0.3882523358349423</v>
+        <v>0</v>
       </c>
       <c r="E558">
         <v>-0.5603756048019864</v>
@@ -16852,7 +16852,7 @@
         <v>2026</v>
       </c>
       <c r="C559">
-        <v>0.323768124128667</v>
+        <v>0</v>
       </c>
       <c r="E559">
         <v>-0.6031053894824117</v>
@@ -16881,7 +16881,7 @@
         <v>2027</v>
       </c>
       <c r="C560">
-        <v>0.295304228988927</v>
+        <v>0</v>
       </c>
       <c r="E560">
         <v>-0.6291909689488772</v>
@@ -16910,7 +16910,7 @@
         <v>2028</v>
       </c>
       <c r="C561">
-        <v>0.2371084795329141</v>
+        <v>0</v>
       </c>
       <c r="E561">
         <v>-0.6495669211475096</v>
@@ -17259,7 +17259,7 @@
         <v>2024</v>
       </c>
       <c r="C572">
-        <v>-0.1429872177735866</v>
+        <v>0</v>
       </c>
       <c r="D572">
         <v>-0.2172321852965786</v>
@@ -17291,7 +17291,7 @@
         <v>2025</v>
       </c>
       <c r="C573">
-        <v>-0.1235936619225156</v>
+        <v>0</v>
       </c>
       <c r="D573">
         <v>-0.2226075020044714</v>
@@ -17323,7 +17323,7 @@
         <v>2026</v>
       </c>
       <c r="C574">
-        <v>-0.2087777985554061</v>
+        <v>0</v>
       </c>
       <c r="D574">
         <v>-0.2300903435038503</v>
@@ -17355,7 +17355,7 @@
         <v>2027</v>
       </c>
       <c r="C575">
-        <v>-0.2254316731527862</v>
+        <v>0</v>
       </c>
       <c r="D575">
         <v>-0.2382204314420316</v>
@@ -17387,7 +17387,7 @@
         <v>2028</v>
       </c>
       <c r="C576">
-        <v>-0.2740707059930563</v>
+        <v>0</v>
       </c>
       <c r="D576">
         <v>-0.2417107599730168</v>
@@ -18059,7 +18059,7 @@
         <v>2024</v>
       </c>
       <c r="C597">
-        <v>-0.7155250646893369</v>
+        <v>0</v>
       </c>
       <c r="D597">
         <v>1.636184538705447</v>
@@ -18091,7 +18091,7 @@
         <v>2025</v>
       </c>
       <c r="C598">
-        <v>-0.6928215523380644</v>
+        <v>0</v>
       </c>
       <c r="D598">
         <v>1.811753650186848</v>
@@ -18123,7 +18123,7 @@
         <v>2026</v>
       </c>
       <c r="C599">
-        <v>-0.7284658759881298</v>
+        <v>0</v>
       </c>
       <c r="D599">
         <v>2.000185851355565</v>
@@ -18155,7 +18155,7 @@
         <v>2027</v>
       </c>
       <c r="C600">
-        <v>-0.7160345109278541</v>
+        <v>0</v>
       </c>
       <c r="D600">
         <v>2.155484044532096</v>
@@ -18187,7 +18187,7 @@
         <v>2028</v>
       </c>
       <c r="C601">
-        <v>-0.7189971686797553</v>
+        <v>0</v>
       </c>
       <c r="D601">
         <v>2.311869258922488</v>
@@ -18219,7 +18219,7 @@
         <v>2024</v>
       </c>
       <c r="C602">
-        <v>0.6745970164392803</v>
+        <v>0</v>
       </c>
       <c r="D602">
         <v>0.3570284014031334</v>
@@ -18251,7 +18251,7 @@
         <v>2025</v>
       </c>
       <c r="C603">
-        <v>0.7251840870849956</v>
+        <v>0</v>
       </c>
       <c r="D603">
         <v>0.3767609842119471</v>
@@ -18283,7 +18283,7 @@
         <v>2026</v>
       </c>
       <c r="C604">
-        <v>0.5866533133784808</v>
+        <v>0</v>
       </c>
       <c r="D604">
         <v>0.4649705116439444</v>
@@ -18315,7 +18315,7 @@
         <v>2027</v>
       </c>
       <c r="C605">
-        <v>0.547053899618031</v>
+        <v>0</v>
       </c>
       <c r="D605">
         <v>0.5021643014917198</v>
@@ -18347,7 +18347,7 @@
         <v>2028</v>
       </c>
       <c r="C606">
-        <v>0.4460336343356706</v>
+        <v>0</v>
       </c>
       <c r="D606">
         <v>0.5664671388868713</v>
@@ -18539,7 +18539,7 @@
         <v>2024</v>
       </c>
       <c r="C612">
-        <v>-0.1153896903506959</v>
+        <v>0</v>
       </c>
       <c r="D612">
         <v>0.678298093790538</v>
@@ -18571,7 +18571,7 @@
         <v>2025</v>
       </c>
       <c r="C613">
-        <v>-0.06959322618672342</v>
+        <v>0</v>
       </c>
       <c r="D613">
         <v>0.7678623674787929</v>
@@ -18603,7 +18603,7 @@
         <v>2026</v>
       </c>
       <c r="C614">
-        <v>-0.1448885592186161</v>
+        <v>0</v>
       </c>
       <c r="D614">
         <v>0.8642709856002395</v>
@@ -18635,7 +18635,7 @@
         <v>2027</v>
       </c>
       <c r="C615">
-        <v>-0.1494818582174675</v>
+        <v>0</v>
       </c>
       <c r="D615">
         <v>0.9428439692064758</v>
@@ -18667,7 +18667,7 @@
         <v>2028</v>
       </c>
       <c r="C616">
-        <v>-0.1910984280975868</v>
+        <v>0</v>
       </c>
       <c r="D616">
         <v>1.024285820267813</v>
@@ -18699,7 +18699,7 @@
         <v>2024</v>
       </c>
       <c r="C617">
-        <v>-0.09346435464719707</v>
+        <v>0.09346435464719707</v>
       </c>
       <c r="D617">
         <v>2.612147339690109</v>
@@ -18728,7 +18728,7 @@
         <v>2025</v>
       </c>
       <c r="C618">
-        <v>-0.04993812308629261</v>
+        <v>0.04993812308629261</v>
       </c>
       <c r="D618">
         <v>2.737306086347542</v>
@@ -18757,7 +18757,7 @@
         <v>2026</v>
       </c>
       <c r="C619">
-        <v>-0.11870611187084</v>
+        <v>0.11870611187084</v>
       </c>
       <c r="D619">
         <v>2.877046170240285</v>
@@ -18786,7 +18786,7 @@
         <v>2027</v>
       </c>
       <c r="C620">
-        <v>-0.1193729413422635</v>
+        <v>0.1193729413422635</v>
       </c>
       <c r="D620">
         <v>2.782800414343081</v>
@@ -18815,7 +18815,7 @@
         <v>2028</v>
       </c>
       <c r="C621">
-        <v>-0.1581706515255783</v>
+        <v>0.1581706515255783</v>
       </c>
       <c r="D621">
         <v>2.678715580635587</v>
@@ -18844,7 +18844,7 @@
         <v>2024</v>
       </c>
       <c r="C622">
-        <v>0.4651665691714695</v>
+        <v>0</v>
       </c>
       <c r="D622">
         <v>0.949442900293421</v>
@@ -18876,7 +18876,7 @@
         <v>2025</v>
       </c>
       <c r="C623">
-        <v>0.4720452676699075</v>
+        <v>0</v>
       </c>
       <c r="D623">
         <v>1.074721321837488</v>
@@ -18908,7 +18908,7 @@
         <v>2026</v>
       </c>
       <c r="C624">
-        <v>0.3435163285188202</v>
+        <v>0</v>
       </c>
       <c r="D624">
         <v>1.184637455791985</v>
@@ -18940,7 +18940,7 @@
         <v>2027</v>
       </c>
       <c r="C625">
-        <v>0.2976823507407175</v>
+        <v>0</v>
       </c>
       <c r="D625">
         <v>1.280857170016343</v>
@@ -18972,7 +18972,7 @@
         <v>2028</v>
       </c>
       <c r="C626">
-        <v>0.2039623511130827</v>
+        <v>0</v>
       </c>
       <c r="D626">
         <v>1.377003012475174</v>
@@ -19614,7 +19614,7 @@
         <v>2024</v>
       </c>
       <c r="C647">
-        <v>1.633550948988564</v>
+        <v>0</v>
       </c>
       <c r="D647">
         <v>-0.1181832254508423</v>
@@ -19643,7 +19643,7 @@
         <v>2025</v>
       </c>
       <c r="C648">
-        <v>1.423511182966886</v>
+        <v>0</v>
       </c>
       <c r="D648">
         <v>-0.1347351845864104</v>
@@ -19672,7 +19672,7 @@
         <v>2026</v>
       </c>
       <c r="C649">
-        <v>1.342710730264844</v>
+        <v>0</v>
       </c>
       <c r="D649">
         <v>-0.1453338015868532</v>
@@ -19701,7 +19701,7 @@
         <v>2027</v>
       </c>
       <c r="C650">
-        <v>1.12873868082088</v>
+        <v>0</v>
       </c>
       <c r="D650">
         <v>-0.1595000239513209</v>
@@ -19730,7 +19730,7 @@
         <v>2028</v>
       </c>
       <c r="C651">
-        <v>1.013460479825292</v>
+        <v>0</v>
       </c>
       <c r="D651">
         <v>-0.1677965520174426</v>
@@ -19919,7 +19919,7 @@
         <v>2024</v>
       </c>
       <c r="C657">
-        <v>1.483323225534987</v>
+        <v>0</v>
       </c>
       <c r="D657">
         <v>0.1063530625688408</v>
@@ -19951,7 +19951,7 @@
         <v>2025</v>
       </c>
       <c r="C658">
-        <v>1.290522400114977</v>
+        <v>0</v>
       </c>
       <c r="D658">
         <v>0.2525158984147716</v>
@@ -19983,7 +19983,7 @@
         <v>2026</v>
       </c>
       <c r="C659">
-        <v>1.187134160631586</v>
+        <v>0</v>
       </c>
       <c r="D659">
         <v>0.2693249183581623</v>
@@ -20015,7 +20015,7 @@
         <v>2027</v>
       </c>
       <c r="C660">
-        <v>0.9858059049808056</v>
+        <v>0</v>
       </c>
       <c r="D660">
         <v>0.3799613030029751</v>
@@ -20047,7 +20047,7 @@
         <v>2028</v>
       </c>
       <c r="C661">
-        <v>0.8624392165722947</v>
+        <v>0</v>
       </c>
       <c r="D661">
         <v>0.4099849584081728</v>
@@ -20224,7 +20224,7 @@
         <v>2024</v>
       </c>
       <c r="C667">
-        <v>0.7245614144050126</v>
+        <v>0</v>
       </c>
       <c r="D667">
         <v>1.307184327411494</v>
@@ -20256,7 +20256,7 @@
         <v>2025</v>
       </c>
       <c r="C668">
-        <v>0.8283517330616242</v>
+        <v>0</v>
       </c>
       <c r="D668">
         <v>1.351976569471646</v>
@@ -20288,7 +20288,7 @@
         <v>2026</v>
       </c>
       <c r="C669">
-        <v>0.7773459476035375</v>
+        <v>0</v>
       </c>
       <c r="D669">
         <v>1.409434545213724</v>
@@ -20320,7 +20320,7 @@
         <v>2027</v>
       </c>
       <c r="C670">
-        <v>0.8089702985488308</v>
+        <v>0</v>
       </c>
       <c r="D670">
         <v>1.44620749839745</v>
@@ -20352,7 +20352,7 @@
         <v>2028</v>
       </c>
       <c r="C671">
-        <v>0.7662484758511254</v>
+        <v>0</v>
       </c>
       <c r="D671">
         <v>1.489084866573344</v>
@@ -20384,7 +20384,7 @@
         <v>2024</v>
       </c>
       <c r="C672">
-        <v>-0.2087301380950298</v>
+        <v>0</v>
       </c>
       <c r="D672">
         <v>1.734326268780373</v>
@@ -20416,7 +20416,7 @@
         <v>2025</v>
       </c>
       <c r="C673">
-        <v>-0.1328283562096527</v>
+        <v>0</v>
       </c>
       <c r="D673">
         <v>1.636670802176794</v>
@@ -20448,7 +20448,7 @@
         <v>2026</v>
       </c>
       <c r="C674">
-        <v>-0.1437460791467887</v>
+        <v>0</v>
       </c>
       <c r="D674">
         <v>1.836837093944533</v>
@@ -20480,7 +20480,7 @@
         <v>2027</v>
       </c>
       <c r="C675">
-        <v>-0.09908769651234568</v>
+        <v>0</v>
       </c>
       <c r="D675">
         <v>1.838463996535888</v>
@@ -20512,7 +20512,7 @@
         <v>2028</v>
       </c>
       <c r="C676">
-        <v>-0.09531974369033652</v>
+        <v>0</v>
       </c>
       <c r="D676">
         <v>1.94983276582879</v>
@@ -20689,7 +20689,7 @@
         <v>2024</v>
       </c>
       <c r="C682">
-        <v>3.252233628150282</v>
+        <v>-3.252233628150282</v>
       </c>
       <c r="D682">
         <v>1.577262961377176</v>
@@ -20715,7 +20715,7 @@
         <v>2025</v>
       </c>
       <c r="C683">
-        <v>4.134980334144389</v>
+        <v>-4</v>
       </c>
       <c r="D683">
         <v>1.480805545474226</v>
@@ -20741,7 +20741,7 @@
         <v>2026</v>
       </c>
       <c r="C684">
-        <v>4.566632686845785</v>
+        <v>-4</v>
       </c>
       <c r="D684">
         <v>1.703556355838531</v>
@@ -20767,7 +20767,7 @@
         <v>2027</v>
       </c>
       <c r="C685">
-        <v>5.273810878525204</v>
+        <v>-4</v>
       </c>
       <c r="D685">
         <v>1.62729947498248</v>
@@ -20793,7 +20793,7 @@
         <v>2028</v>
       </c>
       <c r="C686">
-        <v>5.759071469093669</v>
+        <v>-4</v>
       </c>
       <c r="D686">
         <v>1.803413861120863</v>
@@ -20819,7 +20819,7 @@
         <v>2024</v>
       </c>
       <c r="C687">
-        <v>1.504956239267654</v>
+        <v>-1.504956239267654</v>
       </c>
       <c r="D687">
         <v>1.326249424578383</v>
@@ -20845,7 +20845,7 @@
         <v>2025</v>
       </c>
       <c r="C688">
-        <v>1.837919446773674</v>
+        <v>-1.837919446773674</v>
       </c>
       <c r="D688">
         <v>1.19657245564245</v>
@@ -20871,7 +20871,7 @@
         <v>2026</v>
       </c>
       <c r="C689">
-        <v>1.877316244821316</v>
+        <v>-1.877316244821316</v>
       </c>
       <c r="D689">
         <v>1.08748968639498</v>
@@ -20897,7 +20897,7 @@
         <v>2027</v>
       </c>
       <c r="C690">
-        <v>2.054986709941661</v>
+        <v>-2.054986709941661</v>
       </c>
       <c r="D690">
         <v>0.9682123651738564</v>
@@ -20923,7 +20923,7 @@
         <v>2028</v>
       </c>
       <c r="C691">
-        <v>2.100476122106919</v>
+        <v>-2.100476122106919</v>
       </c>
       <c r="D691">
         <v>0.8630957819365691</v>
@@ -20938,7 +20938,7 @@
         <v>1.141544132738779</v>
       </c>
       <c r="J691">
-        <v>4.064472637117631</v>
+        <v>4</v>
       </c>
     </row>
     <row r="692">
@@ -20949,7 +20949,7 @@
         <v>2024</v>
       </c>
       <c r="C692">
-        <v>-0.5242072182621197</v>
+        <v>0.5242072182621197</v>
       </c>
       <c r="D692">
         <v>1.135741328300393</v>
@@ -20978,7 +20978,7 @@
         <v>2025</v>
       </c>
       <c r="C693">
-        <v>-0.5154534342900283</v>
+        <v>0.5154534342900283</v>
       </c>
       <c r="D693">
         <v>1.13095642114802</v>
@@ -21007,7 +21007,7 @@
         <v>2026</v>
       </c>
       <c r="C694">
-        <v>-0.5205720414091162</v>
+        <v>0.5205720414091162</v>
       </c>
       <c r="D694">
         <v>1.145887568196836</v>
@@ -21036,7 +21036,7 @@
         <v>2027</v>
       </c>
       <c r="C695">
-        <v>-0.5067157830908722</v>
+        <v>0.5067157830908722</v>
       </c>
       <c r="D695">
         <v>1.143520077977193</v>
@@ -21065,7 +21065,7 @@
         <v>2028</v>
       </c>
       <c r="C696">
-        <v>-0.5017149655470359</v>
+        <v>0.5017149655470359</v>
       </c>
       <c r="D696">
         <v>1.149007736718452</v>
@@ -21094,7 +21094,7 @@
         <v>2024</v>
       </c>
       <c r="C697">
-        <v>1.016337891855454</v>
+        <v>0</v>
       </c>
       <c r="D697">
         <v>0.3218794449577196</v>
@@ -21126,7 +21126,7 @@
         <v>2025</v>
       </c>
       <c r="C698">
-        <v>0.8502814009045059</v>
+        <v>0</v>
       </c>
       <c r="D698">
         <v>0.3415212408483256</v>
@@ -21158,7 +21158,7 @@
         <v>2026</v>
       </c>
       <c r="C699">
-        <v>0.7930542574221471</v>
+        <v>0</v>
       </c>
       <c r="D699">
         <v>0.3689309546192141</v>
@@ -21190,7 +21190,7 @@
         <v>2027</v>
       </c>
       <c r="C700">
-        <v>0.629483446414855</v>
+        <v>0</v>
       </c>
       <c r="D700">
         <v>0.3862556067428042</v>
@@ -21222,7 +21222,7 @@
         <v>2028</v>
       </c>
       <c r="C701">
-        <v>0.5494538464481621</v>
+        <v>0</v>
       </c>
       <c r="D701">
         <v>0.4087665878168682</v>
@@ -21414,7 +21414,7 @@
         <v>2024</v>
       </c>
       <c r="C707">
-        <v>0.3201605018224103</v>
+        <v>0</v>
       </c>
       <c r="D707">
         <v>-0.5702386351040648</v>
@@ -21446,7 +21446,7 @@
         <v>2025</v>
       </c>
       <c r="C708">
-        <v>0.2025886014152338</v>
+        <v>0</v>
       </c>
       <c r="D708">
         <v>-0.5290258718601275</v>
@@ -21478,7 +21478,7 @@
         <v>2026</v>
       </c>
       <c r="C709">
-        <v>0.173695046093989</v>
+        <v>0</v>
       </c>
       <c r="D709">
         <v>-0.4859154898923903</v>
@@ -21510,7 +21510,7 @@
         <v>2027</v>
       </c>
       <c r="C710">
-        <v>0.06738409857250671</v>
+        <v>0</v>
       </c>
       <c r="D710">
         <v>-0.4461996882246469</v>
@@ -21542,7 +21542,7 @@
         <v>2028</v>
       </c>
       <c r="C711">
-        <v>0.02769769400656459</v>
+        <v>0</v>
       </c>
       <c r="D711">
         <v>-0.4040837390661916</v>
@@ -22054,7 +22054,7 @@
         <v>2024</v>
       </c>
       <c r="C727">
-        <v>1.968253938707727</v>
+        <v>0</v>
       </c>
       <c r="D727">
         <v>0.00947720287566284</v>
@@ -22086,7 +22086,7 @@
         <v>2025</v>
       </c>
       <c r="C728">
-        <v>1.734291593430234</v>
+        <v>0</v>
       </c>
       <c r="D728">
         <v>0.0551687465010199</v>
@@ -22118,7 +22118,7 @@
         <v>2026</v>
       </c>
       <c r="C729">
-        <v>1.640828669028161</v>
+        <v>0</v>
       </c>
       <c r="D729">
         <v>0.1057960669575314</v>
@@ -22150,7 +22150,7 @@
         <v>2027</v>
       </c>
       <c r="C730">
-        <v>1.399574697759505</v>
+        <v>0</v>
       </c>
       <c r="D730">
         <v>0.1474822785744486</v>
@@ -22182,7 +22182,7 @@
         <v>2028</v>
       </c>
       <c r="C731">
-        <v>1.265215762765852</v>
+        <v>0</v>
       </c>
       <c r="D731">
         <v>0.1925716225548916</v>
@@ -22374,7 +22374,7 @@
         <v>2024</v>
       </c>
       <c r="C737">
-        <v>1.302203704794232</v>
+        <v>0</v>
       </c>
       <c r="D737">
         <v>-0.8882155645360511</v>
@@ -22406,7 +22406,7 @@
         <v>2025</v>
       </c>
       <c r="C738">
-        <v>1.07734602927042</v>
+        <v>0</v>
       </c>
       <c r="D738">
         <v>-0.8398665300443831</v>
@@ -22438,7 +22438,7 @@
         <v>2026</v>
       </c>
       <c r="C739">
-        <v>1.024292527550072</v>
+        <v>0</v>
       </c>
       <c r="D739">
         <v>-0.7913345019378215</v>
@@ -22470,7 +22470,7 @@
         <v>2027</v>
       </c>
       <c r="C740">
-        <v>0.8097765854882475</v>
+        <v>0</v>
       </c>
       <c r="D740">
         <v>-0.7436996246179676</v>
@@ -22502,7 +22502,7 @@
         <v>2028</v>
       </c>
       <c r="C741">
-        <v>0.7238419398962207</v>
+        <v>0</v>
       </c>
       <c r="D741">
         <v>-0.6946298204875764</v>
@@ -22694,7 +22694,7 @@
         <v>2024</v>
       </c>
       <c r="C747">
-        <v>0.9580463811499196</v>
+        <v>0</v>
       </c>
       <c r="D747">
         <v>-1.444963934478881</v>
@@ -22726,7 +22726,7 @@
         <v>2025</v>
       </c>
       <c r="C748">
-        <v>0.8004035160955348</v>
+        <v>0</v>
       </c>
       <c r="D748">
         <v>-1.450776960654412</v>
@@ -22758,7 +22758,7 @@
         <v>2026</v>
       </c>
       <c r="C749">
-        <v>0.7475807641013992</v>
+        <v>0</v>
       </c>
       <c r="D749">
         <v>-1.450873011486672</v>
@@ -22790,7 +22790,7 @@
         <v>2027</v>
       </c>
       <c r="C750">
-        <v>0.5947801572000219</v>
+        <v>0</v>
       </c>
       <c r="D750">
         <v>-1.447148491578876</v>
@@ -22822,7 +22822,7 @@
         <v>2028</v>
       </c>
       <c r="C751">
-        <v>0.5181608403950013</v>
+        <v>0</v>
       </c>
       <c r="D751">
         <v>-1.439244279545388</v>
@@ -22854,7 +22854,7 @@
         <v>2024</v>
       </c>
       <c r="C752">
-        <v>0.882923204090778</v>
+        <v>-0.882923204090778</v>
       </c>
       <c r="D752">
         <v>1.444221225066158</v>
@@ -22886,7 +22886,7 @@
         <v>2025</v>
       </c>
       <c r="C753">
-        <v>0.6540167934864166</v>
+        <v>-0.6540167934864166</v>
       </c>
       <c r="D753">
         <v>1.556253425434707</v>
@@ -22918,7 +22918,7 @@
         <v>2026</v>
       </c>
       <c r="C754">
-        <v>0.6245799111425768</v>
+        <v>-0.6245799111425768</v>
       </c>
       <c r="D754">
         <v>1.679520059395236</v>
@@ -22950,7 +22950,7 @@
         <v>2027</v>
       </c>
       <c r="C755">
-        <v>0.4210212434392014</v>
+        <v>-0.4210212434392014</v>
       </c>
       <c r="D755">
         <v>1.776555519247866</v>
@@ -22982,7 +22982,7 @@
         <v>2028</v>
       </c>
       <c r="C756">
-        <v>0.3644833061527196</v>
+        <v>-0.3644833061527196</v>
       </c>
       <c r="D756">
         <v>1.877011264324278</v>
@@ -23014,7 +23014,7 @@
         <v>2024</v>
       </c>
       <c r="C757">
-        <v>0.8390180237626772</v>
+        <v>-0.8390180237626772</v>
       </c>
       <c r="D757">
         <v>0.01349120968382101</v>
@@ -23046,7 +23046,7 @@
         <v>2025</v>
       </c>
       <c r="C758">
-        <v>0.9293276992611316</v>
+        <v>-0.9293276992611316</v>
       </c>
       <c r="D758">
         <v>-0.009333537470532449</v>
@@ -23078,7 +23078,7 @@
         <v>2026</v>
       </c>
       <c r="C759">
-        <v>0.851713325511172</v>
+        <v>-0.851713325511172</v>
       </c>
       <c r="D759">
         <v>-0.0120189515961208</v>
@@ -23110,7 +23110,7 @@
         <v>2027</v>
       </c>
       <c r="C760">
-        <v>0.858029881916793</v>
+        <v>-0.858029881916793</v>
       </c>
       <c r="D760">
         <v>-0.02338678076477821</v>
@@ -23131,7 +23131,7 @@
         <v>0.4872300442819717</v>
       </c>
       <c r="J760">
-        <v>4.470786359388932</v>
+        <v>4</v>
       </c>
     </row>
     <row r="761">
@@ -23142,7 +23142,7 @@
         <v>2028</v>
       </c>
       <c r="C761">
-        <v>0.7923538247663965</v>
+        <v>-0.7923538247663965</v>
       </c>
       <c r="D761">
         <v>-0.02780845319478295</v>
@@ -23163,7 +23163,7 @@
         <v>0.3282889667221583</v>
       </c>
       <c r="J761">
-        <v>5.217822973247359</v>
+        <v>4</v>
       </c>
     </row>
     <row r="762">
@@ -23334,7 +23334,7 @@
         <v>2024</v>
       </c>
       <c r="C767">
-        <v>1.817289396164992</v>
+        <v>0</v>
       </c>
       <c r="D767">
         <v>0.3141574653171796</v>
@@ -23363,7 +23363,7 @@
         <v>2025</v>
       </c>
       <c r="C768">
-        <v>1.629994106859673</v>
+        <v>0</v>
       </c>
       <c r="D768">
         <v>0.450171315928538</v>
@@ -23392,7 +23392,7 @@
         <v>2026</v>
       </c>
       <c r="C769">
-        <v>1.609798309378277</v>
+        <v>0</v>
       </c>
       <c r="D769">
         <v>0.5921354270941668</v>
@@ -23421,7 +23421,7 @@
         <v>2027</v>
       </c>
       <c r="C770">
-        <v>1.424792455395742</v>
+        <v>0</v>
       </c>
       <c r="D770">
         <v>0.716858102818656</v>
@@ -23450,7 +23450,7 @@
         <v>2028</v>
       </c>
       <c r="C771">
-        <v>1.338212701145973</v>
+        <v>0</v>
       </c>
       <c r="D771">
         <v>0.8415678494069807</v>
@@ -23479,7 +23479,7 @@
         <v>2024</v>
       </c>
       <c r="C772">
-        <v>0.5425545236021897</v>
+        <v>0</v>
       </c>
       <c r="D772">
         <v>0.4223227967739458</v>
@@ -23508,7 +23508,7 @@
         <v>2025</v>
       </c>
       <c r="C773">
-        <v>0.3492275746264552</v>
+        <v>0</v>
       </c>
       <c r="D773">
         <v>0.5617320760599022</v>
@@ -23537,7 +23537,7 @@
         <v>2026</v>
       </c>
       <c r="C774">
-        <v>0.3357585686457533</v>
+        <v>0</v>
       </c>
       <c r="D774">
         <v>0.7038684989739001</v>
@@ -23566,7 +23566,7 @@
         <v>2027</v>
       </c>
       <c r="C775">
-        <v>0.1688450304050501</v>
+        <v>0</v>
       </c>
       <c r="D775">
         <v>0.82725276144066</v>
@@ -23595,7 +23595,7 @@
         <v>2028</v>
       </c>
       <c r="C776">
-        <v>0.133060479366945</v>
+        <v>0</v>
       </c>
       <c r="D776">
         <v>0.9508267884108572</v>
@@ -23624,7 +23624,7 @@
         <v>2024</v>
       </c>
       <c r="C777">
-        <v>0.6877195658131302</v>
+        <v>0</v>
       </c>
       <c r="D777">
         <v>0.9512753162421654</v>
@@ -23656,7 +23656,7 @@
         <v>2025</v>
       </c>
       <c r="C778">
-        <v>0.4751599459257588</v>
+        <v>0</v>
       </c>
       <c r="D778">
         <v>1.086389708281206</v>
@@ -23688,7 +23688,7 @@
         <v>2026</v>
       </c>
       <c r="C779">
-        <v>0.4524605307251029</v>
+        <v>0</v>
       </c>
       <c r="D779">
         <v>1.22908311196761</v>
@@ -23720,7 +23720,7 @@
         <v>2027</v>
       </c>
       <c r="C780">
-        <v>0.2669213943618195</v>
+        <v>0</v>
       </c>
       <c r="D780">
         <v>1.348383306310506</v>
@@ -23752,7 +23752,7 @@
         <v>2028</v>
       </c>
       <c r="C781">
-        <v>0.2208884939511914</v>
+        <v>0</v>
       </c>
       <c r="D781">
         <v>1.469083080511609</v>
@@ -23784,7 +23784,7 @@
         <v>2024</v>
       </c>
       <c r="C782">
-        <v>1.107586065270424</v>
+        <v>0</v>
       </c>
       <c r="D782">
         <v>0.3704969270019656</v>
@@ -23816,7 +23816,7 @@
         <v>2025</v>
       </c>
       <c r="C783">
-        <v>0.8539914213853507</v>
+        <v>0</v>
       </c>
       <c r="D783">
         <v>0.547920847035184</v>
@@ -23848,7 +23848,7 @@
         <v>2026</v>
       </c>
       <c r="C784">
-        <v>0.8177992612851421</v>
+        <v>0</v>
       </c>
       <c r="D784">
         <v>0.7080348080135253</v>
@@ -23880,7 +23880,7 @@
         <v>2027</v>
       </c>
       <c r="C785">
-        <v>0.5893987767734753</v>
+        <v>0</v>
       </c>
       <c r="D785">
         <v>0.8378326038644661</v>
@@ -23912,7 +23912,7 @@
         <v>2028</v>
       </c>
       <c r="C786">
-        <v>0.5215763111466091</v>
+        <v>0</v>
       </c>
       <c r="D786">
         <v>0.9613856485664526</v>
@@ -23944,7 +23944,7 @@
         <v>2024</v>
       </c>
       <c r="C787">
-        <v>0.906926975223165</v>
+        <v>0</v>
       </c>
       <c r="D787">
         <v>-1.142701491886373</v>
@@ -23976,7 +23976,7 @@
         <v>2025</v>
       </c>
       <c r="C788">
-        <v>0.6729434462370421</v>
+        <v>0</v>
       </c>
       <c r="D788">
         <v>-1.231911518640652</v>
@@ -24008,7 +24008,7 @@
         <v>2026</v>
       </c>
       <c r="C789">
-        <v>0.6431996266562907</v>
+        <v>0</v>
       </c>
       <c r="D789">
         <v>-1.119349453799387</v>
@@ -24040,7 +24040,7 @@
         <v>2027</v>
       </c>
       <c r="C790">
-        <v>0.4352830786241266</v>
+        <v>0</v>
       </c>
       <c r="D790">
         <v>-1.144616803954746</v>
@@ -24072,7 +24072,7 @@
         <v>2028</v>
       </c>
       <c r="C791">
-        <v>0.377874100565432</v>
+        <v>0</v>
       </c>
       <c r="D791">
         <v>-1.070631030658494</v>
@@ -24264,7 +24264,7 @@
         <v>2024</v>
       </c>
       <c r="C797">
-        <v>-1.227816225965028</v>
+        <v>0</v>
       </c>
       <c r="D797">
         <v>-0.5535863984123454</v>
@@ -24293,7 +24293,7 @@
         <v>2025</v>
       </c>
       <c r="C798">
-        <v>-1.253163205031061</v>
+        <v>0</v>
       </c>
       <c r="D798">
         <v>-0.5532990911384129</v>
@@ -24322,7 +24322,7 @@
         <v>2026</v>
       </c>
       <c r="C799">
-        <v>-1.21430591869561</v>
+        <v>0</v>
       </c>
       <c r="D799">
         <v>-0.5453520297743478</v>
@@ -24351,7 +24351,7 @@
         <v>2027</v>
       </c>
       <c r="C800">
-        <v>-1.204300258610849</v>
+        <v>0</v>
       </c>
       <c r="D800">
         <v>-0.5392933627622125</v>
@@ -24380,7 +24380,7 @@
         <v>2028</v>
       </c>
       <c r="C801">
-        <v>-1.150924221559734</v>
+        <v>0</v>
       </c>
       <c r="D801">
         <v>-0.5290176197260795</v>
@@ -24409,7 +24409,7 @@
         <v>2024</v>
       </c>
       <c r="C802">
-        <v>1.95069146000323</v>
+        <v>0</v>
       </c>
       <c r="E802">
         <v>0.5394683700639552</v>
@@ -24438,7 +24438,7 @@
         <v>2025</v>
       </c>
       <c r="C803">
-        <v>1.614697238589296</v>
+        <v>0</v>
       </c>
       <c r="E803">
         <v>0.5838786659495941</v>
@@ -24467,7 +24467,7 @@
         <v>2026</v>
       </c>
       <c r="C804">
-        <v>1.551411155899236</v>
+        <v>0</v>
       </c>
       <c r="E804">
         <v>0.5243073374777409</v>
@@ -24496,7 +24496,7 @@
         <v>2027</v>
       </c>
       <c r="C805">
-        <v>1.236943777228024</v>
+        <v>0</v>
       </c>
       <c r="E805">
         <v>0.5188509454657591</v>
@@ -24525,7 +24525,7 @@
         <v>2028</v>
       </c>
       <c r="C806">
-        <v>1.125367114297694</v>
+        <v>0</v>
       </c>
       <c r="E806">
         <v>0.4691416941653833</v>
@@ -24554,7 +24554,7 @@
         <v>2024</v>
       </c>
       <c r="C807">
-        <v>-0.6561904576800697</v>
+        <v>0</v>
       </c>
       <c r="E807">
         <v>0.5274472846129896</v>
@@ -24580,7 +24580,7 @@
         <v>2025</v>
       </c>
       <c r="C808">
-        <v>-0.7374047233586606</v>
+        <v>0</v>
       </c>
       <c r="E808">
         <v>0.8527243535460514</v>
@@ -24606,7 +24606,7 @@
         <v>2026</v>
       </c>
       <c r="C809">
-        <v>-0.7169166807913013</v>
+        <v>0</v>
       </c>
       <c r="E809">
         <v>1.176865583612516</v>
@@ -24632,7 +24632,7 @@
         <v>2027</v>
       </c>
       <c r="C810">
-        <v>-0.7652647595587687</v>
+        <v>0</v>
       </c>
       <c r="E810">
         <v>1.487143888719148</v>
@@ -24658,7 +24658,7 @@
         <v>2028</v>
       </c>
       <c r="C811">
-        <v>-0.7415537197110784</v>
+        <v>0</v>
       </c>
       <c r="E811">
         <v>1.841444482638359</v>
@@ -25004,7 +25004,7 @@
         <v>2024</v>
       </c>
       <c r="C822">
-        <v>-0.04959545339310609</v>
+        <v>0</v>
       </c>
       <c r="D822">
         <v>-0.3913452010703789</v>
@@ -25033,7 +25033,7 @@
         <v>2025</v>
       </c>
       <c r="C823">
-        <v>-0.1247868918913532</v>
+        <v>0</v>
       </c>
       <c r="D823">
         <v>-0.3173476566270936</v>
@@ -25062,7 +25062,7 @@
         <v>2026</v>
       </c>
       <c r="C824">
-        <v>-0.1051124669687458</v>
+        <v>0</v>
       </c>
       <c r="D824">
         <v>-0.2439684540570585</v>
@@ -25091,7 +25091,7 @@
         <v>2027</v>
       </c>
       <c r="C825">
-        <v>-0.1596164742479744</v>
+        <v>0</v>
       </c>
       <c r="D825">
         <v>-0.1772752920793204</v>
@@ -25120,7 +25120,7 @@
         <v>2028</v>
       </c>
       <c r="C826">
-        <v>-0.1586849514072621</v>
+        <v>0</v>
       </c>
       <c r="D826">
         <v>-0.109206712435001</v>
@@ -25149,7 +25149,7 @@
         <v>2024</v>
       </c>
       <c r="C827">
-        <v>-0.06534447790426272</v>
+        <v>0</v>
       </c>
       <c r="D827">
         <v>-0.8198139078181854</v>
@@ -25181,7 +25181,7 @@
         <v>2025</v>
       </c>
       <c r="C828">
-        <v>-0.00541743471556736</v>
+        <v>0</v>
       </c>
       <c r="D828">
         <v>-0.8092429189202137</v>
@@ -25213,7 +25213,7 @@
         <v>2026</v>
       </c>
       <c r="C829">
-        <v>-0.01148254676401328</v>
+        <v>0</v>
       </c>
       <c r="D829">
         <v>-0.7986336366647639</v>
@@ -25245,7 +25245,7 @@
         <v>2027</v>
       </c>
       <c r="C830">
-        <v>0.01781490354759639</v>
+        <v>0</v>
       </c>
       <c r="D830">
         <v>-0.7866338770194716</v>
@@ -25277,7 +25277,7 @@
         <v>2028</v>
       </c>
       <c r="C831">
-        <v>0.0170723467048381</v>
+        <v>0</v>
       </c>
       <c r="D831">
         <v>-0.7714624570358697</v>
@@ -26239,7 +26239,7 @@
         <v>2024</v>
       </c>
       <c r="C862">
-        <v>0.1551733688584812</v>
+        <v>0</v>
       </c>
       <c r="D862">
         <v>-0.7853624361965128</v>
@@ -26271,7 +26271,7 @@
         <v>2025</v>
       </c>
       <c r="C863">
-        <v>0.2047564737112861</v>
+        <v>0</v>
       </c>
       <c r="D863">
         <v>-0.7554540414860199</v>
@@ -26303,7 +26303,7 @@
         <v>2026</v>
       </c>
       <c r="C864">
-        <v>0.2135697726464509</v>
+        <v>0</v>
       </c>
       <c r="D864">
         <v>-0.7231963701594578</v>
@@ -26335,7 +26335,7 @@
         <v>2027</v>
       </c>
       <c r="C865">
-        <v>0.2443404483053406</v>
+        <v>0</v>
       </c>
       <c r="D865">
         <v>-0.6918899157138843</v>
@@ -26367,7 +26367,7 @@
         <v>2028</v>
       </c>
       <c r="C866">
-        <v>0.2446948178713266</v>
+        <v>0</v>
       </c>
       <c r="D866">
         <v>-0.6581577758088019</v>
@@ -26529,7 +26529,7 @@
         <v>2024</v>
       </c>
       <c r="C872">
-        <v>0.1879411067867773</v>
+        <v>0</v>
       </c>
       <c r="D872">
         <v>-0.03732916226271165</v>
@@ -26558,7 +26558,7 @@
         <v>2025</v>
       </c>
       <c r="C873">
-        <v>0.2387782632329406</v>
+        <v>0</v>
       </c>
       <c r="D873">
         <v>-0.01957102246263595</v>
@@ -26587,7 +26587,7 @@
         <v>2026</v>
       </c>
       <c r="C874">
-        <v>0.2470495710366522</v>
+        <v>0</v>
       </c>
       <c r="D874">
         <v>0.00704399392685248</v>
@@ -26616,7 +26616,7 @@
         <v>2027</v>
       </c>
       <c r="C875">
-        <v>0.2777895382354741</v>
+        <v>0</v>
       </c>
       <c r="D875">
         <v>0.02634193332384955</v>
@@ -26645,7 +26645,7 @@
         <v>2028</v>
       </c>
       <c r="C876">
-        <v>0.2770951292565521</v>
+        <v>0</v>
       </c>
       <c r="D876">
         <v>0.05010706792441656</v>
@@ -26774,7 +26774,7 @@
         <v>2024</v>
       </c>
       <c r="C882">
-        <v>-1.143979312198322</v>
+        <v>0</v>
       </c>
       <c r="D882">
         <v>-1.067106293892442</v>
@@ -26803,7 +26803,7 @@
         <v>2025</v>
       </c>
       <c r="C883">
-        <v>-1.099041127632497</v>
+        <v>0</v>
       </c>
       <c r="D883">
         <v>-1.005343544384262</v>
@@ -26832,7 +26832,7 @@
         <v>2026</v>
       </c>
       <c r="C884">
-        <v>-1.066575451724269</v>
+        <v>0</v>
       </c>
       <c r="D884">
         <v>-0.9457679478272336</v>
@@ -26861,7 +26861,7 @@
         <v>2027</v>
       </c>
       <c r="C885">
-        <v>-1.007915221662091</v>
+        <v>0</v>
       </c>
       <c r="D885">
         <v>-0.8860677405084946</v>
@@ -26890,7 +26890,7 @@
         <v>2028</v>
       </c>
       <c r="C886">
-        <v>-0.9560120561365214</v>
+        <v>0</v>
       </c>
       <c r="D886">
         <v>-0.8261104449528573</v>
@@ -26919,7 +26919,7 @@
         <v>2024</v>
       </c>
       <c r="C887">
-        <v>0.4407598831899481</v>
+        <v>0</v>
       </c>
       <c r="D887">
         <v>-0.6603875345354218</v>
@@ -26951,7 +26951,7 @@
         <v>2025</v>
       </c>
       <c r="C888">
-        <v>0.4944151552615008</v>
+        <v>0</v>
       </c>
       <c r="D888">
         <v>-0.6995096321485671</v>
@@ -26983,7 +26983,7 @@
         <v>2026</v>
       </c>
       <c r="C889">
-        <v>0.4964750192543307</v>
+        <v>0</v>
       </c>
       <c r="D889">
         <v>-0.6739145363125293</v>
@@ -27015,7 +27015,7 @@
         <v>2027</v>
       </c>
       <c r="C890">
-        <v>0.5226092359534786</v>
+        <v>0</v>
       </c>
       <c r="D890">
         <v>-0.6712642096075543</v>
@@ -27047,7 +27047,7 @@
         <v>2028</v>
       </c>
       <c r="C891">
-        <v>0.5112838320387046</v>
+        <v>0</v>
       </c>
       <c r="D891">
         <v>-0.656460348704753</v>
@@ -27079,7 +27079,7 @@
         <v>2024</v>
       </c>
       <c r="C892">
-        <v>0.1608584638030726</v>
+        <v>0</v>
       </c>
       <c r="D892">
         <v>-0.4045903536202057</v>
@@ -27111,7 +27111,7 @@
         <v>2025</v>
       </c>
       <c r="C893">
-        <v>0.2075784444826418</v>
+        <v>0</v>
       </c>
       <c r="D893">
         <v>-0.3525281742634793</v>
@@ -27143,7 +27143,7 @@
         <v>2026</v>
       </c>
       <c r="C894">
-        <v>0.2153984451570439</v>
+        <v>0</v>
       </c>
       <c r="D894">
         <v>-0.2975098752435954</v>
@@ -27175,7 +27175,7 @@
         <v>2027</v>
       </c>
       <c r="C895">
-        <v>0.244208660313219</v>
+        <v>0</v>
       </c>
       <c r="D895">
         <v>-0.2481997557196633</v>
@@ -27207,7 +27207,7 @@
         <v>2028</v>
       </c>
       <c r="C896">
-        <v>0.2432520826732982</v>
+        <v>0</v>
       </c>
       <c r="D896">
         <v>-0.1966347229774465</v>
@@ -27239,7 +27239,7 @@
         <v>2024</v>
       </c>
       <c r="C897">
-        <v>0.7525082790361708</v>
+        <v>0</v>
       </c>
       <c r="D897">
         <v>-0.4350972333659803</v>
@@ -27271,7 +27271,7 @@
         <v>2025</v>
       </c>
       <c r="C898">
-        <v>0.6331354165287231</v>
+        <v>0</v>
       </c>
       <c r="D898">
         <v>-0.4288419558347143</v>
@@ -27303,7 +27303,7 @@
         <v>2026</v>
       </c>
       <c r="C899">
-        <v>0.6002084008614618</v>
+        <v>0</v>
       </c>
       <c r="D899">
         <v>-0.418888049423145</v>
@@ -27335,7 +27335,7 @@
         <v>2027</v>
       </c>
       <c r="C900">
-        <v>0.5214778726173053</v>
+        <v>0</v>
       </c>
       <c r="D900">
         <v>-0.4112311069529556</v>
@@ -27367,7 +27367,7 @@
         <v>2028</v>
       </c>
       <c r="C901">
-        <v>0.4535047681305281</v>
+        <v>0</v>
       </c>
       <c r="D901">
         <v>-0.3993540092481284</v>
@@ -27559,7 +27559,7 @@
         <v>2024</v>
       </c>
       <c r="C907">
-        <v>-0.6235787792044869</v>
+        <v>0</v>
       </c>
       <c r="D907">
         <v>0.5000836644926843</v>
@@ -27591,7 +27591,7 @@
         <v>2025</v>
       </c>
       <c r="C908">
-        <v>-0.6624819370883296</v>
+        <v>0</v>
       </c>
       <c r="D908">
         <v>0.4710010560129965</v>
@@ -27623,7 +27623,7 @@
         <v>2026</v>
       </c>
       <c r="C909">
-        <v>-0.6467661533277083</v>
+        <v>0</v>
       </c>
       <c r="D909">
         <v>0.4526537954769251</v>
@@ -27655,7 +27655,7 @@
         <v>2027</v>
       </c>
       <c r="C910">
-        <v>-0.6465882565120803</v>
+        <v>0</v>
       </c>
       <c r="D910">
         <v>0.425760411896048</v>
@@ -27687,7 +27687,7 @@
         <v>2028</v>
       </c>
       <c r="C911">
-        <v>-0.6330634557454891</v>
+        <v>0</v>
       </c>
       <c r="D911">
         <v>0.4065524567038228</v>
@@ -28039,7 +28039,7 @@
         <v>2024</v>
       </c>
       <c r="C922">
-        <v>-0.5463924667890848</v>
+        <v>0</v>
       </c>
       <c r="D922">
         <v>1.469514582230066</v>
@@ -28068,7 +28068,7 @@
         <v>2025</v>
       </c>
       <c r="C923">
-        <v>-0.5898092766234501</v>
+        <v>0</v>
       </c>
       <c r="D923">
         <v>1.422994056329077</v>
@@ -28097,7 +28097,7 @@
         <v>2026</v>
       </c>
       <c r="C924">
-        <v>-0.5768219155305901</v>
+        <v>0</v>
       </c>
       <c r="D924">
         <v>1.424736641458906</v>
@@ -28126,7 +28126,7 @@
         <v>2027</v>
       </c>
       <c r="C925">
-        <v>-0.5810700907114092</v>
+        <v>0</v>
       </c>
       <c r="D925">
         <v>1.3945134943344</v>
@@ -28155,7 +28155,7 @@
         <v>2028</v>
       </c>
       <c r="C926">
-        <v>-0.5721165981722727</v>
+        <v>0</v>
       </c>
       <c r="D926">
         <v>1.380192841510139</v>
@@ -28184,7 +28184,7 @@
         <v>2024</v>
       </c>
       <c r="C927">
-        <v>0.4138056202293615</v>
+        <v>0</v>
       </c>
       <c r="D927">
         <v>0.6835432526462194</v>
@@ -28213,7 +28213,7 @@
         <v>2025</v>
       </c>
       <c r="C928">
-        <v>0.3140794128127129</v>
+        <v>0</v>
       </c>
       <c r="D928">
         <v>0.6599945953369699</v>
@@ -28242,7 +28242,7 @@
         <v>2026</v>
       </c>
       <c r="C929">
-        <v>0.2931477319656372</v>
+        <v>0</v>
       </c>
       <c r="D929">
         <v>0.6524523593898051</v>
@@ -28271,7 +28271,7 @@
         <v>2027</v>
       </c>
       <c r="C930">
-        <v>0.2336754417925478</v>
+        <v>0</v>
       </c>
       <c r="D930">
         <v>0.6350438616423655</v>
@@ -28300,7 +28300,7 @@
         <v>2028</v>
       </c>
       <c r="C931">
-        <v>0.185767422035441</v>
+        <v>0</v>
       </c>
       <c r="D931">
         <v>0.6254092169974089</v>
@@ -28329,7 +28329,7 @@
         <v>2024</v>
       </c>
       <c r="C932">
-        <v>0.17417520419243</v>
+        <v>0</v>
       </c>
       <c r="D932">
         <v>0.1740013978885345</v>
@@ -28358,7 +28358,7 @@
         <v>2025</v>
       </c>
       <c r="C933">
-        <v>0.08605497669703348</v>
+        <v>0</v>
       </c>
       <c r="D933">
         <v>0.2163362033410842</v>
@@ -28387,7 +28387,7 @@
         <v>2026</v>
       </c>
       <c r="C934">
-        <v>0.07404080494806171</v>
+        <v>0</v>
       </c>
       <c r="D934">
         <v>0.271406922949818</v>
@@ -28416,7 +28416,7 @@
         <v>2027</v>
       </c>
       <c r="C935">
-        <v>0.02651408223061518</v>
+        <v>0</v>
       </c>
       <c r="D935">
         <v>0.3144323519840385</v>
@@ -28445,7 +28445,7 @@
         <v>2028</v>
       </c>
       <c r="C936">
-        <v>-0.00714092469393985</v>
+        <v>0</v>
       </c>
       <c r="D936">
         <v>0.3614100540938951</v>
@@ -28474,7 +28474,7 @@
         <v>2024</v>
       </c>
       <c r="C937">
-        <v>-0.2099083995611342</v>
+        <v>0</v>
       </c>
       <c r="D937">
         <v>-1.087411491590306</v>
@@ -28506,7 +28506,7 @@
         <v>2025</v>
       </c>
       <c r="C938">
-        <v>-0.2730018896940761</v>
+        <v>0</v>
       </c>
       <c r="D938">
         <v>-1.070283652294323</v>
@@ -28538,7 +28538,7 @@
         <v>2026</v>
       </c>
       <c r="C939">
-        <v>-0.2719087574726487</v>
+        <v>0</v>
       </c>
       <c r="D939">
         <v>-1.060953556130646</v>
@@ -28570,7 +28570,7 @@
         <v>2027</v>
       </c>
       <c r="C940">
-        <v>-0.2954518281365019</v>
+        <v>0</v>
       </c>
       <c r="D940">
         <v>-1.045837031973423</v>
@@ -28602,7 +28602,7 @@
         <v>2028</v>
       </c>
       <c r="C941">
-        <v>-0.3064263864215854</v>
+        <v>0</v>
       </c>
       <c r="D941">
         <v>-1.028883565839573</v>
@@ -28634,7 +28634,7 @@
         <v>2024</v>
       </c>
       <c r="C942">
-        <v>0.4015298242731776</v>
+        <v>0</v>
       </c>
       <c r="D942">
         <v>-0.4620634272729991</v>
@@ -28660,7 +28660,7 @@
         <v>2025</v>
       </c>
       <c r="C943">
-        <v>0.5841346395314624</v>
+        <v>0</v>
       </c>
       <c r="D943">
         <v>-0.5595232363633356</v>
@@ -28686,7 +28686,7 @@
         <v>2026</v>
       </c>
       <c r="C944">
-        <v>0.6833532124708698</v>
+        <v>0</v>
       </c>
       <c r="D944">
         <v>-0.5986234721223921</v>
@@ -28712,7 +28712,7 @@
         <v>2027</v>
       </c>
       <c r="C945">
-        <v>0.8450456255067512</v>
+        <v>0</v>
       </c>
       <c r="D945">
         <v>-0.6539513864882285</v>
@@ -28738,7 +28738,7 @@
         <v>2028</v>
       </c>
       <c r="C946">
-        <v>0.9351924264107192</v>
+        <v>0</v>
       </c>
       <c r="D946">
         <v>-0.6956389892263578</v>
@@ -28764,7 +28764,7 @@
         <v>2024</v>
       </c>
       <c r="C947">
-        <v>1.891787810807942</v>
+        <v>0</v>
       </c>
       <c r="D947">
         <v>-0.9425557938887792</v>
@@ -28796,7 +28796,7 @@
         <v>2025</v>
       </c>
       <c r="C948">
-        <v>1.589070749908635</v>
+        <v>0</v>
       </c>
       <c r="D948">
         <v>-0.8365367092835709</v>
@@ -28828,7 +28828,7 @@
         <v>2026</v>
       </c>
       <c r="C949">
-        <v>1.566230843139149</v>
+        <v>0</v>
       </c>
       <c r="D949">
         <v>-0.9089783053888651</v>
@@ -28860,7 +28860,7 @@
         <v>2027</v>
       </c>
       <c r="C950">
-        <v>1.297716502483796</v>
+        <v>0</v>
       </c>
       <c r="D950">
         <v>-0.8066831830320245</v>
@@ -28892,7 +28892,7 @@
         <v>2028</v>
       </c>
       <c r="C951">
-        <v>1.203722769043853</v>
+        <v>0</v>
       </c>
       <c r="D951">
         <v>-0.8686666507121558</v>
@@ -28924,7 +28924,7 @@
         <v>2024</v>
       </c>
       <c r="C952">
-        <v>0.1873581595232357</v>
+        <v>-0.1873581595232357</v>
       </c>
       <c r="D952">
         <v>0.05859610092734954</v>
@@ -28953,7 +28953,7 @@
         <v>2025</v>
       </c>
       <c r="C953">
-        <v>0.2792648456167483</v>
+        <v>-0.2792648456167483</v>
       </c>
       <c r="D953">
         <v>0.01934962346744844</v>
@@ -28982,7 +28982,7 @@
         <v>2026</v>
       </c>
       <c r="C954">
-        <v>0.3529961176626262</v>
+        <v>-0.3529961176626262</v>
       </c>
       <c r="D954">
         <v>-0.01417966528106475</v>
@@ -29011,13 +29011,13 @@
         <v>2027</v>
       </c>
       <c r="C955">
-        <v>0.4459664554887386</v>
+        <v>-0.4459664554887386</v>
       </c>
       <c r="D955">
         <v>-0.05093685701056905</v>
       </c>
       <c r="E955">
-        <v>4.116400315756557</v>
+        <v>4</v>
       </c>
       <c r="F955">
         <v>0.5020574125965167</v>
@@ -29040,7 +29040,7 @@
         <v>2028</v>
       </c>
       <c r="C956">
-        <v>0.4986975743819047</v>
+        <v>-0.4986975743819047</v>
       </c>
       <c r="D956">
         <v>-0.08043843679814125</v>
@@ -29069,7 +29069,7 @@
         <v>2024</v>
       </c>
       <c r="C957">
-        <v>-0.347988903408719</v>
+        <v>0.347988903408719</v>
       </c>
       <c r="D957">
         <v>0.4818358922794729</v>
@@ -29092,7 +29092,7 @@
         <v>2025</v>
       </c>
       <c r="C958">
-        <v>-0.2169241374921583</v>
+        <v>0.2169241374921583</v>
       </c>
       <c r="D958">
         <v>0.9293441827406032</v>
@@ -29115,7 +29115,7 @@
         <v>2026</v>
       </c>
       <c r="C959">
-        <v>-0.1318718767400695</v>
+        <v>0.1318718767400695</v>
       </c>
       <c r="D959">
         <v>0.5126162597669773</v>
@@ -29138,7 +29138,7 @@
         <v>2027</v>
       </c>
       <c r="C960">
-        <v>-0.00189529395708948</v>
+        <v>0.00189529395708948</v>
       </c>
       <c r="D960">
         <v>0.9175211157243728</v>
@@ -29161,7 +29161,7 @@
         <v>2028</v>
       </c>
       <c r="C961">
-        <v>0.08618458946754766</v>
+        <v>-0.08618458946754766</v>
       </c>
       <c r="D961">
         <v>0.5360007089696887</v>
@@ -29184,7 +29184,7 @@
         <v>2024</v>
       </c>
       <c r="C962">
-        <v>0.6924435262791415</v>
+        <v>0</v>
       </c>
       <c r="D962">
         <v>-1.36029094971028</v>
@@ -29216,7 +29216,7 @@
         <v>2025</v>
       </c>
       <c r="C963">
-        <v>0.765526897033493</v>
+        <v>0</v>
       </c>
       <c r="D963">
         <v>-1.378636699432439</v>
@@ -29248,7 +29248,7 @@
         <v>2026</v>
       </c>
       <c r="C964">
-        <v>0.7316003435761802</v>
+        <v>0</v>
       </c>
       <c r="D964">
         <v>-1.411131187152202</v>
@@ -29280,7 +29280,7 @@
         <v>2027</v>
       </c>
       <c r="C965">
-        <v>0.7440425409288752</v>
+        <v>0</v>
       </c>
       <c r="D965">
         <v>-1.430743459011706</v>
@@ -29312,7 +29312,7 @@
         <v>2028</v>
       </c>
       <c r="C966">
-        <v>0.7065159226322</v>
+        <v>0</v>
       </c>
       <c r="D966">
         <v>-1.447946872547353</v>
@@ -29344,7 +29344,7 @@
         <v>2024</v>
       </c>
       <c r="C967">
-        <v>-0.2570137915636114</v>
+        <v>0</v>
       </c>
       <c r="D967">
         <v>-0.1860047718614726</v>
@@ -29367,7 +29367,7 @@
         <v>2025</v>
       </c>
       <c r="C968">
-        <v>-0.2956685033368722</v>
+        <v>0</v>
       </c>
       <c r="D968">
         <v>-0.185548396561824</v>
@@ -29390,7 +29390,7 @@
         <v>2026</v>
       </c>
       <c r="C969">
-        <v>-0.3206108263425704</v>
+        <v>0</v>
       </c>
       <c r="D969">
         <v>-0.02052645251381068</v>
@@ -29413,7 +29413,7 @@
         <v>2027</v>
       </c>
       <c r="C970">
-        <v>-0.3460726630780928</v>
+        <v>0</v>
       </c>
       <c r="D970">
         <v>-0.01733243080156201</v>
@@ -29436,7 +29436,7 @@
         <v>2028</v>
       </c>
       <c r="C971">
-        <v>-0.3659772133533875</v>
+        <v>0</v>
       </c>
       <c r="D971">
         <v>0.1299983312543951</v>
@@ -29459,7 +29459,7 @@
         <v>2024</v>
       </c>
       <c r="C972">
-        <v>0.6106169043163243</v>
+        <v>-0.6106169043163243</v>
       </c>
       <c r="D972">
         <v>-1.321338892694069</v>
@@ -29485,7 +29485,7 @@
         <v>2025</v>
       </c>
       <c r="C973">
-        <v>0.6827682339906906</v>
+        <v>-0.6827682339906906</v>
       </c>
       <c r="D973">
         <v>-1.208493398535326</v>
@@ -29511,7 +29511,7 @@
         <v>2026</v>
       </c>
       <c r="C974">
-        <v>0.6520027176871223</v>
+        <v>-0.6520027176871223</v>
       </c>
       <c r="D974">
         <v>-1.279412638411549</v>
@@ -29537,7 +29537,7 @@
         <v>2027</v>
       </c>
       <c r="C975">
-        <v>0.6666016708893753</v>
+        <v>-0.6666016708893753</v>
       </c>
       <c r="D975">
         <v>-1.185880194643074</v>
@@ -29563,7 +29563,7 @@
         <v>2028</v>
       </c>
       <c r="C976">
-        <v>0.633223619605553</v>
+        <v>-0.633223619605553</v>
       </c>
       <c r="D976">
         <v>-1.229739391869177</v>
@@ -29589,7 +29589,7 @@
         <v>2024</v>
       </c>
       <c r="C977">
-        <v>-1.648317054559669</v>
+        <v>0</v>
       </c>
       <c r="D977">
         <v>-0.7294883644189052</v>
@@ -29615,7 +29615,7 @@
         <v>2025</v>
       </c>
       <c r="C978">
-        <v>-1.624501470565536</v>
+        <v>0</v>
       </c>
       <c r="D978">
         <v>-0.7325915458047202</v>
@@ -29641,7 +29641,7 @@
         <v>2026</v>
       </c>
       <c r="C979">
-        <v>-1.57475274674914</v>
+        <v>0</v>
       </c>
       <c r="D979">
         <v>-0.7781116999262307</v>
@@ -29667,7 +29667,7 @@
         <v>2027</v>
       </c>
       <c r="C980">
-        <v>-1.515718103816426</v>
+        <v>0</v>
       </c>
       <c r="D980">
         <v>-0.8042323233087398</v>
@@ -29693,7 +29693,7 @@
         <v>2028</v>
       </c>
       <c r="C981">
-        <v>-1.442293750919973</v>
+        <v>0</v>
       </c>
       <c r="D981">
         <v>-0.8305738702400799</v>
@@ -29719,7 +29719,7 @@
         <v>2024</v>
       </c>
       <c r="C982">
-        <v>-0.6319787978641088</v>
+        <v>0.6319787978641088</v>
       </c>
       <c r="D982">
         <v>-0.04569245950944486</v>
@@ -29748,7 +29748,7 @@
         <v>2025</v>
       </c>
       <c r="C983">
-        <v>-0.5822988702296853</v>
+        <v>0.5822988702296853</v>
       </c>
       <c r="D983">
         <v>-0.471104083195453</v>
@@ -29777,7 +29777,7 @@
         <v>2026</v>
       </c>
       <c r="C984">
-        <v>-0.5676585400957443</v>
+        <v>0.5676585400957443</v>
       </c>
       <c r="D984">
         <v>-0.2799047154763219</v>
@@ -29806,7 +29806,7 @@
         <v>2027</v>
       </c>
       <c r="C985">
-        <v>-0.5260398202677689</v>
+        <v>0.5260398202677689</v>
       </c>
       <c r="D985">
         <v>-0.6261967949388783</v>
@@ -29835,7 +29835,7 @@
         <v>2028</v>
       </c>
       <c r="C986">
-        <v>-0.4994252127410435</v>
+        <v>0.4994252127410435</v>
       </c>
       <c r="D986">
         <v>-0.4825962005353345</v>
@@ -29864,7 +29864,7 @@
         <v>2024</v>
       </c>
       <c r="C987">
-        <v>-0.03867933505885024</v>
+        <v>0</v>
       </c>
       <c r="E987">
         <v>2.208099196245366</v>
@@ -29884,7 +29884,7 @@
         <v>2025</v>
       </c>
       <c r="C988">
-        <v>0.02172993113696774</v>
+        <v>0</v>
       </c>
       <c r="E988">
         <v>2.185387337650096</v>
@@ -29904,7 +29904,7 @@
         <v>2026</v>
       </c>
       <c r="C989">
-        <v>0.01469044359448533</v>
+        <v>0</v>
       </c>
       <c r="E989">
         <v>2.074912082530358</v>
@@ -29924,7 +29924,7 @@
         <v>2027</v>
       </c>
       <c r="C990">
-        <v>0.04340807335314993</v>
+        <v>0</v>
       </c>
       <c r="E990">
         <v>1.946415843723596</v>
@@ -29944,7 +29944,7 @@
         <v>2028</v>
       </c>
       <c r="C991">
-        <v>0.04137812030628276</v>
+        <v>0</v>
       </c>
       <c r="E991">
         <v>1.845344668507536</v>
@@ -29964,7 +29964,7 @@
         <v>2024</v>
       </c>
       <c r="C992">
-        <v>1.002594513307267</v>
+        <v>-1.002594513307267</v>
       </c>
       <c r="D992">
         <v>-0.4423092999136606</v>
@@ -29990,7 +29990,7 @@
         <v>2025</v>
       </c>
       <c r="C993">
-        <v>1.081834526510447</v>
+        <v>-1.081834526510447</v>
       </c>
       <c r="D993">
         <v>-0.3765457828498567</v>
@@ -30016,7 +30016,7 @@
         <v>2026</v>
       </c>
       <c r="C994">
-        <v>1.036745696632096</v>
+        <v>-1.036745696632096</v>
       </c>
       <c r="D994">
         <v>-0.2901925703024903</v>
@@ -30042,7 +30042,7 @@
         <v>2027</v>
       </c>
       <c r="C995">
-        <v>1.042821293114601</v>
+        <v>-1.042821293114601</v>
       </c>
       <c r="D995">
         <v>-0.2271191280231026</v>
@@ -30068,7 +30068,7 @@
         <v>2028</v>
       </c>
       <c r="C996">
-        <v>0.990518522134029</v>
+        <v>-0.990518522134029</v>
       </c>
       <c r="D996">
         <v>-0.1489481508104891</v>
@@ -30094,7 +30094,7 @@
         <v>2024</v>
       </c>
       <c r="C997">
-        <v>0.7900951526349727</v>
+        <v>-0.7900951526349727</v>
       </c>
       <c r="D997">
         <v>0.01725523134293314</v>
@@ -30120,7 +30120,7 @@
         <v>2025</v>
       </c>
       <c r="C998">
-        <v>1.016279505126859</v>
+        <v>-1.016279505126859</v>
       </c>
       <c r="D998">
         <v>-0.00655505324991906</v>
@@ -30146,7 +30146,7 @@
         <v>2026</v>
       </c>
       <c r="C999">
-        <v>1.073855291324046</v>
+        <v>-1.073855291324046</v>
       </c>
       <c r="D999">
         <v>-0.044852208598609</v>
@@ -30172,7 +30172,7 @@
         <v>2027</v>
       </c>
       <c r="C1000">
-        <v>1.22241334091692</v>
+        <v>-1.22241334091692</v>
       </c>
       <c r="D1000">
         <v>-0.07589080204126605</v>
@@ -30198,7 +30198,7 @@
         <v>2028</v>
       </c>
       <c r="C1001">
-        <v>1.278151508429518</v>
+        <v>-1.278151508429518</v>
       </c>
       <c r="D1001">
         <v>-0.1048639185848495</v>
@@ -30224,7 +30224,7 @@
         <v>2024</v>
       </c>
       <c r="C1002">
-        <v>-0.7116834860065813</v>
+        <v>0.7116834860065813</v>
       </c>
       <c r="E1002">
         <v>-1.305488652956226</v>
@@ -30244,7 +30244,7 @@
         <v>2025</v>
       </c>
       <c r="C1003">
-        <v>-0.6006784671510912</v>
+        <v>0.6006784671510912</v>
       </c>
       <c r="E1003">
         <v>-1.287354899423193</v>
@@ -30264,7 +30264,7 @@
         <v>2026</v>
       </c>
       <c r="C1004">
-        <v>-0.5436230025525917</v>
+        <v>0.5436230025525917</v>
       </c>
       <c r="E1004">
         <v>-1.244865188409868</v>
@@ -30284,7 +30284,7 @@
         <v>2027</v>
       </c>
       <c r="C1005">
-        <v>-0.4428849863459186</v>
+        <v>0.4428849863459186</v>
       </c>
       <c r="E1005">
         <v>-1.184136473856567</v>
@@ -30304,7 +30304,7 @@
         <v>2028</v>
       </c>
       <c r="C1006">
-        <v>-0.3717199976789783</v>
+        <v>0.3717199976789783</v>
       </c>
       <c r="E1006">
         <v>-1.136080985314011</v>
@@ -30324,7 +30324,7 @@
         <v>2024</v>
       </c>
       <c r="C1007">
-        <v>1.507924247493933</v>
+        <v>-1.507924247493933</v>
       </c>
       <c r="D1007">
         <v>0.02499861988366305</v>
@@ -30350,7 +30350,7 @@
         <v>2025</v>
       </c>
       <c r="C1008">
-        <v>1.787451709918128</v>
+        <v>-1.787451709918128</v>
       </c>
       <c r="D1008">
         <v>0.0001541535325721845</v>
@@ -30376,7 +30376,7 @@
         <v>2026</v>
       </c>
       <c r="C1009">
-        <v>1.844464200496642</v>
+        <v>-1.844464200496642</v>
       </c>
       <c r="D1009">
         <v>-0.1079912291443827</v>
@@ -30402,7 +30402,7 @@
         <v>2027</v>
       </c>
       <c r="C1010">
-        <v>2.014538131755292</v>
+        <v>-2.014538131755292</v>
       </c>
       <c r="D1010">
         <v>-0.171560244004485</v>
@@ -30428,7 +30428,7 @@
         <v>2028</v>
       </c>
       <c r="C1011">
-        <v>2.061863406616036</v>
+        <v>-2.061863406616036</v>
       </c>
       <c r="D1011">
         <v>-0.247598377587412</v>
@@ -30454,7 +30454,7 @@
         <v>2024</v>
       </c>
       <c r="C1012">
-        <v>-0.1863887764394666</v>
+        <v>0</v>
       </c>
       <c r="D1012">
         <v>-0.4762701748786656</v>
@@ -30483,7 +30483,7 @@
         <v>2025</v>
       </c>
       <c r="C1013">
-        <v>-0.23279796230598</v>
+        <v>0</v>
       </c>
       <c r="D1013">
         <v>-0.4241867062183665</v>
@@ -30512,7 +30512,7 @@
         <v>2026</v>
       </c>
       <c r="C1014">
-        <v>-0.1938531899429282</v>
+        <v>0</v>
       </c>
       <c r="D1014">
         <v>-0.3765400092629211</v>
@@ -30541,7 +30541,7 @@
         <v>2027</v>
       </c>
       <c r="C1015">
-        <v>-0.1977221003393296</v>
+        <v>0</v>
       </c>
       <c r="D1015">
         <v>-0.3300686802792954</v>
@@ -30570,7 +30570,7 @@
         <v>2028</v>
       </c>
       <c r="C1016">
-        <v>-0.1844782282647125</v>
+        <v>0</v>
       </c>
       <c r="D1016">
         <v>-0.2831572594448054</v>
@@ -30599,7 +30599,7 @@
         <v>2024</v>
       </c>
       <c r="C1017">
-        <v>-0.7563224094460862</v>
+        <v>0</v>
       </c>
       <c r="E1017">
         <v>0.2052862827213146</v>
@@ -30622,7 +30622,7 @@
         <v>2025</v>
       </c>
       <c r="C1018">
-        <v>-0.8051035868483559</v>
+        <v>0</v>
       </c>
       <c r="E1018">
         <v>0.03196023793836717</v>
@@ -30645,7 +30645,7 @@
         <v>2026</v>
       </c>
       <c r="C1019">
-        <v>-0.6831358160856696</v>
+        <v>0</v>
       </c>
       <c r="E1019">
         <v>-0.0201974066016627</v>
@@ -30668,7 +30668,7 @@
         <v>2027</v>
       </c>
       <c r="C1020">
-        <v>-0.6638753353292348</v>
+        <v>0</v>
       </c>
       <c r="E1020">
         <v>-0.1330666682944069</v>
@@ -30691,7 +30691,7 @@
         <v>2028</v>
       </c>
       <c r="C1021">
-        <v>-0.57660503241775</v>
+        <v>0</v>
       </c>
       <c r="E1021">
         <v>-0.1834979045892006</v>
@@ -30714,7 +30714,7 @@
         <v>2024</v>
       </c>
       <c r="C1022">
-        <v>-0.5152257145239262</v>
+        <v>0</v>
       </c>
       <c r="E1022">
         <v>0.9376673113955644</v>
@@ -30740,7 +30740,7 @@
         <v>2025</v>
       </c>
       <c r="C1023">
-        <v>-0.5731644303139416</v>
+        <v>0</v>
       </c>
       <c r="E1023">
         <v>0.4104009010396054</v>
@@ -30766,7 +30766,7 @@
         <v>2026</v>
       </c>
       <c r="C1024">
-        <v>-0.529308795309548</v>
+        <v>0</v>
       </c>
       <c r="E1024">
         <v>0.6592706852460485</v>
@@ -30792,7 +30792,7 @@
         <v>2027</v>
       </c>
       <c r="C1025">
-        <v>-0.5269987033030671</v>
+        <v>0</v>
       </c>
       <c r="E1025">
         <v>0.2407311329237413</v>
@@ -30818,7 +30818,7 @@
         <v>2028</v>
       </c>
       <c r="C1026">
-        <v>-0.5034142547090361</v>
+        <v>0</v>
       </c>
       <c r="E1026">
         <v>0.4064477891485197</v>
@@ -30844,7 +30844,7 @@
         <v>2024</v>
       </c>
       <c r="C1027">
-        <v>-0.4289972442153051</v>
+        <v>0</v>
       </c>
       <c r="D1027">
         <v>-0.5864903720349458</v>
@@ -30873,7 +30873,7 @@
         <v>2025</v>
       </c>
       <c r="C1028">
-        <v>-0.4911649032381625</v>
+        <v>0</v>
       </c>
       <c r="D1028">
         <v>-0.5219814716354337</v>
@@ -30902,7 +30902,7 @@
         <v>2026</v>
       </c>
       <c r="C1029">
-        <v>-0.3372684451766297</v>
+        <v>0</v>
       </c>
       <c r="D1029">
         <v>-0.4836776862124075</v>
@@ -30931,7 +30931,7 @@
         <v>2027</v>
       </c>
       <c r="C1030">
-        <v>-0.3179875111353463</v>
+        <v>0</v>
       </c>
       <c r="D1030">
         <v>-0.4366333600506017</v>
@@ -30960,7 +30960,7 @@
         <v>2028</v>
       </c>
       <c r="C1031">
-        <v>-0.2195564429520766</v>
+        <v>0</v>
       </c>
       <c r="D1031">
         <v>-0.3928383323349337</v>
@@ -30989,7 +30989,7 @@
         <v>2024</v>
       </c>
       <c r="C1032">
-        <v>-1.772462613610498</v>
+        <v>0</v>
       </c>
       <c r="D1032">
         <v>-0.8496328742425872</v>
@@ -31021,7 +31021,7 @@
         <v>2025</v>
       </c>
       <c r="C1033">
-        <v>-1.744578740842634</v>
+        <v>0</v>
       </c>
       <c r="D1033">
         <v>-0.8468967606872385</v>
@@ -31053,7 +31053,7 @@
         <v>2026</v>
       </c>
       <c r="C1034">
-        <v>-1.688219405224044</v>
+        <v>0</v>
       </c>
       <c r="D1034">
         <v>-0.8390922225964992</v>
@@ -31085,7 +31085,7 @@
         <v>2027</v>
       </c>
       <c r="C1035">
-        <v>-1.622613795697692</v>
+        <v>0</v>
       </c>
       <c r="D1035">
         <v>-0.8311237468745793</v>
@@ -31117,7 +31117,7 @@
         <v>2028</v>
       </c>
       <c r="C1036">
-        <v>-1.540973088981241</v>
+        <v>0</v>
       </c>
       <c r="D1036">
         <v>-0.819208622917556</v>
@@ -31149,7 +31149,7 @@
         <v>2024</v>
       </c>
       <c r="C1037">
-        <v>-0.8612436807718277</v>
+        <v>0.8612436807718277</v>
       </c>
       <c r="D1037">
         <v>-0.7029484453069008</v>
@@ -31178,7 +31178,7 @@
         <v>2025</v>
       </c>
       <c r="C1038">
-        <v>-0.8944603712913961</v>
+        <v>0.8944603712913961</v>
       </c>
       <c r="D1038">
         <v>-0.7139305806226023</v>
@@ -31207,7 +31207,7 @@
         <v>2026</v>
       </c>
       <c r="C1039">
-        <v>-0.7860822809069025</v>
+        <v>0.7860822809069025</v>
       </c>
       <c r="D1039">
         <v>-0.7195708335278177</v>
@@ -31236,7 +31236,7 @@
         <v>2027</v>
       </c>
       <c r="C1040">
-        <v>-0.7540700278965825</v>
+        <v>0.7540700278965825</v>
       </c>
       <c r="D1040">
         <v>-0.7246643155387806</v>
@@ -31265,7 +31265,7 @@
         <v>2028</v>
       </c>
       <c r="C1041">
-        <v>-0.6721840496043148</v>
+        <v>0.6721840496043148</v>
       </c>
       <c r="D1041">
         <v>-0.7252869160879226</v>
@@ -31294,7 +31294,7 @@
         <v>2024</v>
       </c>
       <c r="C1042">
-        <v>-0.772837851761814</v>
+        <v>0</v>
       </c>
       <c r="D1042">
         <v>-0.9751524794496892</v>
@@ -31323,7 +31323,7 @@
         <v>2025</v>
       </c>
       <c r="C1043">
-        <v>-0.8128749426460073</v>
+        <v>0</v>
       </c>
       <c r="D1043">
         <v>-0.9592294967653746</v>
@@ -31352,7 +31352,7 @@
         <v>2026</v>
       </c>
       <c r="C1044">
-        <v>-0.7664241665704529</v>
+        <v>0</v>
       </c>
       <c r="D1044">
         <v>-1.009250275395835</v>
@@ -31381,7 +31381,7 @@
         <v>2027</v>
       </c>
       <c r="C1045">
-        <v>-0.7508026511489564</v>
+        <v>0</v>
       </c>
       <c r="D1045">
         <v>-1.018217759646805</v>
@@ -31410,7 +31410,7 @@
         <v>2028</v>
       </c>
       <c r="C1046">
-        <v>-0.7152920177605595</v>
+        <v>0</v>
       </c>
       <c r="D1046">
         <v>-1.04189304983587</v>
@@ -31439,7 +31439,7 @@
         <v>2024</v>
       </c>
       <c r="C1047">
-        <v>-0.2406445961955461</v>
+        <v>0</v>
       </c>
       <c r="D1047">
         <v>-0.7232818187933751</v>
@@ -31468,7 +31468,7 @@
         <v>2025</v>
       </c>
       <c r="C1048">
-        <v>-0.3170009468918479</v>
+        <v>0</v>
       </c>
       <c r="D1048">
         <v>-0.7385073716300573</v>
@@ -31497,7 +31497,7 @@
         <v>2026</v>
       </c>
       <c r="C1049">
-        <v>-0.2759440625618654</v>
+        <v>0</v>
       </c>
       <c r="D1049">
         <v>-0.7010958356500043</v>
@@ -31526,7 +31526,7 @@
         <v>2027</v>
       </c>
       <c r="C1050">
-        <v>-0.2872113315256776</v>
+        <v>0</v>
       </c>
       <c r="D1050">
         <v>-0.6885821530192573</v>
@@ -31555,7 +31555,7 @@
         <v>2028</v>
       </c>
       <c r="C1051">
-        <v>-0.2762907343738265</v>
+        <v>0</v>
       </c>
       <c r="D1051">
         <v>-0.661218756755746</v>
@@ -31584,7 +31584,7 @@
         <v>2024</v>
       </c>
       <c r="C1052">
-        <v>0.0123605344171628</v>
+        <v>0</v>
       </c>
       <c r="D1052">
         <v>-0.8328674851236189</v>
@@ -31613,7 +31613,7 @@
         <v>2025</v>
       </c>
       <c r="C1053">
-        <v>-0.02707315054813419</v>
+        <v>0</v>
       </c>
       <c r="D1053">
         <v>-0.8376649218832481</v>
@@ -31642,7 +31642,7 @@
         <v>2026</v>
       </c>
       <c r="C1054">
-        <v>0.0047774425462155</v>
+        <v>0</v>
       </c>
       <c r="D1054">
         <v>-0.854164125513814</v>
@@ -31671,7 +31671,7 @@
         <v>2027</v>
       </c>
       <c r="C1055">
-        <v>0.0079357770887873</v>
+        <v>0</v>
       </c>
       <c r="D1055">
         <v>-0.8639239461532608</v>
@@ -31700,7 +31700,7 @@
         <v>2028</v>
       </c>
       <c r="C1056">
-        <v>0.0113208468458626</v>
+        <v>0</v>
       </c>
       <c r="D1056">
         <v>-0.8704710455147985</v>
@@ -31729,7 +31729,7 @@
         <v>2024</v>
       </c>
       <c r="C1057">
-        <v>0.3356133195988148</v>
+        <v>0</v>
       </c>
       <c r="D1057">
         <v>-0.2176088368464082</v>
@@ -31755,7 +31755,7 @@
         <v>2025</v>
       </c>
       <c r="C1058">
-        <v>0.3392656932419725</v>
+        <v>0</v>
       </c>
       <c r="D1058">
         <v>-0.2897530050768787</v>
@@ -31781,7 +31781,7 @@
         <v>2026</v>
       </c>
       <c r="C1059">
-        <v>0.3632224143629272</v>
+        <v>0</v>
       </c>
       <c r="D1059">
         <v>-0.1559090758795372</v>
@@ -31807,7 +31807,7 @@
         <v>2027</v>
       </c>
       <c r="C1060">
-        <v>0.3837181355448119</v>
+        <v>0</v>
       </c>
       <c r="D1060">
         <v>-0.1500149941136193</v>
@@ -31833,7 +31833,7 @@
         <v>2028</v>
       </c>
       <c r="C1061">
-        <v>0.3802819998713037</v>
+        <v>0</v>
       </c>
       <c r="D1061">
         <v>-0.06954440753015866</v>
@@ -31859,7 +31859,7 @@
         <v>2024</v>
       </c>
       <c r="C1062">
-        <v>-0.7411596788389502</v>
+        <v>0</v>
       </c>
       <c r="E1062">
         <v>-0.4650881404578167</v>
@@ -31885,7 +31885,7 @@
         <v>2025</v>
       </c>
       <c r="C1063">
-        <v>-0.783358633995728</v>
+        <v>0</v>
       </c>
       <c r="E1063">
         <v>-0.4060178359969608</v>
@@ -31911,7 +31911,7 @@
         <v>2026</v>
       </c>
       <c r="C1064">
-        <v>-0.7372289206345833</v>
+        <v>0</v>
       </c>
       <c r="E1064">
         <v>-0.3233912081512658</v>
@@ -31937,7 +31937,7 @@
         <v>2027</v>
       </c>
       <c r="C1065">
-        <v>-0.7232079300174831</v>
+        <v>0</v>
       </c>
       <c r="E1065">
         <v>-0.2542094416606334</v>
@@ -31963,7 +31963,7 @@
         <v>2028</v>
       </c>
       <c r="C1066">
-        <v>-0.6891609884155393</v>
+        <v>0</v>
       </c>
       <c r="E1066">
         <v>-0.1878644070708167</v>
@@ -31989,7 +31989,7 @@
         <v>2024</v>
       </c>
       <c r="C1067">
-        <v>0.2571094855794999</v>
+        <v>-0.2571094855794999</v>
       </c>
       <c r="D1067">
         <v>-0.1632082382926972</v>
@@ -32015,7 +32015,7 @@
         <v>2025</v>
       </c>
       <c r="C1068">
-        <v>0.1483205916338208</v>
+        <v>-0.1483205916338208</v>
       </c>
       <c r="D1068">
         <v>-0.1528258158320008</v>
@@ -32041,7 +32041,7 @@
         <v>2026</v>
       </c>
       <c r="C1069">
-        <v>0.2456543680309391</v>
+        <v>-0.2456543680309391</v>
       </c>
       <c r="D1069">
         <v>-0.1476948491649462</v>
@@ -32067,7 +32067,7 @@
         <v>2027</v>
       </c>
       <c r="C1070">
-        <v>0.2226037781953303</v>
+        <v>-0.2226037781953303</v>
       </c>
       <c r="D1070">
         <v>-0.1507644995045488</v>
@@ -32093,7 +32093,7 @@
         <v>2028</v>
       </c>
       <c r="C1071">
-        <v>0.2506038508116902</v>
+        <v>-0.2506038508116902</v>
       </c>
       <c r="D1071">
         <v>-0.1498344058427639</v>
@@ -32119,7 +32119,7 @@
         <v>2024</v>
       </c>
       <c r="C1072">
-        <v>1.981071381079356</v>
+        <v>-1.981071381079356</v>
       </c>
       <c r="D1072">
         <v>0.04720127138972901</v>
@@ -32145,7 +32145,7 @@
         <v>2025</v>
       </c>
       <c r="C1073">
-        <v>1.756807107603657</v>
+        <v>-1.756807107603657</v>
       </c>
       <c r="D1073">
         <v>-0.05370520869885573</v>
@@ -32171,7 +32171,7 @@
         <v>2026</v>
       </c>
       <c r="C1074">
-        <v>2.083789282431395</v>
+        <v>-2.083789282431395</v>
       </c>
       <c r="D1074">
         <v>-0.1189069497502052</v>
@@ -32197,7 +32197,7 @@
         <v>2027</v>
       </c>
       <c r="C1075">
-        <v>2.018751022054074</v>
+        <v>-2.018751022054074</v>
       </c>
       <c r="D1075">
         <v>-0.1725943160857104</v>
@@ -32223,7 +32223,7 @@
         <v>2028</v>
       </c>
       <c r="C1076">
-        <v>2.146141865408153</v>
+        <v>-2.146141865408153</v>
       </c>
       <c r="D1076">
         <v>-0.211553960255678</v>
@@ -32249,7 +32249,7 @@
         <v>2024</v>
       </c>
       <c r="C1077">
-        <v>-0.2601413224567699</v>
+        <v>0.2601413224567699</v>
       </c>
       <c r="D1077">
         <v>0.6175831061307688</v>
@@ -32278,7 +32278,7 @@
         <v>2025</v>
       </c>
       <c r="C1078">
-        <v>-0.2734414795697902</v>
+        <v>0.2734414795697902</v>
       </c>
       <c r="D1078">
         <v>0.6501925204461138</v>
@@ -32307,7 +32307,7 @@
         <v>2026</v>
       </c>
       <c r="C1079">
-        <v>-0.2391229557840991</v>
+        <v>0.2391229557840991</v>
       </c>
       <c r="D1079">
         <v>0.6929595059843768</v>
@@ -32336,7 +32336,7 @@
         <v>2027</v>
       </c>
       <c r="C1080">
-        <v>-0.218227930264152</v>
+        <v>0.218227930264152</v>
       </c>
       <c r="D1080">
         <v>0.7219389326483167</v>
@@ -32365,7 +32365,7 @@
         <v>2028</v>
       </c>
       <c r="C1081">
-        <v>-0.201080131515791</v>
+        <v>0.201080131515791</v>
       </c>
       <c r="D1081">
         <v>0.7561032458585717</v>
@@ -32394,7 +32394,7 @@
         <v>2024</v>
       </c>
       <c r="C1082">
-        <v>-0.535251568028041</v>
+        <v>0</v>
       </c>
       <c r="D1082">
         <v>-0.9463405679323208</v>
@@ -32423,7 +32423,7 @@
         <v>2025</v>
       </c>
       <c r="C1083">
-        <v>-0.5915026256082095</v>
+        <v>0</v>
       </c>
       <c r="D1083">
         <v>-0.9921182897988442</v>
@@ -32452,7 +32452,7 @@
         <v>2026</v>
       </c>
       <c r="C1084">
-        <v>-0.5474598300089065</v>
+        <v>0</v>
       </c>
       <c r="D1084">
         <v>-1.1210145727187</v>
@@ -32481,7 +32481,7 @@
         <v>2027</v>
       </c>
       <c r="C1085">
-        <v>-0.5438422424289804</v>
+        <v>0</v>
       </c>
       <c r="D1085">
         <v>-1.164700661605691</v>
@@ -32510,7 +32510,7 @@
         <v>2028</v>
       </c>
       <c r="C1086">
-        <v>-0.5193093012818147</v>
+        <v>0</v>
       </c>
       <c r="D1086">
         <v>-1.26710297448059</v>
@@ -32669,7 +32669,7 @@
         <v>2024</v>
       </c>
       <c r="C1092">
-        <v>0.4216417794410794</v>
+        <v>-0.4216417794410794</v>
       </c>
       <c r="D1092">
         <v>-0.1839914101301301</v>
@@ -32698,7 +32698,7 @@
         <v>2025</v>
       </c>
       <c r="C1093">
-        <v>0.4514311008924707</v>
+        <v>-0.4514311008924707</v>
       </c>
       <c r="D1093">
         <v>-0.3084763926314694</v>
@@ -32727,7 +32727,7 @@
         <v>2026</v>
       </c>
       <c r="C1094">
-        <v>0.4739487790644989</v>
+        <v>-0.4739487790644989</v>
       </c>
       <c r="D1094">
         <v>-0.3924129165827439</v>
@@ -32756,7 +32756,7 @@
         <v>2027</v>
       </c>
       <c r="C1095">
-        <v>0.5071112848862686</v>
+        <v>-0.5071112848862686</v>
       </c>
       <c r="D1095">
         <v>-0.4592771312562641</v>
@@ -32785,7 +32785,7 @@
         <v>2028</v>
       </c>
       <c r="C1096">
-        <v>0.505189658754111</v>
+        <v>-0.505189658754111</v>
       </c>
       <c r="D1096">
         <v>-0.5102840532006051</v>
@@ -32814,7 +32814,7 @@
         <v>2024</v>
       </c>
       <c r="C1097">
-        <v>0.5045271885123634</v>
+        <v>0</v>
       </c>
       <c r="D1097">
         <v>-0.65254253311513</v>
@@ -32840,7 +32840,7 @@
         <v>2025</v>
       </c>
       <c r="C1098">
-        <v>0.6190275000192892</v>
+        <v>0</v>
       </c>
       <c r="D1098">
         <v>-0.7191247008132345</v>
@@ -32866,7 +32866,7 @@
         <v>2026</v>
       </c>
       <c r="C1099">
-        <v>0.6484320984855809</v>
+        <v>0</v>
       </c>
       <c r="D1099">
         <v>-0.7801086955227677</v>
@@ -32892,7 +32892,7 @@
         <v>2027</v>
       </c>
       <c r="C1100">
-        <v>0.7284365508562441</v>
+        <v>0</v>
       </c>
       <c r="D1100">
         <v>-0.836742221607693</v>
@@ -32918,7 +32918,7 @@
         <v>2028</v>
       </c>
       <c r="C1101">
-        <v>0.7461967798386535</v>
+        <v>0</v>
       </c>
       <c r="D1101">
         <v>-0.8864226540853434</v>
@@ -32944,7 +32944,7 @@
         <v>2024</v>
       </c>
       <c r="C1102">
-        <v>-0.9161815826603762</v>
+        <v>0</v>
       </c>
       <c r="D1102">
         <v>-1.176055423492917</v>
@@ -32973,7 +32973,7 @@
         <v>2025</v>
       </c>
       <c r="C1103">
-        <v>-0.9464362383280672</v>
+        <v>0</v>
       </c>
       <c r="D1103">
         <v>-1.200198471756227</v>
@@ -33002,7 +33002,7 @@
         <v>2026</v>
       </c>
       <c r="C1104">
-        <v>-0.8985326523311871</v>
+        <v>0</v>
       </c>
       <c r="D1104">
         <v>-1.222407900465496</v>
@@ -33031,7 +33031,7 @@
         <v>2027</v>
       </c>
       <c r="C1105">
-        <v>-0.8756687623282323</v>
+        <v>0</v>
       </c>
       <c r="D1105">
         <v>-1.238422399166832</v>
@@ -33060,7 +33060,7 @@
         <v>2028</v>
       </c>
       <c r="C1106">
-        <v>-0.8335349230353315</v>
+        <v>0</v>
       </c>
       <c r="D1106">
         <v>-1.250452656856007</v>
@@ -33089,7 +33089,7 @@
         <v>2024</v>
       </c>
       <c r="C1107">
-        <v>-0.2113422903664309</v>
+        <v>0</v>
       </c>
       <c r="D1107">
         <v>-0.8112224899191324</v>
@@ -33118,7 +33118,7 @@
         <v>2025</v>
       </c>
       <c r="C1108">
-        <v>-0.2896983603016158</v>
+        <v>0</v>
       </c>
       <c r="D1108">
         <v>-0.9738605104319724</v>
@@ -33147,7 +33147,7 @@
         <v>2026</v>
       </c>
       <c r="C1109">
-        <v>-0.2489384621712489</v>
+        <v>0</v>
       </c>
       <c r="D1109">
         <v>-0.960398162797134</v>
@@ -33176,7 +33176,7 @@
         <v>2027</v>
       </c>
       <c r="C1110">
-        <v>-0.2616862137389557</v>
+        <v>0</v>
       </c>
       <c r="D1110">
         <v>-1.048086490876726</v>
@@ -33205,7 +33205,7 @@
         <v>2028</v>
       </c>
       <c r="C1111">
-        <v>-0.2521195326537831</v>
+        <v>0</v>
       </c>
       <c r="D1111">
         <v>-1.063344982559002</v>
@@ -33234,7 +33234,7 @@
         <v>2024</v>
       </c>
       <c r="C1112">
-        <v>0.9799965182629508</v>
+        <v>0</v>
       </c>
       <c r="D1112">
         <v>-0.4131042414997981</v>
@@ -33260,7 +33260,7 @@
         <v>2025</v>
       </c>
       <c r="C1113">
-        <v>0.8223884614200487</v>
+        <v>0</v>
       </c>
       <c r="D1113">
         <v>-0.3273914832437106</v>
@@ -33286,7 +33286,7 @@
         <v>2026</v>
       </c>
       <c r="C1114">
-        <v>0.930698310385441</v>
+        <v>0</v>
       </c>
       <c r="D1114">
         <v>-0.2699098219170954</v>
@@ -33312,7 +33312,7 @@
         <v>2027</v>
       </c>
       <c r="C1115">
-        <v>0.8751923882939175</v>
+        <v>0</v>
       </c>
       <c r="D1115">
         <v>-0.2373342272596989</v>
@@ -33338,7 +33338,7 @@
         <v>2028</v>
       </c>
       <c r="C1116">
-        <v>0.8816478863206985</v>
+        <v>0</v>
       </c>
       <c r="D1116">
         <v>-0.2138791263995284</v>
@@ -33364,7 +33364,7 @@
         <v>2024</v>
       </c>
       <c r="C1117">
-        <v>-0.1377593088036342</v>
+        <v>0</v>
       </c>
       <c r="D1117">
         <v>0.03533059812102036</v>
@@ -33390,7 +33390,7 @@
         <v>2025</v>
       </c>
       <c r="C1118">
-        <v>-0.2201450809714117</v>
+        <v>0</v>
       </c>
       <c r="D1118">
         <v>-0.00489952436925929</v>
@@ -33416,7 +33416,7 @@
         <v>2026</v>
       </c>
       <c r="C1119">
-        <v>-0.1802763970179744</v>
+        <v>0</v>
       </c>
       <c r="D1119">
         <v>-0.03760942765375282</v>
@@ -33442,7 +33442,7 @@
         <v>2027</v>
       </c>
       <c r="C1120">
-        <v>-0.19625176714146</v>
+        <v>0</v>
       </c>
       <c r="D1120">
         <v>-0.07375720283822781</v>
@@ -33468,7 +33468,7 @@
         <v>2028</v>
       </c>
       <c r="C1121">
-        <v>-0.1900322386240589</v>
+        <v>0</v>
       </c>
       <c r="D1121">
         <v>-0.1026584241015077</v>
@@ -33494,7 +33494,7 @@
         <v>2024</v>
       </c>
       <c r="C1122">
-        <v>-0.7594591587792615</v>
+        <v>0.7594591587792615</v>
       </c>
       <c r="D1122">
         <v>0.1296232131183284</v>
@@ -33514,7 +33514,7 @@
         <v>2025</v>
       </c>
       <c r="C1123">
-        <v>-0.6521183048147366</v>
+        <v>0.6521183048147366</v>
       </c>
       <c r="D1123">
         <v>0.1317150379264316</v>
@@ -33534,7 +33534,7 @@
         <v>2026</v>
       </c>
       <c r="C1124">
-        <v>-0.595079392757344</v>
+        <v>0.595079392757344</v>
       </c>
       <c r="D1124">
         <v>0.07104908844256634</v>
@@ -33554,7 +33554,7 @@
         <v>2027</v>
       </c>
       <c r="C1125">
-        <v>-0.4958626600947946</v>
+        <v>0.4958626600947946</v>
       </c>
       <c r="D1125">
         <v>0.06853203997058328</v>
@@ -33574,7 +33574,7 @@
         <v>2028</v>
       </c>
       <c r="C1126">
-        <v>-0.4242069009856102</v>
+        <v>0.4242069009856102</v>
       </c>
       <c r="D1126">
         <v>0.01809459761290006</v>
@@ -33594,7 +33594,7 @@
         <v>2024</v>
       </c>
       <c r="C1127">
-        <v>1.36094824531478</v>
+        <v>0</v>
       </c>
       <c r="D1127">
         <v>-0.7914664876743479</v>
@@ -33623,7 +33623,7 @@
         <v>2025</v>
       </c>
       <c r="C1128">
-        <v>1.067064109777278</v>
+        <v>0</v>
       </c>
       <c r="D1128">
         <v>-0.8073162851709186</v>
@@ -33652,7 +33652,7 @@
         <v>2026</v>
       </c>
       <c r="C1129">
-        <v>1.111555333907432</v>
+        <v>0</v>
       </c>
       <c r="D1129">
         <v>-0.8197895011981987</v>
@@ -33681,7 +33681,7 @@
         <v>2027</v>
       </c>
       <c r="C1130">
-        <v>0.872107890587666</v>
+        <v>0</v>
       </c>
       <c r="D1130">
         <v>-0.8300284381782616</v>
@@ -33710,7 +33710,7 @@
         <v>2028</v>
       </c>
       <c r="C1131">
-        <v>0.8373824306185951</v>
+        <v>0</v>
       </c>
       <c r="D1131">
         <v>-0.8358398924023077</v>
@@ -33739,7 +33739,7 @@
         <v>2024</v>
       </c>
       <c r="C1132">
-        <v>0.212650620238838</v>
+        <v>-0.212650620238838</v>
       </c>
       <c r="D1132">
         <v>0.03464315224767662</v>
@@ -33768,7 +33768,7 @@
         <v>2025</v>
       </c>
       <c r="C1133">
-        <v>0.06818739704543531</v>
+        <v>-0.06818739704543531</v>
       </c>
       <c r="D1133">
         <v>0.1216704556170939</v>
@@ -33797,7 +33797,7 @@
         <v>2026</v>
       </c>
       <c r="C1134">
-        <v>0.2007274289213073</v>
+        <v>-0.2007274289213073</v>
       </c>
       <c r="D1134">
         <v>0.05999361155616256</v>
@@ -33826,7 +33826,7 @@
         <v>2027</v>
       </c>
       <c r="C1135">
-        <v>0.1327273637374293</v>
+        <v>-0.1327273637374293</v>
       </c>
       <c r="D1135">
         <v>0.09273813844955243</v>
@@ -33855,7 +33855,7 @@
         <v>2028</v>
       </c>
       <c r="C1136">
-        <v>0.1888271553578773</v>
+        <v>-0.1888271553578773</v>
       </c>
       <c r="D1136">
         <v>0.06672622336359144</v>
@@ -33884,7 +33884,7 @@
         <v>2024</v>
       </c>
       <c r="C1137">
-        <v>1.175559436656752</v>
+        <v>-1.175559436656752</v>
       </c>
       <c r="D1137">
         <v>0.186277374275127</v>
@@ -33913,7 +33913,7 @@
         <v>2025</v>
       </c>
       <c r="C1138">
-        <v>1.392612450779433</v>
+        <v>-1.392612450779433</v>
       </c>
       <c r="D1138">
         <v>0.1848202811519867</v>
@@ -33942,7 +33942,7 @@
         <v>2026</v>
       </c>
       <c r="C1139">
-        <v>1.501813566817375</v>
+        <v>-1.501813566817375</v>
       </c>
       <c r="D1139">
         <v>0.3019778025555833</v>
@@ -33971,7 +33971,7 @@
         <v>2027</v>
       </c>
       <c r="C1140">
-        <v>1.683225772894758</v>
+        <v>-1.683225772894758</v>
       </c>
       <c r="D1140">
         <v>0.3162059414348282</v>
@@ -34000,7 +34000,7 @@
         <v>2028</v>
       </c>
       <c r="C1141">
-        <v>1.766681787495797</v>
+        <v>-1.766681787495797</v>
       </c>
       <c r="D1141">
         <v>0.4073944457113143</v>
@@ -34029,7 +34029,7 @@
         <v>2024</v>
       </c>
       <c r="C1142">
-        <v>1.015065264056701</v>
+        <v>-1.015065264056701</v>
       </c>
       <c r="D1142">
         <v>-0.02857819511696285</v>
@@ -34061,7 +34061,7 @@
         <v>2025</v>
       </c>
       <c r="C1143">
-        <v>1.243225107705453</v>
+        <v>-1.243225107705453</v>
       </c>
       <c r="D1143">
         <v>-0.03664441461219901</v>
@@ -34093,7 +34093,7 @@
         <v>2026</v>
       </c>
       <c r="C1144">
-        <v>1.355228275321736</v>
+        <v>-1.355228275321736</v>
       </c>
       <c r="D1144">
         <v>-0.0483360487318985</v>
@@ -34125,7 +34125,7 @@
         <v>2027</v>
       </c>
       <c r="C1145">
-        <v>1.545382577085911</v>
+        <v>-1.545382577085911</v>
       </c>
       <c r="D1145">
         <v>-0.0621744491217353</v>
@@ -34157,7 +34157,7 @@
         <v>2028</v>
       </c>
       <c r="C1146">
-        <v>1.639079576406366</v>
+        <v>-1.639079576406366</v>
       </c>
       <c r="D1146">
         <v>-0.07048042566312457</v>
@@ -34189,7 +34189,7 @@
         <v>2024</v>
       </c>
       <c r="C1147">
-        <v>-0.7820896151380039</v>
+        <v>1.564179230276008</v>
       </c>
       <c r="D1147">
         <v>0.1307860840293005</v>
@@ -34221,7 +34221,7 @@
         <v>2025</v>
       </c>
       <c r="C1148">
-        <v>-0.6819479189177269</v>
+        <v>1.363895837835454</v>
       </c>
       <c r="D1148">
         <v>0.1394479868221955</v>
@@ -34253,7 +34253,7 @@
         <v>2026</v>
       </c>
       <c r="C1149">
-        <v>-0.6054795691406715</v>
+        <v>1.210959138281343</v>
       </c>
       <c r="D1149">
         <v>0.1549298293083164</v>
@@ -34285,7 +34285,7 @@
         <v>2027</v>
       </c>
       <c r="C1150">
-        <v>-0.4946688929141621</v>
+        <v>0.9893377858283242</v>
       </c>
       <c r="D1150">
         <v>0.1628067255198446</v>
@@ -34317,7 +34317,7 @@
         <v>2028</v>
       </c>
       <c r="C1151">
-        <v>-0.4083786152745599</v>
+        <v>0.8167572305491198</v>
       </c>
       <c r="D1151">
         <v>0.1759688496723356</v>
@@ -34349,7 +34349,7 @@
         <v>2024</v>
       </c>
       <c r="C1152">
-        <v>1.588053050793188</v>
+        <v>-1.588053050793188</v>
       </c>
       <c r="D1152">
         <v>0.7271829319140076</v>
@@ -34375,7 +34375,7 @@
         <v>2025</v>
       </c>
       <c r="C1153">
-        <v>1.390222376048696</v>
+        <v>-1.390222376048696</v>
       </c>
       <c r="D1153">
         <v>0.4616483894554763</v>
@@ -34401,7 +34401,7 @@
         <v>2026</v>
       </c>
       <c r="C1154">
-        <v>1.6889789068855</v>
+        <v>-1.6889789068855</v>
       </c>
       <c r="D1154">
         <v>0.6204762422365083</v>
@@ -34427,7 +34427,7 @@
         <v>2027</v>
       </c>
       <c r="C1155">
-        <v>1.637690822498667</v>
+        <v>-1.637690822498667</v>
       </c>
       <c r="D1155">
         <v>0.4862649734966563</v>
@@ -34453,7 +34453,7 @@
         <v>2028</v>
       </c>
       <c r="C1156">
-        <v>1.760359124794449</v>
+        <v>-1.760359124794449</v>
       </c>
       <c r="D1156">
         <v>0.5531989742024914</v>
@@ -34479,7 +34479,7 @@
         <v>2024</v>
       </c>
       <c r="C1157">
-        <v>-0.4832166856888082</v>
+        <v>0.4832166856888082</v>
       </c>
       <c r="D1157">
         <v>0.5910280327012453</v>
@@ -34508,7 +34508,7 @@
         <v>2025</v>
       </c>
       <c r="C1158">
-        <v>-0.3617848955564531</v>
+        <v>0.3617848955564531</v>
       </c>
       <c r="D1158">
         <v>0.552095659349505</v>
@@ -34537,7 +34537,7 @@
         <v>2026</v>
       </c>
       <c r="C1159">
-        <v>-0.2794066631872371</v>
+        <v>0.2794066631872371</v>
       </c>
       <c r="D1159">
         <v>0.5540139687031965</v>
@@ -34566,7 +34566,7 @@
         <v>2027</v>
       </c>
       <c r="C1160">
-        <v>-0.1554005480694766</v>
+        <v>0.1554005480694766</v>
       </c>
       <c r="D1160">
         <v>0.5337469129643294</v>
@@ -34595,7 +34595,7 @@
         <v>2028</v>
       </c>
       <c r="C1161">
-        <v>-0.0678781899589479</v>
+        <v>0.0678781899589479</v>
       </c>
       <c r="D1161">
         <v>0.5257605031849215</v>
@@ -34624,7 +34624,7 @@
         <v>2024</v>
       </c>
       <c r="C1162">
-        <v>0.910644678397556</v>
+        <v>-0.910644678397556</v>
       </c>
       <c r="D1162">
         <v>0.3749897569434648</v>
@@ -34647,7 +34647,7 @@
         <v>2025</v>
       </c>
       <c r="C1163">
-        <v>0.7593233216589912</v>
+        <v>-0.7593233216589912</v>
       </c>
       <c r="D1163">
         <v>0.3330364042098692</v>
@@ -34670,7 +34670,7 @@
         <v>2026</v>
       </c>
       <c r="C1164">
-        <v>1.009085116084694</v>
+        <v>-1.009085116084694</v>
       </c>
       <c r="D1164">
         <v>0.2986982097021347</v>
@@ -34693,7 +34693,7 @@
         <v>2027</v>
       </c>
       <c r="C1165">
-        <v>0.9821369568193788</v>
+        <v>-0.9821369568193788</v>
       </c>
       <c r="D1165">
         <v>0.2584243386570079</v>
@@ -34716,7 +34716,7 @@
         <v>2028</v>
       </c>
       <c r="C1166">
-        <v>1.096559507976982</v>
+        <v>-1.096559507976982</v>
       </c>
       <c r="D1166">
         <v>0.226181967003261</v>
@@ -34739,7 +34739,7 @@
         <v>2024</v>
       </c>
       <c r="C1167">
-        <v>2.188904797050017</v>
+        <v>-2.188904797050017</v>
       </c>
       <c r="D1167">
         <v>0.4357871872457335</v>
@@ -34762,7 +34762,7 @@
         <v>2025</v>
       </c>
       <c r="C1168">
-        <v>1.950662087003294</v>
+        <v>-1.950662087003294</v>
       </c>
       <c r="D1168">
         <v>0.26006040840343</v>
@@ -34785,7 +34785,7 @@
         <v>2026</v>
       </c>
       <c r="C1169">
-        <v>2.292570358101002</v>
+        <v>-2.292570358101002</v>
       </c>
       <c r="D1169">
         <v>0.1593677588617516</v>
@@ -34808,7 +34808,7 @@
         <v>2027</v>
       </c>
       <c r="C1170">
-        <v>2.220260825101441</v>
+        <v>-2.220260825101441</v>
       </c>
       <c r="D1170">
         <v>0.00536817660808373</v>
@@ -34831,7 +34831,7 @@
         <v>2028</v>
       </c>
       <c r="C1171">
-        <v>2.350149008086893</v>
+        <v>-2.350149008086893</v>
       </c>
       <c r="D1171">
         <v>-0.08938779458133532</v>
@@ -34854,7 +34854,7 @@
         <v>2024</v>
       </c>
       <c r="C1172">
-        <v>-0.3930260641310187</v>
+        <v>0.3930260641310187</v>
       </c>
       <c r="D1172">
         <v>0.3484343435354163</v>
@@ -34880,7 +34880,7 @@
         <v>2025</v>
       </c>
       <c r="C1173">
-        <v>-0.4576130849580753</v>
+        <v>0.4576130849580753</v>
       </c>
       <c r="D1173">
         <v>0.4353308675188717</v>
@@ -34906,7 +34906,7 @@
         <v>2026</v>
       </c>
       <c r="C1174">
-        <v>-0.3011332505316427</v>
+        <v>0.3011332505316427</v>
       </c>
       <c r="D1174">
         <v>0.1356284858170597</v>
@@ -34932,7 +34932,7 @@
         <v>2027</v>
       </c>
       <c r="C1175">
-        <v>-0.2831108191796222</v>
+        <v>0.2831108191796222</v>
       </c>
       <c r="D1175">
         <v>0.2202684781157296</v>
@@ -34958,7 +34958,7 @@
         <v>2028</v>
       </c>
       <c r="C1176">
-        <v>-0.1842475111446732</v>
+        <v>0.1842475111446732</v>
       </c>
       <c r="D1176">
         <v>-0.05615424994060836</v>
@@ -34984,7 +34984,7 @@
         <v>2024</v>
       </c>
       <c r="C1177">
-        <v>0.7274094681418896</v>
+        <v>-0.7274094681418896</v>
       </c>
       <c r="E1177">
         <v>-0.4788511612018827</v>
@@ -35007,7 +35007,7 @@
         <v>2025</v>
       </c>
       <c r="C1178">
-        <v>0.5874639677715299</v>
+        <v>-0.5874639677715299</v>
       </c>
       <c r="E1178">
         <v>-0.572525067912058</v>
@@ -35030,7 +35030,7 @@
         <v>2026</v>
       </c>
       <c r="C1179">
-        <v>0.8244110628078167</v>
+        <v>-0.8244110628078167</v>
       </c>
       <c r="E1179">
         <v>-0.6238007844218062</v>
@@ -35053,7 +35053,7 @@
         <v>2027</v>
       </c>
       <c r="C1180">
-        <v>0.8032335900634974</v>
+        <v>-0.8032335900634974</v>
       </c>
       <c r="E1180">
         <v>-0.6627062460173166</v>
@@ -35076,7 +35076,7 @@
         <v>2028</v>
       </c>
       <c r="C1181">
-        <v>0.9155602926276188</v>
+        <v>-0.9155602926276188</v>
       </c>
       <c r="E1181">
         <v>-0.6885057582994614</v>
@@ -35259,7 +35259,7 @@
         <v>2024</v>
       </c>
       <c r="C1187">
-        <v>-1.130265825481729</v>
+        <v>0</v>
       </c>
       <c r="D1187">
         <v>2.050216493302933</v>
@@ -35288,7 +35288,7 @@
         <v>2025</v>
       </c>
       <c r="C1188">
-        <v>-1.125328323313013</v>
+        <v>0</v>
       </c>
       <c r="D1188">
         <v>2.170266860915951</v>
@@ -35317,7 +35317,7 @@
         <v>2026</v>
       </c>
       <c r="C1189">
-        <v>-1.099882342504352</v>
+        <v>0</v>
       </c>
       <c r="D1189">
         <v>2.031452447525021</v>
@@ -35346,7 +35346,7 @@
         <v>2027</v>
       </c>
       <c r="C1190">
-        <v>-1.066320662651502</v>
+        <v>0</v>
       </c>
       <c r="D1190">
         <v>2.111040067562215</v>
@@ -35375,7 +35375,7 @@
         <v>2028</v>
       </c>
       <c r="C1191">
-        <v>-1.025589433145626</v>
+        <v>0</v>
       </c>
       <c r="D1191">
         <v>1.992518356787174</v>
@@ -35404,7 +35404,7 @@
         <v>2024</v>
       </c>
       <c r="C1192">
-        <v>-1.4387085112616</v>
+        <v>0</v>
       </c>
       <c r="D1192">
         <v>1.113405975645891</v>
@@ -35430,7 +35430,7 @@
         <v>2025</v>
       </c>
       <c r="C1193">
-        <v>-1.422395607231709</v>
+        <v>0</v>
       </c>
       <c r="D1193">
         <v>1.1787787996872</v>
@@ -35456,7 +35456,7 @@
         <v>2026</v>
       </c>
       <c r="C1194">
-        <v>-1.38219741825243</v>
+        <v>0</v>
       </c>
       <c r="D1194">
         <v>1.254447630709396</v>
@@ -35482,7 +35482,7 @@
         <v>2027</v>
       </c>
       <c r="C1195">
-        <v>-1.332960139943733</v>
+        <v>0</v>
       </c>
       <c r="D1195">
         <v>1.309898787968923</v>
@@ -35508,7 +35508,7 @@
         <v>2028</v>
       </c>
       <c r="C1196">
-        <v>-1.272641112848638</v>
+        <v>0</v>
       </c>
       <c r="D1196">
         <v>1.370174154874733</v>
@@ -35694,7 +35694,7 @@
         <v>2024</v>
       </c>
       <c r="C1202">
-        <v>-1.781550202038881</v>
+        <v>0</v>
       </c>
       <c r="I1202">
         <v>-1.139580579556082</v>
@@ -35708,7 +35708,7 @@
         <v>2025</v>
       </c>
       <c r="C1203">
-        <v>-1.75272317466252</v>
+        <v>0</v>
       </c>
       <c r="I1203">
         <v>-1.153925071011537</v>
@@ -35722,7 +35722,7 @@
         <v>2026</v>
       </c>
       <c r="C1204">
-        <v>-1.696093857008251</v>
+        <v>0</v>
       </c>
       <c r="I1204">
         <v>-1.177436549144997</v>
@@ -35736,7 +35736,7 @@
         <v>2027</v>
       </c>
       <c r="C1205">
-        <v>-1.629517627006499</v>
+        <v>0</v>
       </c>
       <c r="I1205">
         <v>-1.209009002669389</v>
@@ -35750,7 +35750,7 @@
         <v>2028</v>
       </c>
       <c r="C1206">
-        <v>-1.547420810823148</v>
+        <v>0</v>
       </c>
       <c r="I1206">
         <v>-1.248309053115991</v>
@@ -35764,7 +35764,7 @@
         <v>2024</v>
       </c>
       <c r="C1207">
-        <v>0.5737107336785754</v>
+        <v>0</v>
       </c>
       <c r="D1207">
         <v>-0.6508327405663186</v>
@@ -35796,7 +35796,7 @@
         <v>2025</v>
       </c>
       <c r="C1208">
-        <v>0.5500201225659319</v>
+        <v>0</v>
       </c>
       <c r="D1208">
         <v>-0.5556411091194779</v>
@@ -35828,7 +35828,7 @@
         <v>2026</v>
       </c>
       <c r="C1209">
-        <v>0.4935952390577745</v>
+        <v>0</v>
       </c>
       <c r="D1209">
         <v>-0.4668032076566895</v>
@@ -35860,7 +35860,7 @@
         <v>2027</v>
       </c>
       <c r="C1210">
-        <v>0.4476483160455727</v>
+        <v>0</v>
       </c>
       <c r="D1210">
         <v>-0.3828903782694597</v>
@@ -35892,7 +35892,7 @@
         <v>2028</v>
       </c>
       <c r="C1211">
-        <v>0.3858093464224861</v>
+        <v>0</v>
       </c>
       <c r="D1211">
         <v>-0.2990300814426978</v>
@@ -35924,7 +35924,7 @@
         <v>2024</v>
       </c>
       <c r="C1212">
-        <v>0.4912385402967973</v>
+        <v>0</v>
       </c>
       <c r="D1212">
         <v>2.125711449727534</v>
@@ -35956,7 +35956,7 @@
         <v>2025</v>
       </c>
       <c r="C1213">
-        <v>0.5880567091647931</v>
+        <v>0</v>
       </c>
       <c r="D1213">
         <v>2.132145954234282</v>
@@ -35988,7 +35988,7 @@
         <v>2026</v>
       </c>
       <c r="C1214">
-        <v>0.5470729412380618</v>
+        <v>0</v>
       </c>
       <c r="D1214">
         <v>2.147865511799601</v>
@@ -36020,7 +36020,7 @@
         <v>2027</v>
       </c>
       <c r="C1215">
-        <v>0.5819557940393532</v>
+        <v>0</v>
       </c>
       <c r="D1215">
         <v>2.135872107990858</v>
@@ -36052,7 +36052,7 @@
         <v>2028</v>
       </c>
       <c r="C1216">
-        <v>0.5508564128908338</v>
+        <v>0</v>
       </c>
       <c r="D1216">
         <v>2.133179493726659</v>
@@ -36084,7 +36084,7 @@
         <v>2024</v>
       </c>
       <c r="C1217">
-        <v>0.4295000251483512</v>
+        <v>0</v>
       </c>
       <c r="D1217">
         <v>1.17559491498552</v>
@@ -36113,7 +36113,7 @@
         <v>2025</v>
       </c>
       <c r="C1218">
-        <v>0.5269826384391741</v>
+        <v>0</v>
       </c>
       <c r="D1218">
         <v>0.7854903225150488</v>
@@ -36142,7 +36142,7 @@
         <v>2026</v>
       </c>
       <c r="C1219">
-        <v>0.5024632950748971</v>
+        <v>0</v>
       </c>
       <c r="D1219">
         <v>0.4275694594922213</v>
@@ -36171,7 +36171,7 @@
         <v>2027</v>
       </c>
       <c r="C1220">
-        <v>0.5440504401651522</v>
+        <v>0</v>
       </c>
       <c r="D1220">
         <v>0.07795787277934026</v>
@@ -36200,7 +36200,7 @@
         <v>2028</v>
       </c>
       <c r="C1221">
-        <v>0.5245114425686109</v>
+        <v>0</v>
       </c>
       <c r="D1221">
         <v>-0.2469046026451726</v>
@@ -36229,7 +36229,7 @@
         <v>2024</v>
       </c>
       <c r="C1222">
-        <v>4.204959515641131</v>
+        <v>-4</v>
       </c>
       <c r="E1222">
         <v>0.7204152471274513</v>
@@ -36252,7 +36252,7 @@
         <v>2025</v>
       </c>
       <c r="C1223">
-        <v>5.089173506351654</v>
+        <v>-4</v>
       </c>
       <c r="E1223">
         <v>0.8369871694394549</v>
@@ -36275,7 +36275,7 @@
         <v>2026</v>
       </c>
       <c r="C1224">
-        <v>5.415235083334916</v>
+        <v>-4</v>
       </c>
       <c r="E1224">
         <v>0.9182743746441998</v>
@@ -36298,7 +36298,7 @@
         <v>2027</v>
       </c>
       <c r="C1225">
-        <v>6.030023287368958</v>
+        <v>-4</v>
       </c>
       <c r="E1225">
         <v>0.970938888639186</v>
@@ -36321,7 +36321,7 @@
         <v>2028</v>
       </c>
       <c r="C1226">
-        <v>6.374137332883872</v>
+        <v>-4</v>
       </c>
       <c r="E1226">
         <v>1.037470741791551</v>
@@ -37125,7 +37125,7 @@
         <v>-1.380902815338509</v>
       </c>
       <c r="F1262">
-        <v>4.100004673277354</v>
+        <v>4</v>
       </c>
       <c r="H1262">
         <v>1.5935236148265</v>
@@ -37667,7 +37667,7 @@
         <v>-1.054785405418776</v>
       </c>
       <c r="E1287">
-        <v>5.213245809427659</v>
+        <v>4</v>
       </c>
       <c r="F1287">
         <v>-0.6507175535664609</v>
@@ -37687,7 +37687,7 @@
         <v>-1.013597671848344</v>
       </c>
       <c r="E1288">
-        <v>4.927602611750167</v>
+        <v>4</v>
       </c>
       <c r="F1288">
         <v>-0.6324681343244698</v>
@@ -37707,7 +37707,7 @@
         <v>-0.9732167109075016</v>
       </c>
       <c r="E1289">
-        <v>4.550600848247245</v>
+        <v>4</v>
       </c>
       <c r="F1289">
         <v>-0.6099626750204649</v>
@@ -37727,7 +37727,7 @@
         <v>-0.9318362128387414</v>
       </c>
       <c r="E1290">
-        <v>4.116400315756557</v>
+        <v>4</v>
       </c>
       <c r="F1290">
         <v>-0.5879754744021466</v>
